--- a/utility_core/static/src/Migration_Template.xlsx
+++ b/utility_core/static/src/Migration_Template.xlsx
@@ -1,150 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="العملاء" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
-  <si>
-    <t>الاسم</t>
-  </si>
-  <si>
-    <t>الموبايل</t>
-  </si>
-  <si>
-    <t>الرقم الوطني</t>
-  </si>
-  <si>
-    <t>رقم المشترك</t>
-  </si>
-  <si>
-    <t>هل فعال؟</t>
-  </si>
-  <si>
-    <t>رمز المنطقة</t>
-  </si>
-  <si>
-    <t>رمز الفرع</t>
-  </si>
-  <si>
-    <t>رمز الفئة</t>
-  </si>
-  <si>
-    <t>رمز نوع المشترك</t>
-  </si>
-  <si>
-    <t>رمز قالب العقد</t>
-  </si>
-  <si>
-    <t>رقم العداد</t>
-  </si>
-  <si>
-    <t>اخر قراءة مسجلة</t>
-  </si>
-  <si>
-    <t>الرصيد السابق (الخط الساخن)</t>
-  </si>
-  <si>
-    <t>الرصيد الحالي (الافتتاحي)</t>
-  </si>
-  <si>
-    <t>محمد عبدالله</t>
-  </si>
-  <si>
-    <t>777123456</t>
-  </si>
-  <si>
-    <t>1234567890</t>
-  </si>
-  <si>
-    <t>CUST-001</t>
-  </si>
-  <si>
-    <t>True</t>
-  </si>
-  <si>
-    <t>REG-01</t>
-  </si>
-  <si>
-    <t>AREA-01</t>
-  </si>
-  <si>
-    <t>CAT-C</t>
-  </si>
-  <si>
-    <t>SUB-1</t>
-  </si>
-  <si>
-    <t>CONT-01</t>
-  </si>
-  <si>
-    <t>MTR-999</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>شركة الأفق</t>
-  </si>
-  <si>
-    <t>777654321</t>
-  </si>
-  <si>
-    <t>0987654321</t>
-  </si>
-  <si>
-    <t>CUST-002</t>
-  </si>
-  <si>
-    <t>False</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD3D3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -152,36 +42,85 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -469,138 +408,117 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="15.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" customWidth="1"/>
-    <col min="12" max="12" width="15.7109375" customWidth="1"/>
-    <col min="13" max="13" width="15.7109375" customWidth="1"/>
-    <col min="14" max="14" width="15.7109375" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2">
-        <v>1542.5</v>
-      </c>
-      <c r="M2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>الاسم</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>الموبايل</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الرقم الوطني</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>رقم المشترك</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>الرقم الجديد</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>رقم الحرف</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>هل فعال؟</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>رمز المنطقة</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>رمز الفرع</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>رمز الفئة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رمز نوع المشترك</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>رمز قالب العقد</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>رقم العداد</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>قراءة العداد في النظام</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>قراءة الافتتاح</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>اخر قراءة مسجلة</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>الرصيد السابق (الخط الساخن)</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>الرصيد الحالي (الافتتاحي)</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>نوع الفاز (single/three)</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>محول خاص (نعم/لا)</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/utility_core/static/src/Migration_Template.xlsx
+++ b/utility_core/static/src/Migration_Template.xlsx
@@ -7,9 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="بيانات التهيئة" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تعليمات الاستيراد" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'بيانات التهيئة'!$A$4:$S$9</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +28,116 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Cairo"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Cairo"/>
+      <i val="1"/>
+      <color rgb="00424242"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Cairo"/>
+      <b val="1"/>
+      <color rgb="001A237E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00212121"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Cairo"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Cairo"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Cairo"/>
+      <color rgb="00212121"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Cairo"/>
+      <b val="1"/>
+      <color rgb="001A237E"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Cairo"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A237E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BBDEFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8BBD0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E1BEE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +145,92 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BDBDBD"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BDBDBD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BDBDBD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BDBDBD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,112 +596,1074 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="44" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>نموذج استيراد بيانات المشتركين - نظام توزيع الكهرباء</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>يرجى التاكد من ملء جميع الخانات الالزامية (*). الحقل هل فعال يقبل: نعم / لا  |  نوع الفاز: single / three  |  محول خاص: نعم / لا</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>البيانات الشخصية</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>الحالة</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>بيانات الترميز (Legacy)</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>بيانات العداد والارصدة</t>
+        </is>
+      </c>
+      <c r="R3" s="7" t="inlineStr">
+        <is>
+          <t>بيانات اضافية</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>الاسم *</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>الموبايل *</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>الرقم الوطني</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>رقم المشترك *</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>الرقم الجديد</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>رقم الحرف</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>هل فعال؟ *</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>رمز المنطقة</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>رمز الفرع</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>رمز الفئة</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>رمز نوع المشترك</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>رمز قالب العقد *</t>
+        </is>
+      </c>
+      <c r="M4" s="11" t="inlineStr">
+        <is>
+          <t>رقم العداد *</t>
+        </is>
+      </c>
+      <c r="N4" s="11" t="inlineStr">
+        <is>
+          <t>قراءة العداد في النظام القديم</t>
+        </is>
+      </c>
+      <c r="O4" s="11" t="inlineStr">
+        <is>
+          <t>القراءة عند تفعيل العقد</t>
+        </is>
+      </c>
+      <c r="P4" s="11" t="inlineStr">
+        <is>
+          <t>الرصيد السابق (الخط الساخن)</t>
+        </is>
+      </c>
+      <c r="Q4" s="11" t="inlineStr">
+        <is>
+          <t>الرصيد الحالي (الافتتاحي)</t>
+        </is>
+      </c>
+      <c r="R4" s="12" t="inlineStr">
+        <is>
+          <t>نوع الفاز (single/three)</t>
+        </is>
+      </c>
+      <c r="S4" s="12" t="inlineStr">
+        <is>
+          <t>محول خاص? (نعم/لا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>احمد محمد علي</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>775123456</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>1234567890</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>N001</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t>CAT1</t>
+        </is>
+      </c>
+      <c r="K5" s="13" t="inlineStr">
+        <is>
+          <t>TYPE1</t>
+        </is>
+      </c>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>CT001</t>
+        </is>
+      </c>
+      <c r="M5" s="13" t="inlineStr">
+        <is>
+          <t>M001001</t>
+        </is>
+      </c>
+      <c r="N5" s="13" t="n">
+        <v>1500</v>
+      </c>
+      <c r="O5" s="13" t="n">
+        <v>1500</v>
+      </c>
+      <c r="P5" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="13" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="S5" s="13" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>فاطمة سالم احمد</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>771987654</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>9876543210</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>C002</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>N002</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>B02</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>A02</t>
+        </is>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t>CAT2</t>
+        </is>
+      </c>
+      <c r="K6" s="14" t="inlineStr">
+        <is>
+          <t>TYPE2</t>
+        </is>
+      </c>
+      <c r="L6" s="14" t="inlineStr">
+        <is>
+          <t>CT002</t>
+        </is>
+      </c>
+      <c r="M6" s="14" t="inlineStr">
+        <is>
+          <t>M001002</t>
+        </is>
+      </c>
+      <c r="N6" s="14" t="n">
+        <v>2300</v>
+      </c>
+      <c r="O6" s="14" t="n">
+        <v>2300</v>
+      </c>
+      <c r="P6" s="14" t="inlineStr">
+        <is>
+          <t>50.5</t>
+        </is>
+      </c>
+      <c r="Q6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="14" t="inlineStr">
+        <is>
+          <t>three</t>
+        </is>
+      </c>
+      <c r="S6" s="14" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>شركة النور التجارية</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>733555888</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr"/>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>C003</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>N003</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>A03</t>
+        </is>
+      </c>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t>CAT3</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>TYPE3</t>
+        </is>
+      </c>
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t>CT003</t>
+        </is>
+      </c>
+      <c r="M7" s="13" t="inlineStr">
+        <is>
+          <t>M001003</t>
+        </is>
+      </c>
+      <c r="N7" s="13" t="n">
+        <v>8750</v>
+      </c>
+      <c r="O7" s="13" t="n">
+        <v>8750</v>
+      </c>
+      <c r="P7" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" s="13" t="n">
+        <v>1200</v>
+      </c>
+      <c r="R7" s="13" t="inlineStr">
+        <is>
+          <t>three</t>
+        </is>
+      </c>
+      <c r="S7" s="13" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>خالد عبدالله قاسم</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>776321654</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>1122334455</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>C004</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>N004</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="inlineStr">
+        <is>
+          <t>CAT1</t>
+        </is>
+      </c>
+      <c r="K8" s="14" t="inlineStr">
+        <is>
+          <t>TYPE1</t>
+        </is>
+      </c>
+      <c r="L8" s="14" t="inlineStr">
+        <is>
+          <t>CT001</t>
+        </is>
+      </c>
+      <c r="M8" s="14" t="inlineStr"/>
+      <c r="N8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="14" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="S8" s="14" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>مريم حسن ابراهيم</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>774654321</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>5566778899</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>C005</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>N005</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>E05</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>R03</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>CAT1</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>TYPE2</t>
+        </is>
+      </c>
+      <c r="L9" s="13" t="inlineStr">
+        <is>
+          <t>CT001</t>
+        </is>
+      </c>
+      <c r="M9" s="13" t="inlineStr">
+        <is>
+          <t>M001005</t>
+        </is>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>640</v>
+      </c>
+      <c r="O9" s="13" t="n">
+        <v>640</v>
+      </c>
+      <c r="P9" s="13" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="Q9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="13" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="S9" s="13" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:S9"/>
+  <mergeCells count="6">
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A2:S2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>قواعد ملء النموذج</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="16" t="inlineStr"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>1. الحقول المشار اليها بعلامة (*) الزامية ولا يمكن تركها فارغة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>2. حقل هل فعال يقبل القيمتين: نعم او لا.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>3. حقل نوع الفاز يقبل: single (احادي الطور) او three (ثلاثي الطور).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>4. حقل محول خاص يقبل: نعم او لا.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>5. ارقام الموبايل يجب ان تكون 9 ارقام بدون مسافات او رموز.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>6. رموز المنطقة والفرع والفئة ونوع المشترك وقالب العقد تاتي من جدول الترميز في النظام.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>7. للعملاء غير الفعالين (هل فعال = لا) لا يلزم تعبئة بيانات العداد والقراءات.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>8. قيم الارصدة الرقمية يجب ان لا تحتوي على رموز عملة (ادخل الارقام فقط).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="16" t="inlineStr"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>دليل الاعمدة</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>العمود</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>اسم الحقل</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>الوصف</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>الاسم</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>الزامي - الاسم الكامل للمشترك</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>الموبايل</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>الزامي - 9 ارقام بدون كود الدولة</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>الرقم الوطني</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>اختياري</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>رقم المشترك</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>الزامي - رقم فريد في النظام القديم</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>الرقم الجديد</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>اختياري</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>رقم الحرف</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>اختياري</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>هل فعال؟</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>الزامي - نعم / لا</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>رمز المنطقة</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>اختياري - من جدول الترميز</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>رمز الفرع</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>اختياري - من جدول الترميز</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>رمز الفئة</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>اختياري - من جدول الترميز</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>رمز نوع المشترك</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>اختياري - من جدول الترميز</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>رمز قالب العقد</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>الزامي للفعالين - من جدول الترميز</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>رقم العداد</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>قراءة العداد في النظام</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>قراءة الافتتاح</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>اخر قراءة مسجلة</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>الرصيد السابق (الخط الساخن)</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>الرصيد الحالي (الافتتاحي)</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>نوع الفاز (single/three)</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>محول خاص (نعم/لا)</t>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>الزامي للفعالين</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>قراءة العداد في النظام القديم</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>اختياري - رقم صحيح من النظام القديم</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>القراءة عند تفعيل العقد</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>الزامي للفعالين - القراءة الاولى عند تفعيل العقد</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>الرصيد السابق</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>اختياري - قد يكون نصا</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>الرصيد الحالي</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>اختياري - رقم عشري</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>نوع الفاز</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>اختياري - single او three</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>محول خاص؟</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>اختياري - نعم او لا</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/utility_core/static/src/Migration_Template.xlsx
+++ b/utility_core/static/src/Migration_Template.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تعليمات الاستيراد" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'بيانات التهيئة'!$A$4:$U$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'بيانات التهيئة'!$A$4:$T$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -194,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -278,6 +278,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -643,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U1004"/>
+  <dimension ref="A1:T1004"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -666,7 +672,7 @@
     <col width="29" customWidth="1" min="18" max="18"/>
     <col width="23" customWidth="1" min="19" max="19"/>
     <col width="23" customWidth="1" min="20" max="20"/>
-    <col width="21" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1">
@@ -711,109 +717,104 @@
       </c>
     </row>
     <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>الاسم *</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
-          <t>الموبايل *</t>
+          <t>الموبايل</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t>الرقم الوطني</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="D4" s="31" t="inlineStr">
         <is>
           <t>رقم المشترك *</t>
         </is>
       </c>
-      <c r="E4" s="24" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t>الرقم الجديد</t>
         </is>
       </c>
-      <c r="F4" s="24" t="inlineStr">
+      <c r="F4" s="31" t="inlineStr">
         <is>
           <t>رقم الحرف</t>
         </is>
       </c>
-      <c r="G4" s="24" t="inlineStr">
+      <c r="G4" s="31" t="inlineStr">
         <is>
           <t>هل فعال؟ *</t>
         </is>
       </c>
-      <c r="H4" s="24" t="inlineStr">
+      <c r="H4" s="31" t="inlineStr">
         <is>
           <t>رمز المنطقة</t>
         </is>
       </c>
-      <c r="I4" s="24" t="inlineStr">
+      <c r="I4" s="31" t="inlineStr">
         <is>
           <t>رمز الفرع</t>
         </is>
       </c>
-      <c r="J4" s="24" t="inlineStr">
+      <c r="J4" s="31" t="inlineStr">
         <is>
           <t>رمز الفئة</t>
         </is>
       </c>
-      <c r="K4" s="24" t="inlineStr">
+      <c r="K4" s="31" t="inlineStr">
         <is>
           <t>رمز نوع المشترك</t>
         </is>
       </c>
-      <c r="L4" s="24" t="inlineStr">
+      <c r="L4" s="31" t="inlineStr">
         <is>
           <t>رمز قالب العقد *</t>
         </is>
       </c>
-      <c r="M4" s="23" t="inlineStr">
+      <c r="M4" s="31" t="inlineStr">
         <is>
           <t>رقم العداد *</t>
         </is>
       </c>
-      <c r="N4" s="24" t="inlineStr">
+      <c r="N4" s="31" t="inlineStr">
         <is>
           <t>قراءة العداد في النظام القديم</t>
         </is>
       </c>
-      <c r="O4" s="24" t="inlineStr">
+      <c r="O4" s="31" t="inlineStr">
         <is>
           <t>القراءة عند تفعيل العقد</t>
         </is>
       </c>
-      <c r="P4" s="24" t="inlineStr">
+      <c r="P4" s="31" t="inlineStr">
         <is>
           <t>الرصيد السابق (الخط الساخن)</t>
         </is>
       </c>
-      <c r="Q4" s="24" t="inlineStr">
+      <c r="Q4" s="31" t="inlineStr">
         <is>
           <t>الرصيد الحالي (الافتتاحي)</t>
         </is>
       </c>
-      <c r="R4" s="24" t="inlineStr">
+      <c r="R4" s="31" t="inlineStr">
         <is>
           <t>نوع الفاز (single/three)</t>
         </is>
       </c>
-      <c r="S4" s="24" t="inlineStr">
+      <c r="S4" s="31" t="inlineStr">
         <is>
           <t>محول خاص? (نعم/لا)</t>
         </is>
       </c>
-      <c r="T4" s="25" t="inlineStr">
+      <c r="T4" s="32" t="inlineStr">
         <is>
           <t>مرجع المالك القديم</t>
-        </is>
-      </c>
-      <c r="U4" s="25" t="inlineStr">
-        <is>
-          <t>رمز موديل العداد</t>
         </is>
       </c>
     </row>
@@ -833,7 +834,6 @@
       <c r="O5" s="27" t="n"/>
       <c r="Q5" s="27" t="n"/>
       <c r="T5" s="26" t="n"/>
-      <c r="U5" s="26" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="B6" s="26" t="n"/>
@@ -851,7 +851,6 @@
       <c r="O6" s="27" t="n"/>
       <c r="Q6" s="27" t="n"/>
       <c r="T6" s="26" t="n"/>
-      <c r="U6" s="26" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="B7" s="26" t="n"/>
@@ -869,7 +868,6 @@
       <c r="O7" s="27" t="n"/>
       <c r="Q7" s="27" t="n"/>
       <c r="T7" s="26" t="n"/>
-      <c r="U7" s="26" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="B8" s="26" t="n"/>
@@ -887,7 +885,6 @@
       <c r="O8" s="27" t="n"/>
       <c r="Q8" s="27" t="n"/>
       <c r="T8" s="26" t="n"/>
-      <c r="U8" s="26" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="B9" s="26" t="n"/>
@@ -905,7 +902,6 @@
       <c r="O9" s="27" t="n"/>
       <c r="Q9" s="27" t="n"/>
       <c r="T9" s="26" t="n"/>
-      <c r="U9" s="26" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="26" t="n"/>
@@ -923,7 +919,6 @@
       <c r="O10" s="27" t="n"/>
       <c r="Q10" s="27" t="n"/>
       <c r="T10" s="26" t="n"/>
-      <c r="U10" s="26" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="26" t="n"/>
@@ -941,7 +936,6 @@
       <c r="O11" s="27" t="n"/>
       <c r="Q11" s="27" t="n"/>
       <c r="T11" s="26" t="n"/>
-      <c r="U11" s="26" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="26" t="n"/>
@@ -959,7 +953,6 @@
       <c r="O12" s="27" t="n"/>
       <c r="Q12" s="27" t="n"/>
       <c r="T12" s="26" t="n"/>
-      <c r="U12" s="26" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="26" t="n"/>
@@ -977,7 +970,6 @@
       <c r="O13" s="27" t="n"/>
       <c r="Q13" s="27" t="n"/>
       <c r="T13" s="26" t="n"/>
-      <c r="U13" s="26" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="26" t="n"/>
@@ -995,7 +987,6 @@
       <c r="O14" s="27" t="n"/>
       <c r="Q14" s="27" t="n"/>
       <c r="T14" s="26" t="n"/>
-      <c r="U14" s="26" t="n"/>
     </row>
     <row r="15">
       <c r="B15" s="26" t="n"/>
@@ -1013,7 +1004,6 @@
       <c r="O15" s="27" t="n"/>
       <c r="Q15" s="27" t="n"/>
       <c r="T15" s="26" t="n"/>
-      <c r="U15" s="26" t="n"/>
     </row>
     <row r="16">
       <c r="B16" s="26" t="n"/>
@@ -1031,7 +1021,6 @@
       <c r="O16" s="27" t="n"/>
       <c r="Q16" s="27" t="n"/>
       <c r="T16" s="26" t="n"/>
-      <c r="U16" s="26" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="26" t="n"/>
@@ -1049,7 +1038,6 @@
       <c r="O17" s="27" t="n"/>
       <c r="Q17" s="27" t="n"/>
       <c r="T17" s="26" t="n"/>
-      <c r="U17" s="26" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="26" t="n"/>
@@ -1067,7 +1055,6 @@
       <c r="O18" s="27" t="n"/>
       <c r="Q18" s="27" t="n"/>
       <c r="T18" s="26" t="n"/>
-      <c r="U18" s="26" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="26" t="n"/>
@@ -1085,7 +1072,6 @@
       <c r="O19" s="27" t="n"/>
       <c r="Q19" s="27" t="n"/>
       <c r="T19" s="26" t="n"/>
-      <c r="U19" s="26" t="n"/>
     </row>
     <row r="20">
       <c r="B20" s="26" t="n"/>
@@ -1103,7 +1089,6 @@
       <c r="O20" s="27" t="n"/>
       <c r="Q20" s="27" t="n"/>
       <c r="T20" s="26" t="n"/>
-      <c r="U20" s="26" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="26" t="n"/>
@@ -1121,7 +1106,6 @@
       <c r="O21" s="27" t="n"/>
       <c r="Q21" s="27" t="n"/>
       <c r="T21" s="26" t="n"/>
-      <c r="U21" s="26" t="n"/>
     </row>
     <row r="22">
       <c r="B22" s="26" t="n"/>
@@ -1139,7 +1123,6 @@
       <c r="O22" s="27" t="n"/>
       <c r="Q22" s="27" t="n"/>
       <c r="T22" s="26" t="n"/>
-      <c r="U22" s="26" t="n"/>
     </row>
     <row r="23">
       <c r="B23" s="26" t="n"/>
@@ -1157,7 +1140,6 @@
       <c r="O23" s="27" t="n"/>
       <c r="Q23" s="27" t="n"/>
       <c r="T23" s="26" t="n"/>
-      <c r="U23" s="26" t="n"/>
     </row>
     <row r="24">
       <c r="B24" s="26" t="n"/>
@@ -1175,7 +1157,6 @@
       <c r="O24" s="27" t="n"/>
       <c r="Q24" s="27" t="n"/>
       <c r="T24" s="26" t="n"/>
-      <c r="U24" s="26" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="26" t="n"/>
@@ -1193,7 +1174,6 @@
       <c r="O25" s="27" t="n"/>
       <c r="Q25" s="27" t="n"/>
       <c r="T25" s="26" t="n"/>
-      <c r="U25" s="26" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="26" t="n"/>
@@ -1211,7 +1191,6 @@
       <c r="O26" s="27" t="n"/>
       <c r="Q26" s="27" t="n"/>
       <c r="T26" s="26" t="n"/>
-      <c r="U26" s="26" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="26" t="n"/>
@@ -1229,7 +1208,6 @@
       <c r="O27" s="27" t="n"/>
       <c r="Q27" s="27" t="n"/>
       <c r="T27" s="26" t="n"/>
-      <c r="U27" s="26" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="26" t="n"/>
@@ -1247,7 +1225,6 @@
       <c r="O28" s="27" t="n"/>
       <c r="Q28" s="27" t="n"/>
       <c r="T28" s="26" t="n"/>
-      <c r="U28" s="26" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="26" t="n"/>
@@ -1265,7 +1242,6 @@
       <c r="O29" s="27" t="n"/>
       <c r="Q29" s="27" t="n"/>
       <c r="T29" s="26" t="n"/>
-      <c r="U29" s="26" t="n"/>
     </row>
     <row r="30">
       <c r="B30" s="26" t="n"/>
@@ -1283,7 +1259,6 @@
       <c r="O30" s="27" t="n"/>
       <c r="Q30" s="27" t="n"/>
       <c r="T30" s="26" t="n"/>
-      <c r="U30" s="26" t="n"/>
     </row>
     <row r="31">
       <c r="B31" s="26" t="n"/>
@@ -1301,7 +1276,6 @@
       <c r="O31" s="27" t="n"/>
       <c r="Q31" s="27" t="n"/>
       <c r="T31" s="26" t="n"/>
-      <c r="U31" s="26" t="n"/>
     </row>
     <row r="32">
       <c r="B32" s="26" t="n"/>
@@ -1319,7 +1293,6 @@
       <c r="O32" s="27" t="n"/>
       <c r="Q32" s="27" t="n"/>
       <c r="T32" s="26" t="n"/>
-      <c r="U32" s="26" t="n"/>
     </row>
     <row r="33">
       <c r="B33" s="26" t="n"/>
@@ -1337,7 +1310,6 @@
       <c r="O33" s="27" t="n"/>
       <c r="Q33" s="27" t="n"/>
       <c r="T33" s="26" t="n"/>
-      <c r="U33" s="26" t="n"/>
     </row>
     <row r="34">
       <c r="B34" s="26" t="n"/>
@@ -1355,7 +1327,6 @@
       <c r="O34" s="27" t="n"/>
       <c r="Q34" s="27" t="n"/>
       <c r="T34" s="26" t="n"/>
-      <c r="U34" s="26" t="n"/>
     </row>
     <row r="35">
       <c r="B35" s="26" t="n"/>
@@ -1373,7 +1344,6 @@
       <c r="O35" s="27" t="n"/>
       <c r="Q35" s="27" t="n"/>
       <c r="T35" s="26" t="n"/>
-      <c r="U35" s="26" t="n"/>
     </row>
     <row r="36">
       <c r="B36" s="26" t="n"/>
@@ -1391,7 +1361,6 @@
       <c r="O36" s="27" t="n"/>
       <c r="Q36" s="27" t="n"/>
       <c r="T36" s="26" t="n"/>
-      <c r="U36" s="26" t="n"/>
     </row>
     <row r="37">
       <c r="B37" s="26" t="n"/>
@@ -1409,7 +1378,6 @@
       <c r="O37" s="27" t="n"/>
       <c r="Q37" s="27" t="n"/>
       <c r="T37" s="26" t="n"/>
-      <c r="U37" s="26" t="n"/>
     </row>
     <row r="38">
       <c r="B38" s="26" t="n"/>
@@ -1427,7 +1395,6 @@
       <c r="O38" s="27" t="n"/>
       <c r="Q38" s="27" t="n"/>
       <c r="T38" s="26" t="n"/>
-      <c r="U38" s="26" t="n"/>
     </row>
     <row r="39">
       <c r="B39" s="26" t="n"/>
@@ -1445,7 +1412,6 @@
       <c r="O39" s="27" t="n"/>
       <c r="Q39" s="27" t="n"/>
       <c r="T39" s="26" t="n"/>
-      <c r="U39" s="26" t="n"/>
     </row>
     <row r="40">
       <c r="B40" s="26" t="n"/>
@@ -1463,7 +1429,6 @@
       <c r="O40" s="27" t="n"/>
       <c r="Q40" s="27" t="n"/>
       <c r="T40" s="26" t="n"/>
-      <c r="U40" s="26" t="n"/>
     </row>
     <row r="41">
       <c r="B41" s="26" t="n"/>
@@ -1481,7 +1446,6 @@
       <c r="O41" s="27" t="n"/>
       <c r="Q41" s="27" t="n"/>
       <c r="T41" s="26" t="n"/>
-      <c r="U41" s="26" t="n"/>
     </row>
     <row r="42">
       <c r="B42" s="26" t="n"/>
@@ -1499,7 +1463,6 @@
       <c r="O42" s="27" t="n"/>
       <c r="Q42" s="27" t="n"/>
       <c r="T42" s="26" t="n"/>
-      <c r="U42" s="26" t="n"/>
     </row>
     <row r="43">
       <c r="B43" s="26" t="n"/>
@@ -1517,7 +1480,6 @@
       <c r="O43" s="27" t="n"/>
       <c r="Q43" s="27" t="n"/>
       <c r="T43" s="26" t="n"/>
-      <c r="U43" s="26" t="n"/>
     </row>
     <row r="44">
       <c r="B44" s="26" t="n"/>
@@ -1535,7 +1497,6 @@
       <c r="O44" s="27" t="n"/>
       <c r="Q44" s="27" t="n"/>
       <c r="T44" s="26" t="n"/>
-      <c r="U44" s="26" t="n"/>
     </row>
     <row r="45">
       <c r="B45" s="26" t="n"/>
@@ -1553,7 +1514,6 @@
       <c r="O45" s="27" t="n"/>
       <c r="Q45" s="27" t="n"/>
       <c r="T45" s="26" t="n"/>
-      <c r="U45" s="26" t="n"/>
     </row>
     <row r="46">
       <c r="B46" s="26" t="n"/>
@@ -1571,7 +1531,6 @@
       <c r="O46" s="27" t="n"/>
       <c r="Q46" s="27" t="n"/>
       <c r="T46" s="26" t="n"/>
-      <c r="U46" s="26" t="n"/>
     </row>
     <row r="47">
       <c r="B47" s="26" t="n"/>
@@ -1589,7 +1548,6 @@
       <c r="O47" s="27" t="n"/>
       <c r="Q47" s="27" t="n"/>
       <c r="T47" s="26" t="n"/>
-      <c r="U47" s="26" t="n"/>
     </row>
     <row r="48">
       <c r="B48" s="26" t="n"/>
@@ -1607,7 +1565,6 @@
       <c r="O48" s="27" t="n"/>
       <c r="Q48" s="27" t="n"/>
       <c r="T48" s="26" t="n"/>
-      <c r="U48" s="26" t="n"/>
     </row>
     <row r="49">
       <c r="B49" s="26" t="n"/>
@@ -1625,7 +1582,6 @@
       <c r="O49" s="27" t="n"/>
       <c r="Q49" s="27" t="n"/>
       <c r="T49" s="26" t="n"/>
-      <c r="U49" s="26" t="n"/>
     </row>
     <row r="50">
       <c r="B50" s="26" t="n"/>
@@ -1643,7 +1599,6 @@
       <c r="O50" s="27" t="n"/>
       <c r="Q50" s="27" t="n"/>
       <c r="T50" s="26" t="n"/>
-      <c r="U50" s="26" t="n"/>
     </row>
     <row r="51">
       <c r="B51" s="26" t="n"/>
@@ -1661,7 +1616,6 @@
       <c r="O51" s="27" t="n"/>
       <c r="Q51" s="27" t="n"/>
       <c r="T51" s="26" t="n"/>
-      <c r="U51" s="26" t="n"/>
     </row>
     <row r="52">
       <c r="B52" s="26" t="n"/>
@@ -1679,7 +1633,6 @@
       <c r="O52" s="27" t="n"/>
       <c r="Q52" s="27" t="n"/>
       <c r="T52" s="26" t="n"/>
-      <c r="U52" s="26" t="n"/>
     </row>
     <row r="53">
       <c r="B53" s="26" t="n"/>
@@ -1697,7 +1650,6 @@
       <c r="O53" s="27" t="n"/>
       <c r="Q53" s="27" t="n"/>
       <c r="T53" s="26" t="n"/>
-      <c r="U53" s="26" t="n"/>
     </row>
     <row r="54">
       <c r="B54" s="26" t="n"/>
@@ -1715,7 +1667,6 @@
       <c r="O54" s="27" t="n"/>
       <c r="Q54" s="27" t="n"/>
       <c r="T54" s="26" t="n"/>
-      <c r="U54" s="26" t="n"/>
     </row>
     <row r="55">
       <c r="B55" s="26" t="n"/>
@@ -1733,7 +1684,6 @@
       <c r="O55" s="27" t="n"/>
       <c r="Q55" s="27" t="n"/>
       <c r="T55" s="26" t="n"/>
-      <c r="U55" s="26" t="n"/>
     </row>
     <row r="56">
       <c r="B56" s="26" t="n"/>
@@ -1751,7 +1701,6 @@
       <c r="O56" s="27" t="n"/>
       <c r="Q56" s="27" t="n"/>
       <c r="T56" s="26" t="n"/>
-      <c r="U56" s="26" t="n"/>
     </row>
     <row r="57">
       <c r="B57" s="26" t="n"/>
@@ -1769,7 +1718,6 @@
       <c r="O57" s="27" t="n"/>
       <c r="Q57" s="27" t="n"/>
       <c r="T57" s="26" t="n"/>
-      <c r="U57" s="26" t="n"/>
     </row>
     <row r="58">
       <c r="B58" s="26" t="n"/>
@@ -1787,7 +1735,6 @@
       <c r="O58" s="27" t="n"/>
       <c r="Q58" s="27" t="n"/>
       <c r="T58" s="26" t="n"/>
-      <c r="U58" s="26" t="n"/>
     </row>
     <row r="59">
       <c r="B59" s="26" t="n"/>
@@ -1805,7 +1752,6 @@
       <c r="O59" s="27" t="n"/>
       <c r="Q59" s="27" t="n"/>
       <c r="T59" s="26" t="n"/>
-      <c r="U59" s="26" t="n"/>
     </row>
     <row r="60">
       <c r="B60" s="26" t="n"/>
@@ -1823,7 +1769,6 @@
       <c r="O60" s="27" t="n"/>
       <c r="Q60" s="27" t="n"/>
       <c r="T60" s="26" t="n"/>
-      <c r="U60" s="26" t="n"/>
     </row>
     <row r="61">
       <c r="B61" s="26" t="n"/>
@@ -1841,7 +1786,6 @@
       <c r="O61" s="27" t="n"/>
       <c r="Q61" s="27" t="n"/>
       <c r="T61" s="26" t="n"/>
-      <c r="U61" s="26" t="n"/>
     </row>
     <row r="62">
       <c r="B62" s="26" t="n"/>
@@ -1859,7 +1803,6 @@
       <c r="O62" s="27" t="n"/>
       <c r="Q62" s="27" t="n"/>
       <c r="T62" s="26" t="n"/>
-      <c r="U62" s="26" t="n"/>
     </row>
     <row r="63">
       <c r="B63" s="26" t="n"/>
@@ -1877,7 +1820,6 @@
       <c r="O63" s="27" t="n"/>
       <c r="Q63" s="27" t="n"/>
       <c r="T63" s="26" t="n"/>
-      <c r="U63" s="26" t="n"/>
     </row>
     <row r="64">
       <c r="B64" s="26" t="n"/>
@@ -1895,7 +1837,6 @@
       <c r="O64" s="27" t="n"/>
       <c r="Q64" s="27" t="n"/>
       <c r="T64" s="26" t="n"/>
-      <c r="U64" s="26" t="n"/>
     </row>
     <row r="65">
       <c r="B65" s="26" t="n"/>
@@ -1913,7 +1854,6 @@
       <c r="O65" s="27" t="n"/>
       <c r="Q65" s="27" t="n"/>
       <c r="T65" s="26" t="n"/>
-      <c r="U65" s="26" t="n"/>
     </row>
     <row r="66">
       <c r="B66" s="26" t="n"/>
@@ -1931,7 +1871,6 @@
       <c r="O66" s="27" t="n"/>
       <c r="Q66" s="27" t="n"/>
       <c r="T66" s="26" t="n"/>
-      <c r="U66" s="26" t="n"/>
     </row>
     <row r="67">
       <c r="B67" s="26" t="n"/>
@@ -1949,7 +1888,6 @@
       <c r="O67" s="27" t="n"/>
       <c r="Q67" s="27" t="n"/>
       <c r="T67" s="26" t="n"/>
-      <c r="U67" s="26" t="n"/>
     </row>
     <row r="68">
       <c r="B68" s="26" t="n"/>
@@ -1967,7 +1905,6 @@
       <c r="O68" s="27" t="n"/>
       <c r="Q68" s="27" t="n"/>
       <c r="T68" s="26" t="n"/>
-      <c r="U68" s="26" t="n"/>
     </row>
     <row r="69">
       <c r="B69" s="26" t="n"/>
@@ -1985,7 +1922,6 @@
       <c r="O69" s="27" t="n"/>
       <c r="Q69" s="27" t="n"/>
       <c r="T69" s="26" t="n"/>
-      <c r="U69" s="26" t="n"/>
     </row>
     <row r="70">
       <c r="B70" s="26" t="n"/>
@@ -2003,7 +1939,6 @@
       <c r="O70" s="27" t="n"/>
       <c r="Q70" s="27" t="n"/>
       <c r="T70" s="26" t="n"/>
-      <c r="U70" s="26" t="n"/>
     </row>
     <row r="71">
       <c r="B71" s="26" t="n"/>
@@ -2021,7 +1956,6 @@
       <c r="O71" s="27" t="n"/>
       <c r="Q71" s="27" t="n"/>
       <c r="T71" s="26" t="n"/>
-      <c r="U71" s="26" t="n"/>
     </row>
     <row r="72">
       <c r="B72" s="26" t="n"/>
@@ -2039,7 +1973,6 @@
       <c r="O72" s="27" t="n"/>
       <c r="Q72" s="27" t="n"/>
       <c r="T72" s="26" t="n"/>
-      <c r="U72" s="26" t="n"/>
     </row>
     <row r="73">
       <c r="B73" s="26" t="n"/>
@@ -2057,7 +1990,6 @@
       <c r="O73" s="27" t="n"/>
       <c r="Q73" s="27" t="n"/>
       <c r="T73" s="26" t="n"/>
-      <c r="U73" s="26" t="n"/>
     </row>
     <row r="74">
       <c r="B74" s="26" t="n"/>
@@ -2075,7 +2007,6 @@
       <c r="O74" s="27" t="n"/>
       <c r="Q74" s="27" t="n"/>
       <c r="T74" s="26" t="n"/>
-      <c r="U74" s="26" t="n"/>
     </row>
     <row r="75">
       <c r="B75" s="26" t="n"/>
@@ -2093,7 +2024,6 @@
       <c r="O75" s="27" t="n"/>
       <c r="Q75" s="27" t="n"/>
       <c r="T75" s="26" t="n"/>
-      <c r="U75" s="26" t="n"/>
     </row>
     <row r="76">
       <c r="B76" s="26" t="n"/>
@@ -2111,7 +2041,6 @@
       <c r="O76" s="27" t="n"/>
       <c r="Q76" s="27" t="n"/>
       <c r="T76" s="26" t="n"/>
-      <c r="U76" s="26" t="n"/>
     </row>
     <row r="77">
       <c r="B77" s="26" t="n"/>
@@ -2129,7 +2058,6 @@
       <c r="O77" s="27" t="n"/>
       <c r="Q77" s="27" t="n"/>
       <c r="T77" s="26" t="n"/>
-      <c r="U77" s="26" t="n"/>
     </row>
     <row r="78">
       <c r="B78" s="26" t="n"/>
@@ -2147,7 +2075,6 @@
       <c r="O78" s="27" t="n"/>
       <c r="Q78" s="27" t="n"/>
       <c r="T78" s="26" t="n"/>
-      <c r="U78" s="26" t="n"/>
     </row>
     <row r="79">
       <c r="B79" s="26" t="n"/>
@@ -2165,7 +2092,6 @@
       <c r="O79" s="27" t="n"/>
       <c r="Q79" s="27" t="n"/>
       <c r="T79" s="26" t="n"/>
-      <c r="U79" s="26" t="n"/>
     </row>
     <row r="80">
       <c r="B80" s="26" t="n"/>
@@ -2183,7 +2109,6 @@
       <c r="O80" s="27" t="n"/>
       <c r="Q80" s="27" t="n"/>
       <c r="T80" s="26" t="n"/>
-      <c r="U80" s="26" t="n"/>
     </row>
     <row r="81">
       <c r="B81" s="26" t="n"/>
@@ -2201,7 +2126,6 @@
       <c r="O81" s="27" t="n"/>
       <c r="Q81" s="27" t="n"/>
       <c r="T81" s="26" t="n"/>
-      <c r="U81" s="26" t="n"/>
     </row>
     <row r="82">
       <c r="B82" s="26" t="n"/>
@@ -2219,7 +2143,6 @@
       <c r="O82" s="27" t="n"/>
       <c r="Q82" s="27" t="n"/>
       <c r="T82" s="26" t="n"/>
-      <c r="U82" s="26" t="n"/>
     </row>
     <row r="83">
       <c r="B83" s="26" t="n"/>
@@ -2237,7 +2160,6 @@
       <c r="O83" s="27" t="n"/>
       <c r="Q83" s="27" t="n"/>
       <c r="T83" s="26" t="n"/>
-      <c r="U83" s="26" t="n"/>
     </row>
     <row r="84">
       <c r="B84" s="26" t="n"/>
@@ -2255,7 +2177,6 @@
       <c r="O84" s="27" t="n"/>
       <c r="Q84" s="27" t="n"/>
       <c r="T84" s="26" t="n"/>
-      <c r="U84" s="26" t="n"/>
     </row>
     <row r="85">
       <c r="B85" s="26" t="n"/>
@@ -2273,7 +2194,6 @@
       <c r="O85" s="27" t="n"/>
       <c r="Q85" s="27" t="n"/>
       <c r="T85" s="26" t="n"/>
-      <c r="U85" s="26" t="n"/>
     </row>
     <row r="86">
       <c r="B86" s="26" t="n"/>
@@ -2291,7 +2211,6 @@
       <c r="O86" s="27" t="n"/>
       <c r="Q86" s="27" t="n"/>
       <c r="T86" s="26" t="n"/>
-      <c r="U86" s="26" t="n"/>
     </row>
     <row r="87">
       <c r="B87" s="26" t="n"/>
@@ -2309,7 +2228,6 @@
       <c r="O87" s="27" t="n"/>
       <c r="Q87" s="27" t="n"/>
       <c r="T87" s="26" t="n"/>
-      <c r="U87" s="26" t="n"/>
     </row>
     <row r="88">
       <c r="B88" s="26" t="n"/>
@@ -2327,7 +2245,6 @@
       <c r="O88" s="27" t="n"/>
       <c r="Q88" s="27" t="n"/>
       <c r="T88" s="26" t="n"/>
-      <c r="U88" s="26" t="n"/>
     </row>
     <row r="89">
       <c r="B89" s="26" t="n"/>
@@ -2345,7 +2262,6 @@
       <c r="O89" s="27" t="n"/>
       <c r="Q89" s="27" t="n"/>
       <c r="T89" s="26" t="n"/>
-      <c r="U89" s="26" t="n"/>
     </row>
     <row r="90">
       <c r="B90" s="26" t="n"/>
@@ -2363,7 +2279,6 @@
       <c r="O90" s="27" t="n"/>
       <c r="Q90" s="27" t="n"/>
       <c r="T90" s="26" t="n"/>
-      <c r="U90" s="26" t="n"/>
     </row>
     <row r="91">
       <c r="B91" s="26" t="n"/>
@@ -2381,7 +2296,6 @@
       <c r="O91" s="27" t="n"/>
       <c r="Q91" s="27" t="n"/>
       <c r="T91" s="26" t="n"/>
-      <c r="U91" s="26" t="n"/>
     </row>
     <row r="92">
       <c r="B92" s="26" t="n"/>
@@ -2399,7 +2313,6 @@
       <c r="O92" s="27" t="n"/>
       <c r="Q92" s="27" t="n"/>
       <c r="T92" s="26" t="n"/>
-      <c r="U92" s="26" t="n"/>
     </row>
     <row r="93">
       <c r="B93" s="26" t="n"/>
@@ -2417,7 +2330,6 @@
       <c r="O93" s="27" t="n"/>
       <c r="Q93" s="27" t="n"/>
       <c r="T93" s="26" t="n"/>
-      <c r="U93" s="26" t="n"/>
     </row>
     <row r="94">
       <c r="B94" s="26" t="n"/>
@@ -2435,7 +2347,6 @@
       <c r="O94" s="27" t="n"/>
       <c r="Q94" s="27" t="n"/>
       <c r="T94" s="26" t="n"/>
-      <c r="U94" s="26" t="n"/>
     </row>
     <row r="95">
       <c r="B95" s="26" t="n"/>
@@ -2453,7 +2364,6 @@
       <c r="O95" s="27" t="n"/>
       <c r="Q95" s="27" t="n"/>
       <c r="T95" s="26" t="n"/>
-      <c r="U95" s="26" t="n"/>
     </row>
     <row r="96">
       <c r="B96" s="26" t="n"/>
@@ -2471,7 +2381,6 @@
       <c r="O96" s="27" t="n"/>
       <c r="Q96" s="27" t="n"/>
       <c r="T96" s="26" t="n"/>
-      <c r="U96" s="26" t="n"/>
     </row>
     <row r="97">
       <c r="B97" s="26" t="n"/>
@@ -2489,7 +2398,6 @@
       <c r="O97" s="27" t="n"/>
       <c r="Q97" s="27" t="n"/>
       <c r="T97" s="26" t="n"/>
-      <c r="U97" s="26" t="n"/>
     </row>
     <row r="98">
       <c r="B98" s="26" t="n"/>
@@ -2507,7 +2415,6 @@
       <c r="O98" s="27" t="n"/>
       <c r="Q98" s="27" t="n"/>
       <c r="T98" s="26" t="n"/>
-      <c r="U98" s="26" t="n"/>
     </row>
     <row r="99">
       <c r="B99" s="26" t="n"/>
@@ -2525,7 +2432,6 @@
       <c r="O99" s="27" t="n"/>
       <c r="Q99" s="27" t="n"/>
       <c r="T99" s="26" t="n"/>
-      <c r="U99" s="26" t="n"/>
     </row>
     <row r="100">
       <c r="B100" s="26" t="n"/>
@@ -2543,7 +2449,6 @@
       <c r="O100" s="27" t="n"/>
       <c r="Q100" s="27" t="n"/>
       <c r="T100" s="26" t="n"/>
-      <c r="U100" s="26" t="n"/>
     </row>
     <row r="101">
       <c r="B101" s="26" t="n"/>
@@ -2561,7 +2466,6 @@
       <c r="O101" s="27" t="n"/>
       <c r="Q101" s="27" t="n"/>
       <c r="T101" s="26" t="n"/>
-      <c r="U101" s="26" t="n"/>
     </row>
     <row r="102">
       <c r="B102" s="26" t="n"/>
@@ -2579,7 +2483,6 @@
       <c r="O102" s="27" t="n"/>
       <c r="Q102" s="27" t="n"/>
       <c r="T102" s="26" t="n"/>
-      <c r="U102" s="26" t="n"/>
     </row>
     <row r="103">
       <c r="B103" s="26" t="n"/>
@@ -2597,7 +2500,6 @@
       <c r="O103" s="27" t="n"/>
       <c r="Q103" s="27" t="n"/>
       <c r="T103" s="26" t="n"/>
-      <c r="U103" s="26" t="n"/>
     </row>
     <row r="104">
       <c r="B104" s="26" t="n"/>
@@ -2615,7 +2517,6 @@
       <c r="O104" s="27" t="n"/>
       <c r="Q104" s="27" t="n"/>
       <c r="T104" s="26" t="n"/>
-      <c r="U104" s="26" t="n"/>
     </row>
     <row r="105">
       <c r="B105" s="26" t="n"/>
@@ -2633,7 +2534,6 @@
       <c r="O105" s="27" t="n"/>
       <c r="Q105" s="27" t="n"/>
       <c r="T105" s="26" t="n"/>
-      <c r="U105" s="26" t="n"/>
     </row>
     <row r="106">
       <c r="B106" s="26" t="n"/>
@@ -2651,7 +2551,6 @@
       <c r="O106" s="27" t="n"/>
       <c r="Q106" s="27" t="n"/>
       <c r="T106" s="26" t="n"/>
-      <c r="U106" s="26" t="n"/>
     </row>
     <row r="107">
       <c r="B107" s="26" t="n"/>
@@ -2669,7 +2568,6 @@
       <c r="O107" s="27" t="n"/>
       <c r="Q107" s="27" t="n"/>
       <c r="T107" s="26" t="n"/>
-      <c r="U107" s="26" t="n"/>
     </row>
     <row r="108">
       <c r="B108" s="26" t="n"/>
@@ -2687,7 +2585,6 @@
       <c r="O108" s="27" t="n"/>
       <c r="Q108" s="27" t="n"/>
       <c r="T108" s="26" t="n"/>
-      <c r="U108" s="26" t="n"/>
     </row>
     <row r="109">
       <c r="B109" s="26" t="n"/>
@@ -2705,7 +2602,6 @@
       <c r="O109" s="27" t="n"/>
       <c r="Q109" s="27" t="n"/>
       <c r="T109" s="26" t="n"/>
-      <c r="U109" s="26" t="n"/>
     </row>
     <row r="110">
       <c r="B110" s="26" t="n"/>
@@ -2723,7 +2619,6 @@
       <c r="O110" s="27" t="n"/>
       <c r="Q110" s="27" t="n"/>
       <c r="T110" s="26" t="n"/>
-      <c r="U110" s="26" t="n"/>
     </row>
     <row r="111">
       <c r="B111" s="26" t="n"/>
@@ -2741,7 +2636,6 @@
       <c r="O111" s="27" t="n"/>
       <c r="Q111" s="27" t="n"/>
       <c r="T111" s="26" t="n"/>
-      <c r="U111" s="26" t="n"/>
     </row>
     <row r="112">
       <c r="B112" s="26" t="n"/>
@@ -2759,7 +2653,6 @@
       <c r="O112" s="27" t="n"/>
       <c r="Q112" s="27" t="n"/>
       <c r="T112" s="26" t="n"/>
-      <c r="U112" s="26" t="n"/>
     </row>
     <row r="113">
       <c r="B113" s="26" t="n"/>
@@ -2777,7 +2670,6 @@
       <c r="O113" s="27" t="n"/>
       <c r="Q113" s="27" t="n"/>
       <c r="T113" s="26" t="n"/>
-      <c r="U113" s="26" t="n"/>
     </row>
     <row r="114">
       <c r="B114" s="26" t="n"/>
@@ -2795,7 +2687,6 @@
       <c r="O114" s="27" t="n"/>
       <c r="Q114" s="27" t="n"/>
       <c r="T114" s="26" t="n"/>
-      <c r="U114" s="26" t="n"/>
     </row>
     <row r="115">
       <c r="B115" s="26" t="n"/>
@@ -2813,7 +2704,6 @@
       <c r="O115" s="27" t="n"/>
       <c r="Q115" s="27" t="n"/>
       <c r="T115" s="26" t="n"/>
-      <c r="U115" s="26" t="n"/>
     </row>
     <row r="116">
       <c r="B116" s="26" t="n"/>
@@ -2831,7 +2721,6 @@
       <c r="O116" s="27" t="n"/>
       <c r="Q116" s="27" t="n"/>
       <c r="T116" s="26" t="n"/>
-      <c r="U116" s="26" t="n"/>
     </row>
     <row r="117">
       <c r="B117" s="26" t="n"/>
@@ -2849,7 +2738,6 @@
       <c r="O117" s="27" t="n"/>
       <c r="Q117" s="27" t="n"/>
       <c r="T117" s="26" t="n"/>
-      <c r="U117" s="26" t="n"/>
     </row>
     <row r="118">
       <c r="B118" s="26" t="n"/>
@@ -2867,7 +2755,6 @@
       <c r="O118" s="27" t="n"/>
       <c r="Q118" s="27" t="n"/>
       <c r="T118" s="26" t="n"/>
-      <c r="U118" s="26" t="n"/>
     </row>
     <row r="119">
       <c r="B119" s="26" t="n"/>
@@ -2885,7 +2772,6 @@
       <c r="O119" s="27" t="n"/>
       <c r="Q119" s="27" t="n"/>
       <c r="T119" s="26" t="n"/>
-      <c r="U119" s="26" t="n"/>
     </row>
     <row r="120">
       <c r="B120" s="26" t="n"/>
@@ -2903,7 +2789,6 @@
       <c r="O120" s="27" t="n"/>
       <c r="Q120" s="27" t="n"/>
       <c r="T120" s="26" t="n"/>
-      <c r="U120" s="26" t="n"/>
     </row>
     <row r="121">
       <c r="B121" s="26" t="n"/>
@@ -2921,7 +2806,6 @@
       <c r="O121" s="27" t="n"/>
       <c r="Q121" s="27" t="n"/>
       <c r="T121" s="26" t="n"/>
-      <c r="U121" s="26" t="n"/>
     </row>
     <row r="122">
       <c r="B122" s="26" t="n"/>
@@ -2939,7 +2823,6 @@
       <c r="O122" s="27" t="n"/>
       <c r="Q122" s="27" t="n"/>
       <c r="T122" s="26" t="n"/>
-      <c r="U122" s="26" t="n"/>
     </row>
     <row r="123">
       <c r="B123" s="26" t="n"/>
@@ -2957,7 +2840,6 @@
       <c r="O123" s="27" t="n"/>
       <c r="Q123" s="27" t="n"/>
       <c r="T123" s="26" t="n"/>
-      <c r="U123" s="26" t="n"/>
     </row>
     <row r="124">
       <c r="B124" s="26" t="n"/>
@@ -2975,7 +2857,6 @@
       <c r="O124" s="27" t="n"/>
       <c r="Q124" s="27" t="n"/>
       <c r="T124" s="26" t="n"/>
-      <c r="U124" s="26" t="n"/>
     </row>
     <row r="125">
       <c r="B125" s="26" t="n"/>
@@ -2993,7 +2874,6 @@
       <c r="O125" s="27" t="n"/>
       <c r="Q125" s="27" t="n"/>
       <c r="T125" s="26" t="n"/>
-      <c r="U125" s="26" t="n"/>
     </row>
     <row r="126">
       <c r="B126" s="26" t="n"/>
@@ -3011,7 +2891,6 @@
       <c r="O126" s="27" t="n"/>
       <c r="Q126" s="27" t="n"/>
       <c r="T126" s="26" t="n"/>
-      <c r="U126" s="26" t="n"/>
     </row>
     <row r="127">
       <c r="B127" s="26" t="n"/>
@@ -3029,7 +2908,6 @@
       <c r="O127" s="27" t="n"/>
       <c r="Q127" s="27" t="n"/>
       <c r="T127" s="26" t="n"/>
-      <c r="U127" s="26" t="n"/>
     </row>
     <row r="128">
       <c r="B128" s="26" t="n"/>
@@ -3047,7 +2925,6 @@
       <c r="O128" s="27" t="n"/>
       <c r="Q128" s="27" t="n"/>
       <c r="T128" s="26" t="n"/>
-      <c r="U128" s="26" t="n"/>
     </row>
     <row r="129">
       <c r="B129" s="26" t="n"/>
@@ -3065,7 +2942,6 @@
       <c r="O129" s="27" t="n"/>
       <c r="Q129" s="27" t="n"/>
       <c r="T129" s="26" t="n"/>
-      <c r="U129" s="26" t="n"/>
     </row>
     <row r="130">
       <c r="B130" s="26" t="n"/>
@@ -3083,7 +2959,6 @@
       <c r="O130" s="27" t="n"/>
       <c r="Q130" s="27" t="n"/>
       <c r="T130" s="26" t="n"/>
-      <c r="U130" s="26" t="n"/>
     </row>
     <row r="131">
       <c r="B131" s="26" t="n"/>
@@ -3101,7 +2976,6 @@
       <c r="O131" s="27" t="n"/>
       <c r="Q131" s="27" t="n"/>
       <c r="T131" s="26" t="n"/>
-      <c r="U131" s="26" t="n"/>
     </row>
     <row r="132">
       <c r="B132" s="26" t="n"/>
@@ -3119,7 +2993,6 @@
       <c r="O132" s="27" t="n"/>
       <c r="Q132" s="27" t="n"/>
       <c r="T132" s="26" t="n"/>
-      <c r="U132" s="26" t="n"/>
     </row>
     <row r="133">
       <c r="B133" s="26" t="n"/>
@@ -3137,7 +3010,6 @@
       <c r="O133" s="27" t="n"/>
       <c r="Q133" s="27" t="n"/>
       <c r="T133" s="26" t="n"/>
-      <c r="U133" s="26" t="n"/>
     </row>
     <row r="134">
       <c r="B134" s="26" t="n"/>
@@ -3155,7 +3027,6 @@
       <c r="O134" s="27" t="n"/>
       <c r="Q134" s="27" t="n"/>
       <c r="T134" s="26" t="n"/>
-      <c r="U134" s="26" t="n"/>
     </row>
     <row r="135">
       <c r="B135" s="26" t="n"/>
@@ -3173,7 +3044,6 @@
       <c r="O135" s="27" t="n"/>
       <c r="Q135" s="27" t="n"/>
       <c r="T135" s="26" t="n"/>
-      <c r="U135" s="26" t="n"/>
     </row>
     <row r="136">
       <c r="B136" s="26" t="n"/>
@@ -3191,7 +3061,6 @@
       <c r="O136" s="27" t="n"/>
       <c r="Q136" s="27" t="n"/>
       <c r="T136" s="26" t="n"/>
-      <c r="U136" s="26" t="n"/>
     </row>
     <row r="137">
       <c r="B137" s="26" t="n"/>
@@ -3209,7 +3078,6 @@
       <c r="O137" s="27" t="n"/>
       <c r="Q137" s="27" t="n"/>
       <c r="T137" s="26" t="n"/>
-      <c r="U137" s="26" t="n"/>
     </row>
     <row r="138">
       <c r="B138" s="26" t="n"/>
@@ -3227,7 +3095,6 @@
       <c r="O138" s="27" t="n"/>
       <c r="Q138" s="27" t="n"/>
       <c r="T138" s="26" t="n"/>
-      <c r="U138" s="26" t="n"/>
     </row>
     <row r="139">
       <c r="B139" s="26" t="n"/>
@@ -3245,7 +3112,6 @@
       <c r="O139" s="27" t="n"/>
       <c r="Q139" s="27" t="n"/>
       <c r="T139" s="26" t="n"/>
-      <c r="U139" s="26" t="n"/>
     </row>
     <row r="140">
       <c r="B140" s="26" t="n"/>
@@ -3263,7 +3129,6 @@
       <c r="O140" s="27" t="n"/>
       <c r="Q140" s="27" t="n"/>
       <c r="T140" s="26" t="n"/>
-      <c r="U140" s="26" t="n"/>
     </row>
     <row r="141">
       <c r="B141" s="26" t="n"/>
@@ -3281,7 +3146,6 @@
       <c r="O141" s="27" t="n"/>
       <c r="Q141" s="27" t="n"/>
       <c r="T141" s="26" t="n"/>
-      <c r="U141" s="26" t="n"/>
     </row>
     <row r="142">
       <c r="B142" s="26" t="n"/>
@@ -3299,7 +3163,6 @@
       <c r="O142" s="27" t="n"/>
       <c r="Q142" s="27" t="n"/>
       <c r="T142" s="26" t="n"/>
-      <c r="U142" s="26" t="n"/>
     </row>
     <row r="143">
       <c r="B143" s="26" t="n"/>
@@ -3317,7 +3180,6 @@
       <c r="O143" s="27" t="n"/>
       <c r="Q143" s="27" t="n"/>
       <c r="T143" s="26" t="n"/>
-      <c r="U143" s="26" t="n"/>
     </row>
     <row r="144">
       <c r="B144" s="26" t="n"/>
@@ -3335,7 +3197,6 @@
       <c r="O144" s="27" t="n"/>
       <c r="Q144" s="27" t="n"/>
       <c r="T144" s="26" t="n"/>
-      <c r="U144" s="26" t="n"/>
     </row>
     <row r="145">
       <c r="B145" s="26" t="n"/>
@@ -3353,7 +3214,6 @@
       <c r="O145" s="27" t="n"/>
       <c r="Q145" s="27" t="n"/>
       <c r="T145" s="26" t="n"/>
-      <c r="U145" s="26" t="n"/>
     </row>
     <row r="146">
       <c r="B146" s="26" t="n"/>
@@ -3371,7 +3231,6 @@
       <c r="O146" s="27" t="n"/>
       <c r="Q146" s="27" t="n"/>
       <c r="T146" s="26" t="n"/>
-      <c r="U146" s="26" t="n"/>
     </row>
     <row r="147">
       <c r="B147" s="26" t="n"/>
@@ -3389,7 +3248,6 @@
       <c r="O147" s="27" t="n"/>
       <c r="Q147" s="27" t="n"/>
       <c r="T147" s="26" t="n"/>
-      <c r="U147" s="26" t="n"/>
     </row>
     <row r="148">
       <c r="B148" s="26" t="n"/>
@@ -3407,7 +3265,6 @@
       <c r="O148" s="27" t="n"/>
       <c r="Q148" s="27" t="n"/>
       <c r="T148" s="26" t="n"/>
-      <c r="U148" s="26" t="n"/>
     </row>
     <row r="149">
       <c r="B149" s="26" t="n"/>
@@ -3425,7 +3282,6 @@
       <c r="O149" s="27" t="n"/>
       <c r="Q149" s="27" t="n"/>
       <c r="T149" s="26" t="n"/>
-      <c r="U149" s="26" t="n"/>
     </row>
     <row r="150">
       <c r="B150" s="26" t="n"/>
@@ -3443,7 +3299,6 @@
       <c r="O150" s="27" t="n"/>
       <c r="Q150" s="27" t="n"/>
       <c r="T150" s="26" t="n"/>
-      <c r="U150" s="26" t="n"/>
     </row>
     <row r="151">
       <c r="B151" s="26" t="n"/>
@@ -3461,7 +3316,6 @@
       <c r="O151" s="27" t="n"/>
       <c r="Q151" s="27" t="n"/>
       <c r="T151" s="26" t="n"/>
-      <c r="U151" s="26" t="n"/>
     </row>
     <row r="152">
       <c r="B152" s="26" t="n"/>
@@ -3479,7 +3333,6 @@
       <c r="O152" s="27" t="n"/>
       <c r="Q152" s="27" t="n"/>
       <c r="T152" s="26" t="n"/>
-      <c r="U152" s="26" t="n"/>
     </row>
     <row r="153">
       <c r="B153" s="26" t="n"/>
@@ -3497,7 +3350,6 @@
       <c r="O153" s="27" t="n"/>
       <c r="Q153" s="27" t="n"/>
       <c r="T153" s="26" t="n"/>
-      <c r="U153" s="26" t="n"/>
     </row>
     <row r="154">
       <c r="B154" s="26" t="n"/>
@@ -3515,7 +3367,6 @@
       <c r="O154" s="27" t="n"/>
       <c r="Q154" s="27" t="n"/>
       <c r="T154" s="26" t="n"/>
-      <c r="U154" s="26" t="n"/>
     </row>
     <row r="155">
       <c r="B155" s="26" t="n"/>
@@ -3533,7 +3384,6 @@
       <c r="O155" s="27" t="n"/>
       <c r="Q155" s="27" t="n"/>
       <c r="T155" s="26" t="n"/>
-      <c r="U155" s="26" t="n"/>
     </row>
     <row r="156">
       <c r="B156" s="26" t="n"/>
@@ -3551,7 +3401,6 @@
       <c r="O156" s="27" t="n"/>
       <c r="Q156" s="27" t="n"/>
       <c r="T156" s="26" t="n"/>
-      <c r="U156" s="26" t="n"/>
     </row>
     <row r="157">
       <c r="B157" s="26" t="n"/>
@@ -3569,7 +3418,6 @@
       <c r="O157" s="27" t="n"/>
       <c r="Q157" s="27" t="n"/>
       <c r="T157" s="26" t="n"/>
-      <c r="U157" s="26" t="n"/>
     </row>
     <row r="158">
       <c r="B158" s="26" t="n"/>
@@ -3587,7 +3435,6 @@
       <c r="O158" s="27" t="n"/>
       <c r="Q158" s="27" t="n"/>
       <c r="T158" s="26" t="n"/>
-      <c r="U158" s="26" t="n"/>
     </row>
     <row r="159">
       <c r="B159" s="26" t="n"/>
@@ -3605,7 +3452,6 @@
       <c r="O159" s="27" t="n"/>
       <c r="Q159" s="27" t="n"/>
       <c r="T159" s="26" t="n"/>
-      <c r="U159" s="26" t="n"/>
     </row>
     <row r="160">
       <c r="B160" s="26" t="n"/>
@@ -3623,7 +3469,6 @@
       <c r="O160" s="27" t="n"/>
       <c r="Q160" s="27" t="n"/>
       <c r="T160" s="26" t="n"/>
-      <c r="U160" s="26" t="n"/>
     </row>
     <row r="161">
       <c r="B161" s="26" t="n"/>
@@ -3641,7 +3486,6 @@
       <c r="O161" s="27" t="n"/>
       <c r="Q161" s="27" t="n"/>
       <c r="T161" s="26" t="n"/>
-      <c r="U161" s="26" t="n"/>
     </row>
     <row r="162">
       <c r="B162" s="26" t="n"/>
@@ -3659,7 +3503,6 @@
       <c r="O162" s="27" t="n"/>
       <c r="Q162" s="27" t="n"/>
       <c r="T162" s="26" t="n"/>
-      <c r="U162" s="26" t="n"/>
     </row>
     <row r="163">
       <c r="B163" s="26" t="n"/>
@@ -3677,7 +3520,6 @@
       <c r="O163" s="27" t="n"/>
       <c r="Q163" s="27" t="n"/>
       <c r="T163" s="26" t="n"/>
-      <c r="U163" s="26" t="n"/>
     </row>
     <row r="164">
       <c r="B164" s="26" t="n"/>
@@ -3695,7 +3537,6 @@
       <c r="O164" s="27" t="n"/>
       <c r="Q164" s="27" t="n"/>
       <c r="T164" s="26" t="n"/>
-      <c r="U164" s="26" t="n"/>
     </row>
     <row r="165">
       <c r="B165" s="26" t="n"/>
@@ -3713,7 +3554,6 @@
       <c r="O165" s="27" t="n"/>
       <c r="Q165" s="27" t="n"/>
       <c r="T165" s="26" t="n"/>
-      <c r="U165" s="26" t="n"/>
     </row>
     <row r="166">
       <c r="B166" s="26" t="n"/>
@@ -3731,7 +3571,6 @@
       <c r="O166" s="27" t="n"/>
       <c r="Q166" s="27" t="n"/>
       <c r="T166" s="26" t="n"/>
-      <c r="U166" s="26" t="n"/>
     </row>
     <row r="167">
       <c r="B167" s="26" t="n"/>
@@ -3749,7 +3588,6 @@
       <c r="O167" s="27" t="n"/>
       <c r="Q167" s="27" t="n"/>
       <c r="T167" s="26" t="n"/>
-      <c r="U167" s="26" t="n"/>
     </row>
     <row r="168">
       <c r="B168" s="26" t="n"/>
@@ -3767,7 +3605,6 @@
       <c r="O168" s="27" t="n"/>
       <c r="Q168" s="27" t="n"/>
       <c r="T168" s="26" t="n"/>
-      <c r="U168" s="26" t="n"/>
     </row>
     <row r="169">
       <c r="B169" s="26" t="n"/>
@@ -3785,7 +3622,6 @@
       <c r="O169" s="27" t="n"/>
       <c r="Q169" s="27" t="n"/>
       <c r="T169" s="26" t="n"/>
-      <c r="U169" s="26" t="n"/>
     </row>
     <row r="170">
       <c r="B170" s="26" t="n"/>
@@ -3803,7 +3639,6 @@
       <c r="O170" s="27" t="n"/>
       <c r="Q170" s="27" t="n"/>
       <c r="T170" s="26" t="n"/>
-      <c r="U170" s="26" t="n"/>
     </row>
     <row r="171">
       <c r="B171" s="26" t="n"/>
@@ -3821,7 +3656,6 @@
       <c r="O171" s="27" t="n"/>
       <c r="Q171" s="27" t="n"/>
       <c r="T171" s="26" t="n"/>
-      <c r="U171" s="26" t="n"/>
     </row>
     <row r="172">
       <c r="B172" s="26" t="n"/>
@@ -3839,7 +3673,6 @@
       <c r="O172" s="27" t="n"/>
       <c r="Q172" s="27" t="n"/>
       <c r="T172" s="26" t="n"/>
-      <c r="U172" s="26" t="n"/>
     </row>
     <row r="173">
       <c r="B173" s="26" t="n"/>
@@ -3857,7 +3690,6 @@
       <c r="O173" s="27" t="n"/>
       <c r="Q173" s="27" t="n"/>
       <c r="T173" s="26" t="n"/>
-      <c r="U173" s="26" t="n"/>
     </row>
     <row r="174">
       <c r="B174" s="26" t="n"/>
@@ -3875,7 +3707,6 @@
       <c r="O174" s="27" t="n"/>
       <c r="Q174" s="27" t="n"/>
       <c r="T174" s="26" t="n"/>
-      <c r="U174" s="26" t="n"/>
     </row>
     <row r="175">
       <c r="B175" s="26" t="n"/>
@@ -3893,7 +3724,6 @@
       <c r="O175" s="27" t="n"/>
       <c r="Q175" s="27" t="n"/>
       <c r="T175" s="26" t="n"/>
-      <c r="U175" s="26" t="n"/>
     </row>
     <row r="176">
       <c r="B176" s="26" t="n"/>
@@ -3911,7 +3741,6 @@
       <c r="O176" s="27" t="n"/>
       <c r="Q176" s="27" t="n"/>
       <c r="T176" s="26" t="n"/>
-      <c r="U176" s="26" t="n"/>
     </row>
     <row r="177">
       <c r="B177" s="26" t="n"/>
@@ -3929,7 +3758,6 @@
       <c r="O177" s="27" t="n"/>
       <c r="Q177" s="27" t="n"/>
       <c r="T177" s="26" t="n"/>
-      <c r="U177" s="26" t="n"/>
     </row>
     <row r="178">
       <c r="B178" s="26" t="n"/>
@@ -3947,7 +3775,6 @@
       <c r="O178" s="27" t="n"/>
       <c r="Q178" s="27" t="n"/>
       <c r="T178" s="26" t="n"/>
-      <c r="U178" s="26" t="n"/>
     </row>
     <row r="179">
       <c r="B179" s="26" t="n"/>
@@ -3965,7 +3792,6 @@
       <c r="O179" s="27" t="n"/>
       <c r="Q179" s="27" t="n"/>
       <c r="T179" s="26" t="n"/>
-      <c r="U179" s="26" t="n"/>
     </row>
     <row r="180">
       <c r="B180" s="26" t="n"/>
@@ -3983,7 +3809,6 @@
       <c r="O180" s="27" t="n"/>
       <c r="Q180" s="27" t="n"/>
       <c r="T180" s="26" t="n"/>
-      <c r="U180" s="26" t="n"/>
     </row>
     <row r="181">
       <c r="B181" s="26" t="n"/>
@@ -4001,7 +3826,6 @@
       <c r="O181" s="27" t="n"/>
       <c r="Q181" s="27" t="n"/>
       <c r="T181" s="26" t="n"/>
-      <c r="U181" s="26" t="n"/>
     </row>
     <row r="182">
       <c r="B182" s="26" t="n"/>
@@ -4019,7 +3843,6 @@
       <c r="O182" s="27" t="n"/>
       <c r="Q182" s="27" t="n"/>
       <c r="T182" s="26" t="n"/>
-      <c r="U182" s="26" t="n"/>
     </row>
     <row r="183">
       <c r="B183" s="26" t="n"/>
@@ -4037,7 +3860,6 @@
       <c r="O183" s="27" t="n"/>
       <c r="Q183" s="27" t="n"/>
       <c r="T183" s="26" t="n"/>
-      <c r="U183" s="26" t="n"/>
     </row>
     <row r="184">
       <c r="B184" s="26" t="n"/>
@@ -4055,7 +3877,6 @@
       <c r="O184" s="27" t="n"/>
       <c r="Q184" s="27" t="n"/>
       <c r="T184" s="26" t="n"/>
-      <c r="U184" s="26" t="n"/>
     </row>
     <row r="185">
       <c r="B185" s="26" t="n"/>
@@ -4073,7 +3894,6 @@
       <c r="O185" s="27" t="n"/>
       <c r="Q185" s="27" t="n"/>
       <c r="T185" s="26" t="n"/>
-      <c r="U185" s="26" t="n"/>
     </row>
     <row r="186">
       <c r="B186" s="26" t="n"/>
@@ -4091,7 +3911,6 @@
       <c r="O186" s="27" t="n"/>
       <c r="Q186" s="27" t="n"/>
       <c r="T186" s="26" t="n"/>
-      <c r="U186" s="26" t="n"/>
     </row>
     <row r="187">
       <c r="B187" s="26" t="n"/>
@@ -4109,7 +3928,6 @@
       <c r="O187" s="27" t="n"/>
       <c r="Q187" s="27" t="n"/>
       <c r="T187" s="26" t="n"/>
-      <c r="U187" s="26" t="n"/>
     </row>
     <row r="188">
       <c r="B188" s="26" t="n"/>
@@ -4127,7 +3945,6 @@
       <c r="O188" s="27" t="n"/>
       <c r="Q188" s="27" t="n"/>
       <c r="T188" s="26" t="n"/>
-      <c r="U188" s="26" t="n"/>
     </row>
     <row r="189">
       <c r="B189" s="26" t="n"/>
@@ -4145,7 +3962,6 @@
       <c r="O189" s="27" t="n"/>
       <c r="Q189" s="27" t="n"/>
       <c r="T189" s="26" t="n"/>
-      <c r="U189" s="26" t="n"/>
     </row>
     <row r="190">
       <c r="B190" s="26" t="n"/>
@@ -4163,7 +3979,6 @@
       <c r="O190" s="27" t="n"/>
       <c r="Q190" s="27" t="n"/>
       <c r="T190" s="26" t="n"/>
-      <c r="U190" s="26" t="n"/>
     </row>
     <row r="191">
       <c r="B191" s="26" t="n"/>
@@ -4181,7 +3996,6 @@
       <c r="O191" s="27" t="n"/>
       <c r="Q191" s="27" t="n"/>
       <c r="T191" s="26" t="n"/>
-      <c r="U191" s="26" t="n"/>
     </row>
     <row r="192">
       <c r="B192" s="26" t="n"/>
@@ -4199,7 +4013,6 @@
       <c r="O192" s="27" t="n"/>
       <c r="Q192" s="27" t="n"/>
       <c r="T192" s="26" t="n"/>
-      <c r="U192" s="26" t="n"/>
     </row>
     <row r="193">
       <c r="B193" s="26" t="n"/>
@@ -4217,7 +4030,6 @@
       <c r="O193" s="27" t="n"/>
       <c r="Q193" s="27" t="n"/>
       <c r="T193" s="26" t="n"/>
-      <c r="U193" s="26" t="n"/>
     </row>
     <row r="194">
       <c r="B194" s="26" t="n"/>
@@ -4235,7 +4047,6 @@
       <c r="O194" s="27" t="n"/>
       <c r="Q194" s="27" t="n"/>
       <c r="T194" s="26" t="n"/>
-      <c r="U194" s="26" t="n"/>
     </row>
     <row r="195">
       <c r="B195" s="26" t="n"/>
@@ -4253,7 +4064,6 @@
       <c r="O195" s="27" t="n"/>
       <c r="Q195" s="27" t="n"/>
       <c r="T195" s="26" t="n"/>
-      <c r="U195" s="26" t="n"/>
     </row>
     <row r="196">
       <c r="B196" s="26" t="n"/>
@@ -4271,7 +4081,6 @@
       <c r="O196" s="27" t="n"/>
       <c r="Q196" s="27" t="n"/>
       <c r="T196" s="26" t="n"/>
-      <c r="U196" s="26" t="n"/>
     </row>
     <row r="197">
       <c r="B197" s="26" t="n"/>
@@ -4289,7 +4098,6 @@
       <c r="O197" s="27" t="n"/>
       <c r="Q197" s="27" t="n"/>
       <c r="T197" s="26" t="n"/>
-      <c r="U197" s="26" t="n"/>
     </row>
     <row r="198">
       <c r="B198" s="26" t="n"/>
@@ -4307,7 +4115,6 @@
       <c r="O198" s="27" t="n"/>
       <c r="Q198" s="27" t="n"/>
       <c r="T198" s="26" t="n"/>
-      <c r="U198" s="26" t="n"/>
     </row>
     <row r="199">
       <c r="B199" s="26" t="n"/>
@@ -4325,7 +4132,6 @@
       <c r="O199" s="27" t="n"/>
       <c r="Q199" s="27" t="n"/>
       <c r="T199" s="26" t="n"/>
-      <c r="U199" s="26" t="n"/>
     </row>
     <row r="200">
       <c r="B200" s="26" t="n"/>
@@ -4343,7 +4149,6 @@
       <c r="O200" s="27" t="n"/>
       <c r="Q200" s="27" t="n"/>
       <c r="T200" s="26" t="n"/>
-      <c r="U200" s="26" t="n"/>
     </row>
     <row r="201">
       <c r="B201" s="26" t="n"/>
@@ -4361,7 +4166,6 @@
       <c r="O201" s="27" t="n"/>
       <c r="Q201" s="27" t="n"/>
       <c r="T201" s="26" t="n"/>
-      <c r="U201" s="26" t="n"/>
     </row>
     <row r="202">
       <c r="B202" s="26" t="n"/>
@@ -4379,7 +4183,6 @@
       <c r="O202" s="27" t="n"/>
       <c r="Q202" s="27" t="n"/>
       <c r="T202" s="26" t="n"/>
-      <c r="U202" s="26" t="n"/>
     </row>
     <row r="203">
       <c r="B203" s="26" t="n"/>
@@ -4397,7 +4200,6 @@
       <c r="O203" s="27" t="n"/>
       <c r="Q203" s="27" t="n"/>
       <c r="T203" s="26" t="n"/>
-      <c r="U203" s="26" t="n"/>
     </row>
     <row r="204">
       <c r="B204" s="26" t="n"/>
@@ -4415,7 +4217,6 @@
       <c r="O204" s="27" t="n"/>
       <c r="Q204" s="27" t="n"/>
       <c r="T204" s="26" t="n"/>
-      <c r="U204" s="26" t="n"/>
     </row>
     <row r="205">
       <c r="B205" s="26" t="n"/>
@@ -4433,7 +4234,6 @@
       <c r="O205" s="27" t="n"/>
       <c r="Q205" s="27" t="n"/>
       <c r="T205" s="26" t="n"/>
-      <c r="U205" s="26" t="n"/>
     </row>
     <row r="206">
       <c r="B206" s="26" t="n"/>
@@ -4451,7 +4251,6 @@
       <c r="O206" s="27" t="n"/>
       <c r="Q206" s="27" t="n"/>
       <c r="T206" s="26" t="n"/>
-      <c r="U206" s="26" t="n"/>
     </row>
     <row r="207">
       <c r="B207" s="26" t="n"/>
@@ -4469,7 +4268,6 @@
       <c r="O207" s="27" t="n"/>
       <c r="Q207" s="27" t="n"/>
       <c r="T207" s="26" t="n"/>
-      <c r="U207" s="26" t="n"/>
     </row>
     <row r="208">
       <c r="B208" s="26" t="n"/>
@@ -4487,7 +4285,6 @@
       <c r="O208" s="27" t="n"/>
       <c r="Q208" s="27" t="n"/>
       <c r="T208" s="26" t="n"/>
-      <c r="U208" s="26" t="n"/>
     </row>
     <row r="209">
       <c r="B209" s="26" t="n"/>
@@ -4505,7 +4302,6 @@
       <c r="O209" s="27" t="n"/>
       <c r="Q209" s="27" t="n"/>
       <c r="T209" s="26" t="n"/>
-      <c r="U209" s="26" t="n"/>
     </row>
     <row r="210">
       <c r="B210" s="26" t="n"/>
@@ -4523,7 +4319,6 @@
       <c r="O210" s="27" t="n"/>
       <c r="Q210" s="27" t="n"/>
       <c r="T210" s="26" t="n"/>
-      <c r="U210" s="26" t="n"/>
     </row>
     <row r="211">
       <c r="B211" s="26" t="n"/>
@@ -4541,7 +4336,6 @@
       <c r="O211" s="27" t="n"/>
       <c r="Q211" s="27" t="n"/>
       <c r="T211" s="26" t="n"/>
-      <c r="U211" s="26" t="n"/>
     </row>
     <row r="212">
       <c r="B212" s="26" t="n"/>
@@ -4559,7 +4353,6 @@
       <c r="O212" s="27" t="n"/>
       <c r="Q212" s="27" t="n"/>
       <c r="T212" s="26" t="n"/>
-      <c r="U212" s="26" t="n"/>
     </row>
     <row r="213">
       <c r="B213" s="26" t="n"/>
@@ -4577,7 +4370,6 @@
       <c r="O213" s="27" t="n"/>
       <c r="Q213" s="27" t="n"/>
       <c r="T213" s="26" t="n"/>
-      <c r="U213" s="26" t="n"/>
     </row>
     <row r="214">
       <c r="B214" s="26" t="n"/>
@@ -4595,7 +4387,6 @@
       <c r="O214" s="27" t="n"/>
       <c r="Q214" s="27" t="n"/>
       <c r="T214" s="26" t="n"/>
-      <c r="U214" s="26" t="n"/>
     </row>
     <row r="215">
       <c r="B215" s="26" t="n"/>
@@ -4613,7 +4404,6 @@
       <c r="O215" s="27" t="n"/>
       <c r="Q215" s="27" t="n"/>
       <c r="T215" s="26" t="n"/>
-      <c r="U215" s="26" t="n"/>
     </row>
     <row r="216">
       <c r="B216" s="26" t="n"/>
@@ -4631,7 +4421,6 @@
       <c r="O216" s="27" t="n"/>
       <c r="Q216" s="27" t="n"/>
       <c r="T216" s="26" t="n"/>
-      <c r="U216" s="26" t="n"/>
     </row>
     <row r="217">
       <c r="B217" s="26" t="n"/>
@@ -4649,7 +4438,6 @@
       <c r="O217" s="27" t="n"/>
       <c r="Q217" s="27" t="n"/>
       <c r="T217" s="26" t="n"/>
-      <c r="U217" s="26" t="n"/>
     </row>
     <row r="218">
       <c r="B218" s="26" t="n"/>
@@ -4667,7 +4455,6 @@
       <c r="O218" s="27" t="n"/>
       <c r="Q218" s="27" t="n"/>
       <c r="T218" s="26" t="n"/>
-      <c r="U218" s="26" t="n"/>
     </row>
     <row r="219">
       <c r="B219" s="26" t="n"/>
@@ -4685,7 +4472,6 @@
       <c r="O219" s="27" t="n"/>
       <c r="Q219" s="27" t="n"/>
       <c r="T219" s="26" t="n"/>
-      <c r="U219" s="26" t="n"/>
     </row>
     <row r="220">
       <c r="B220" s="26" t="n"/>
@@ -4703,7 +4489,6 @@
       <c r="O220" s="27" t="n"/>
       <c r="Q220" s="27" t="n"/>
       <c r="T220" s="26" t="n"/>
-      <c r="U220" s="26" t="n"/>
     </row>
     <row r="221">
       <c r="B221" s="26" t="n"/>
@@ -4721,7 +4506,6 @@
       <c r="O221" s="27" t="n"/>
       <c r="Q221" s="27" t="n"/>
       <c r="T221" s="26" t="n"/>
-      <c r="U221" s="26" t="n"/>
     </row>
     <row r="222">
       <c r="B222" s="26" t="n"/>
@@ -4739,7 +4523,6 @@
       <c r="O222" s="27" t="n"/>
       <c r="Q222" s="27" t="n"/>
       <c r="T222" s="26" t="n"/>
-      <c r="U222" s="26" t="n"/>
     </row>
     <row r="223">
       <c r="B223" s="26" t="n"/>
@@ -4757,7 +4540,6 @@
       <c r="O223" s="27" t="n"/>
       <c r="Q223" s="27" t="n"/>
       <c r="T223" s="26" t="n"/>
-      <c r="U223" s="26" t="n"/>
     </row>
     <row r="224">
       <c r="B224" s="26" t="n"/>
@@ -4775,7 +4557,6 @@
       <c r="O224" s="27" t="n"/>
       <c r="Q224" s="27" t="n"/>
       <c r="T224" s="26" t="n"/>
-      <c r="U224" s="26" t="n"/>
     </row>
     <row r="225">
       <c r="B225" s="26" t="n"/>
@@ -4793,7 +4574,6 @@
       <c r="O225" s="27" t="n"/>
       <c r="Q225" s="27" t="n"/>
       <c r="T225" s="26" t="n"/>
-      <c r="U225" s="26" t="n"/>
     </row>
     <row r="226">
       <c r="B226" s="26" t="n"/>
@@ -4811,7 +4591,6 @@
       <c r="O226" s="27" t="n"/>
       <c r="Q226" s="27" t="n"/>
       <c r="T226" s="26" t="n"/>
-      <c r="U226" s="26" t="n"/>
     </row>
     <row r="227">
       <c r="B227" s="26" t="n"/>
@@ -4829,7 +4608,6 @@
       <c r="O227" s="27" t="n"/>
       <c r="Q227" s="27" t="n"/>
       <c r="T227" s="26" t="n"/>
-      <c r="U227" s="26" t="n"/>
     </row>
     <row r="228">
       <c r="B228" s="26" t="n"/>
@@ -4847,7 +4625,6 @@
       <c r="O228" s="27" t="n"/>
       <c r="Q228" s="27" t="n"/>
       <c r="T228" s="26" t="n"/>
-      <c r="U228" s="26" t="n"/>
     </row>
     <row r="229">
       <c r="B229" s="26" t="n"/>
@@ -4865,7 +4642,6 @@
       <c r="O229" s="27" t="n"/>
       <c r="Q229" s="27" t="n"/>
       <c r="T229" s="26" t="n"/>
-      <c r="U229" s="26" t="n"/>
     </row>
     <row r="230">
       <c r="B230" s="26" t="n"/>
@@ -4883,7 +4659,6 @@
       <c r="O230" s="27" t="n"/>
       <c r="Q230" s="27" t="n"/>
       <c r="T230" s="26" t="n"/>
-      <c r="U230" s="26" t="n"/>
     </row>
     <row r="231">
       <c r="B231" s="26" t="n"/>
@@ -4901,7 +4676,6 @@
       <c r="O231" s="27" t="n"/>
       <c r="Q231" s="27" t="n"/>
       <c r="T231" s="26" t="n"/>
-      <c r="U231" s="26" t="n"/>
     </row>
     <row r="232">
       <c r="B232" s="26" t="n"/>
@@ -4919,7 +4693,6 @@
       <c r="O232" s="27" t="n"/>
       <c r="Q232" s="27" t="n"/>
       <c r="T232" s="26" t="n"/>
-      <c r="U232" s="26" t="n"/>
     </row>
     <row r="233">
       <c r="B233" s="26" t="n"/>
@@ -4937,7 +4710,6 @@
       <c r="O233" s="27" t="n"/>
       <c r="Q233" s="27" t="n"/>
       <c r="T233" s="26" t="n"/>
-      <c r="U233" s="26" t="n"/>
     </row>
     <row r="234">
       <c r="B234" s="26" t="n"/>
@@ -4955,7 +4727,6 @@
       <c r="O234" s="27" t="n"/>
       <c r="Q234" s="27" t="n"/>
       <c r="T234" s="26" t="n"/>
-      <c r="U234" s="26" t="n"/>
     </row>
     <row r="235">
       <c r="B235" s="26" t="n"/>
@@ -4973,7 +4744,6 @@
       <c r="O235" s="27" t="n"/>
       <c r="Q235" s="27" t="n"/>
       <c r="T235" s="26" t="n"/>
-      <c r="U235" s="26" t="n"/>
     </row>
     <row r="236">
       <c r="B236" s="26" t="n"/>
@@ -4991,7 +4761,6 @@
       <c r="O236" s="27" t="n"/>
       <c r="Q236" s="27" t="n"/>
       <c r="T236" s="26" t="n"/>
-      <c r="U236" s="26" t="n"/>
     </row>
     <row r="237">
       <c r="B237" s="26" t="n"/>
@@ -5009,7 +4778,6 @@
       <c r="O237" s="27" t="n"/>
       <c r="Q237" s="27" t="n"/>
       <c r="T237" s="26" t="n"/>
-      <c r="U237" s="26" t="n"/>
     </row>
     <row r="238">
       <c r="B238" s="26" t="n"/>
@@ -5027,7 +4795,6 @@
       <c r="O238" s="27" t="n"/>
       <c r="Q238" s="27" t="n"/>
       <c r="T238" s="26" t="n"/>
-      <c r="U238" s="26" t="n"/>
     </row>
     <row r="239">
       <c r="B239" s="26" t="n"/>
@@ -5045,7 +4812,6 @@
       <c r="O239" s="27" t="n"/>
       <c r="Q239" s="27" t="n"/>
       <c r="T239" s="26" t="n"/>
-      <c r="U239" s="26" t="n"/>
     </row>
     <row r="240">
       <c r="B240" s="26" t="n"/>
@@ -5063,7 +4829,6 @@
       <c r="O240" s="27" t="n"/>
       <c r="Q240" s="27" t="n"/>
       <c r="T240" s="26" t="n"/>
-      <c r="U240" s="26" t="n"/>
     </row>
     <row r="241">
       <c r="B241" s="26" t="n"/>
@@ -5081,7 +4846,6 @@
       <c r="O241" s="27" t="n"/>
       <c r="Q241" s="27" t="n"/>
       <c r="T241" s="26" t="n"/>
-      <c r="U241" s="26" t="n"/>
     </row>
     <row r="242">
       <c r="B242" s="26" t="n"/>
@@ -5099,7 +4863,6 @@
       <c r="O242" s="27" t="n"/>
       <c r="Q242" s="27" t="n"/>
       <c r="T242" s="26" t="n"/>
-      <c r="U242" s="26" t="n"/>
     </row>
     <row r="243">
       <c r="B243" s="26" t="n"/>
@@ -5117,7 +4880,6 @@
       <c r="O243" s="27" t="n"/>
       <c r="Q243" s="27" t="n"/>
       <c r="T243" s="26" t="n"/>
-      <c r="U243" s="26" t="n"/>
     </row>
     <row r="244">
       <c r="B244" s="26" t="n"/>
@@ -5135,7 +4897,6 @@
       <c r="O244" s="27" t="n"/>
       <c r="Q244" s="27" t="n"/>
       <c r="T244" s="26" t="n"/>
-      <c r="U244" s="26" t="n"/>
     </row>
     <row r="245">
       <c r="B245" s="26" t="n"/>
@@ -5153,7 +4914,6 @@
       <c r="O245" s="27" t="n"/>
       <c r="Q245" s="27" t="n"/>
       <c r="T245" s="26" t="n"/>
-      <c r="U245" s="26" t="n"/>
     </row>
     <row r="246">
       <c r="B246" s="26" t="n"/>
@@ -5171,7 +4931,6 @@
       <c r="O246" s="27" t="n"/>
       <c r="Q246" s="27" t="n"/>
       <c r="T246" s="26" t="n"/>
-      <c r="U246" s="26" t="n"/>
     </row>
     <row r="247">
       <c r="B247" s="26" t="n"/>
@@ -5189,7 +4948,6 @@
       <c r="O247" s="27" t="n"/>
       <c r="Q247" s="27" t="n"/>
       <c r="T247" s="26" t="n"/>
-      <c r="U247" s="26" t="n"/>
     </row>
     <row r="248">
       <c r="B248" s="26" t="n"/>
@@ -5207,7 +4965,6 @@
       <c r="O248" s="27" t="n"/>
       <c r="Q248" s="27" t="n"/>
       <c r="T248" s="26" t="n"/>
-      <c r="U248" s="26" t="n"/>
     </row>
     <row r="249">
       <c r="B249" s="26" t="n"/>
@@ -5225,7 +4982,6 @@
       <c r="O249" s="27" t="n"/>
       <c r="Q249" s="27" t="n"/>
       <c r="T249" s="26" t="n"/>
-      <c r="U249" s="26" t="n"/>
     </row>
     <row r="250">
       <c r="B250" s="26" t="n"/>
@@ -5243,7 +4999,6 @@
       <c r="O250" s="27" t="n"/>
       <c r="Q250" s="27" t="n"/>
       <c r="T250" s="26" t="n"/>
-      <c r="U250" s="26" t="n"/>
     </row>
     <row r="251">
       <c r="B251" s="26" t="n"/>
@@ -5261,7 +5016,6 @@
       <c r="O251" s="27" t="n"/>
       <c r="Q251" s="27" t="n"/>
       <c r="T251" s="26" t="n"/>
-      <c r="U251" s="26" t="n"/>
     </row>
     <row r="252">
       <c r="B252" s="26" t="n"/>
@@ -5279,7 +5033,6 @@
       <c r="O252" s="27" t="n"/>
       <c r="Q252" s="27" t="n"/>
       <c r="T252" s="26" t="n"/>
-      <c r="U252" s="26" t="n"/>
     </row>
     <row r="253">
       <c r="B253" s="26" t="n"/>
@@ -5297,7 +5050,6 @@
       <c r="O253" s="27" t="n"/>
       <c r="Q253" s="27" t="n"/>
       <c r="T253" s="26" t="n"/>
-      <c r="U253" s="26" t="n"/>
     </row>
     <row r="254">
       <c r="B254" s="26" t="n"/>
@@ -5315,7 +5067,6 @@
       <c r="O254" s="27" t="n"/>
       <c r="Q254" s="27" t="n"/>
       <c r="T254" s="26" t="n"/>
-      <c r="U254" s="26" t="n"/>
     </row>
     <row r="255">
       <c r="B255" s="26" t="n"/>
@@ -5333,7 +5084,6 @@
       <c r="O255" s="27" t="n"/>
       <c r="Q255" s="27" t="n"/>
       <c r="T255" s="26" t="n"/>
-      <c r="U255" s="26" t="n"/>
     </row>
     <row r="256">
       <c r="B256" s="26" t="n"/>
@@ -5351,7 +5101,6 @@
       <c r="O256" s="27" t="n"/>
       <c r="Q256" s="27" t="n"/>
       <c r="T256" s="26" t="n"/>
-      <c r="U256" s="26" t="n"/>
     </row>
     <row r="257">
       <c r="B257" s="26" t="n"/>
@@ -5369,7 +5118,6 @@
       <c r="O257" s="27" t="n"/>
       <c r="Q257" s="27" t="n"/>
       <c r="T257" s="26" t="n"/>
-      <c r="U257" s="26" t="n"/>
     </row>
     <row r="258">
       <c r="B258" s="26" t="n"/>
@@ -5387,7 +5135,6 @@
       <c r="O258" s="27" t="n"/>
       <c r="Q258" s="27" t="n"/>
       <c r="T258" s="26" t="n"/>
-      <c r="U258" s="26" t="n"/>
     </row>
     <row r="259">
       <c r="B259" s="26" t="n"/>
@@ -5405,7 +5152,6 @@
       <c r="O259" s="27" t="n"/>
       <c r="Q259" s="27" t="n"/>
       <c r="T259" s="26" t="n"/>
-      <c r="U259" s="26" t="n"/>
     </row>
     <row r="260">
       <c r="B260" s="26" t="n"/>
@@ -5423,7 +5169,6 @@
       <c r="O260" s="27" t="n"/>
       <c r="Q260" s="27" t="n"/>
       <c r="T260" s="26" t="n"/>
-      <c r="U260" s="26" t="n"/>
     </row>
     <row r="261">
       <c r="B261" s="26" t="n"/>
@@ -5441,7 +5186,6 @@
       <c r="O261" s="27" t="n"/>
       <c r="Q261" s="27" t="n"/>
       <c r="T261" s="26" t="n"/>
-      <c r="U261" s="26" t="n"/>
     </row>
     <row r="262">
       <c r="B262" s="26" t="n"/>
@@ -5459,7 +5203,6 @@
       <c r="O262" s="27" t="n"/>
       <c r="Q262" s="27" t="n"/>
       <c r="T262" s="26" t="n"/>
-      <c r="U262" s="26" t="n"/>
     </row>
     <row r="263">
       <c r="B263" s="26" t="n"/>
@@ -5477,7 +5220,6 @@
       <c r="O263" s="27" t="n"/>
       <c r="Q263" s="27" t="n"/>
       <c r="T263" s="26" t="n"/>
-      <c r="U263" s="26" t="n"/>
     </row>
     <row r="264">
       <c r="B264" s="26" t="n"/>
@@ -5495,7 +5237,6 @@
       <c r="O264" s="27" t="n"/>
       <c r="Q264" s="27" t="n"/>
       <c r="T264" s="26" t="n"/>
-      <c r="U264" s="26" t="n"/>
     </row>
     <row r="265">
       <c r="B265" s="26" t="n"/>
@@ -5513,7 +5254,6 @@
       <c r="O265" s="27" t="n"/>
       <c r="Q265" s="27" t="n"/>
       <c r="T265" s="26" t="n"/>
-      <c r="U265" s="26" t="n"/>
     </row>
     <row r="266">
       <c r="B266" s="26" t="n"/>
@@ -5531,7 +5271,6 @@
       <c r="O266" s="27" t="n"/>
       <c r="Q266" s="27" t="n"/>
       <c r="T266" s="26" t="n"/>
-      <c r="U266" s="26" t="n"/>
     </row>
     <row r="267">
       <c r="B267" s="26" t="n"/>
@@ -5549,7 +5288,6 @@
       <c r="O267" s="27" t="n"/>
       <c r="Q267" s="27" t="n"/>
       <c r="T267" s="26" t="n"/>
-      <c r="U267" s="26" t="n"/>
     </row>
     <row r="268">
       <c r="B268" s="26" t="n"/>
@@ -5567,7 +5305,6 @@
       <c r="O268" s="27" t="n"/>
       <c r="Q268" s="27" t="n"/>
       <c r="T268" s="26" t="n"/>
-      <c r="U268" s="26" t="n"/>
     </row>
     <row r="269">
       <c r="B269" s="26" t="n"/>
@@ -5585,7 +5322,6 @@
       <c r="O269" s="27" t="n"/>
       <c r="Q269" s="27" t="n"/>
       <c r="T269" s="26" t="n"/>
-      <c r="U269" s="26" t="n"/>
     </row>
     <row r="270">
       <c r="B270" s="26" t="n"/>
@@ -5603,7 +5339,6 @@
       <c r="O270" s="27" t="n"/>
       <c r="Q270" s="27" t="n"/>
       <c r="T270" s="26" t="n"/>
-      <c r="U270" s="26" t="n"/>
     </row>
     <row r="271">
       <c r="B271" s="26" t="n"/>
@@ -5621,7 +5356,6 @@
       <c r="O271" s="27" t="n"/>
       <c r="Q271" s="27" t="n"/>
       <c r="T271" s="26" t="n"/>
-      <c r="U271" s="26" t="n"/>
     </row>
     <row r="272">
       <c r="B272" s="26" t="n"/>
@@ -5639,7 +5373,6 @@
       <c r="O272" s="27" t="n"/>
       <c r="Q272" s="27" t="n"/>
       <c r="T272" s="26" t="n"/>
-      <c r="U272" s="26" t="n"/>
     </row>
     <row r="273">
       <c r="B273" s="26" t="n"/>
@@ -5657,7 +5390,6 @@
       <c r="O273" s="27" t="n"/>
       <c r="Q273" s="27" t="n"/>
       <c r="T273" s="26" t="n"/>
-      <c r="U273" s="26" t="n"/>
     </row>
     <row r="274">
       <c r="B274" s="26" t="n"/>
@@ -5675,7 +5407,6 @@
       <c r="O274" s="27" t="n"/>
       <c r="Q274" s="27" t="n"/>
       <c r="T274" s="26" t="n"/>
-      <c r="U274" s="26" t="n"/>
     </row>
     <row r="275">
       <c r="B275" s="26" t="n"/>
@@ -5693,7 +5424,6 @@
       <c r="O275" s="27" t="n"/>
       <c r="Q275" s="27" t="n"/>
       <c r="T275" s="26" t="n"/>
-      <c r="U275" s="26" t="n"/>
     </row>
     <row r="276">
       <c r="B276" s="26" t="n"/>
@@ -5711,7 +5441,6 @@
       <c r="O276" s="27" t="n"/>
       <c r="Q276" s="27" t="n"/>
       <c r="T276" s="26" t="n"/>
-      <c r="U276" s="26" t="n"/>
     </row>
     <row r="277">
       <c r="B277" s="26" t="n"/>
@@ -5729,7 +5458,6 @@
       <c r="O277" s="27" t="n"/>
       <c r="Q277" s="27" t="n"/>
       <c r="T277" s="26" t="n"/>
-      <c r="U277" s="26" t="n"/>
     </row>
     <row r="278">
       <c r="B278" s="26" t="n"/>
@@ -5747,7 +5475,6 @@
       <c r="O278" s="27" t="n"/>
       <c r="Q278" s="27" t="n"/>
       <c r="T278" s="26" t="n"/>
-      <c r="U278" s="26" t="n"/>
     </row>
     <row r="279">
       <c r="B279" s="26" t="n"/>
@@ -5765,7 +5492,6 @@
       <c r="O279" s="27" t="n"/>
       <c r="Q279" s="27" t="n"/>
       <c r="T279" s="26" t="n"/>
-      <c r="U279" s="26" t="n"/>
     </row>
     <row r="280">
       <c r="B280" s="26" t="n"/>
@@ -5783,7 +5509,6 @@
       <c r="O280" s="27" t="n"/>
       <c r="Q280" s="27" t="n"/>
       <c r="T280" s="26" t="n"/>
-      <c r="U280" s="26" t="n"/>
     </row>
     <row r="281">
       <c r="B281" s="26" t="n"/>
@@ -5801,7 +5526,6 @@
       <c r="O281" s="27" t="n"/>
       <c r="Q281" s="27" t="n"/>
       <c r="T281" s="26" t="n"/>
-      <c r="U281" s="26" t="n"/>
     </row>
     <row r="282">
       <c r="B282" s="26" t="n"/>
@@ -5819,7 +5543,6 @@
       <c r="O282" s="27" t="n"/>
       <c r="Q282" s="27" t="n"/>
       <c r="T282" s="26" t="n"/>
-      <c r="U282" s="26" t="n"/>
     </row>
     <row r="283">
       <c r="B283" s="26" t="n"/>
@@ -5837,7 +5560,6 @@
       <c r="O283" s="27" t="n"/>
       <c r="Q283" s="27" t="n"/>
       <c r="T283" s="26" t="n"/>
-      <c r="U283" s="26" t="n"/>
     </row>
     <row r="284">
       <c r="B284" s="26" t="n"/>
@@ -5855,7 +5577,6 @@
       <c r="O284" s="27" t="n"/>
       <c r="Q284" s="27" t="n"/>
       <c r="T284" s="26" t="n"/>
-      <c r="U284" s="26" t="n"/>
     </row>
     <row r="285">
       <c r="B285" s="26" t="n"/>
@@ -5873,7 +5594,6 @@
       <c r="O285" s="27" t="n"/>
       <c r="Q285" s="27" t="n"/>
       <c r="T285" s="26" t="n"/>
-      <c r="U285" s="26" t="n"/>
     </row>
     <row r="286">
       <c r="B286" s="26" t="n"/>
@@ -5891,7 +5611,6 @@
       <c r="O286" s="27" t="n"/>
       <c r="Q286" s="27" t="n"/>
       <c r="T286" s="26" t="n"/>
-      <c r="U286" s="26" t="n"/>
     </row>
     <row r="287">
       <c r="B287" s="26" t="n"/>
@@ -5909,7 +5628,6 @@
       <c r="O287" s="27" t="n"/>
       <c r="Q287" s="27" t="n"/>
       <c r="T287" s="26" t="n"/>
-      <c r="U287" s="26" t="n"/>
     </row>
     <row r="288">
       <c r="B288" s="26" t="n"/>
@@ -5927,7 +5645,6 @@
       <c r="O288" s="27" t="n"/>
       <c r="Q288" s="27" t="n"/>
       <c r="T288" s="26" t="n"/>
-      <c r="U288" s="26" t="n"/>
     </row>
     <row r="289">
       <c r="B289" s="26" t="n"/>
@@ -5945,7 +5662,6 @@
       <c r="O289" s="27" t="n"/>
       <c r="Q289" s="27" t="n"/>
       <c r="T289" s="26" t="n"/>
-      <c r="U289" s="26" t="n"/>
     </row>
     <row r="290">
       <c r="B290" s="26" t="n"/>
@@ -5963,7 +5679,6 @@
       <c r="O290" s="27" t="n"/>
       <c r="Q290" s="27" t="n"/>
       <c r="T290" s="26" t="n"/>
-      <c r="U290" s="26" t="n"/>
     </row>
     <row r="291">
       <c r="B291" s="26" t="n"/>
@@ -5981,7 +5696,6 @@
       <c r="O291" s="27" t="n"/>
       <c r="Q291" s="27" t="n"/>
       <c r="T291" s="26" t="n"/>
-      <c r="U291" s="26" t="n"/>
     </row>
     <row r="292">
       <c r="B292" s="26" t="n"/>
@@ -5999,7 +5713,6 @@
       <c r="O292" s="27" t="n"/>
       <c r="Q292" s="27" t="n"/>
       <c r="T292" s="26" t="n"/>
-      <c r="U292" s="26" t="n"/>
     </row>
     <row r="293">
       <c r="B293" s="26" t="n"/>
@@ -6017,7 +5730,6 @@
       <c r="O293" s="27" t="n"/>
       <c r="Q293" s="27" t="n"/>
       <c r="T293" s="26" t="n"/>
-      <c r="U293" s="26" t="n"/>
     </row>
     <row r="294">
       <c r="B294" s="26" t="n"/>
@@ -6035,7 +5747,6 @@
       <c r="O294" s="27" t="n"/>
       <c r="Q294" s="27" t="n"/>
       <c r="T294" s="26" t="n"/>
-      <c r="U294" s="26" t="n"/>
     </row>
     <row r="295">
       <c r="B295" s="26" t="n"/>
@@ -6053,7 +5764,6 @@
       <c r="O295" s="27" t="n"/>
       <c r="Q295" s="27" t="n"/>
       <c r="T295" s="26" t="n"/>
-      <c r="U295" s="26" t="n"/>
     </row>
     <row r="296">
       <c r="B296" s="26" t="n"/>
@@ -6071,7 +5781,6 @@
       <c r="O296" s="27" t="n"/>
       <c r="Q296" s="27" t="n"/>
       <c r="T296" s="26" t="n"/>
-      <c r="U296" s="26" t="n"/>
     </row>
     <row r="297">
       <c r="B297" s="26" t="n"/>
@@ -6089,7 +5798,6 @@
       <c r="O297" s="27" t="n"/>
       <c r="Q297" s="27" t="n"/>
       <c r="T297" s="26" t="n"/>
-      <c r="U297" s="26" t="n"/>
     </row>
     <row r="298">
       <c r="B298" s="26" t="n"/>
@@ -6107,7 +5815,6 @@
       <c r="O298" s="27" t="n"/>
       <c r="Q298" s="27" t="n"/>
       <c r="T298" s="26" t="n"/>
-      <c r="U298" s="26" t="n"/>
     </row>
     <row r="299">
       <c r="B299" s="26" t="n"/>
@@ -6125,7 +5832,6 @@
       <c r="O299" s="27" t="n"/>
       <c r="Q299" s="27" t="n"/>
       <c r="T299" s="26" t="n"/>
-      <c r="U299" s="26" t="n"/>
     </row>
     <row r="300">
       <c r="B300" s="26" t="n"/>
@@ -6143,7 +5849,6 @@
       <c r="O300" s="27" t="n"/>
       <c r="Q300" s="27" t="n"/>
       <c r="T300" s="26" t="n"/>
-      <c r="U300" s="26" t="n"/>
     </row>
     <row r="301">
       <c r="B301" s="26" t="n"/>
@@ -6161,7 +5866,6 @@
       <c r="O301" s="27" t="n"/>
       <c r="Q301" s="27" t="n"/>
       <c r="T301" s="26" t="n"/>
-      <c r="U301" s="26" t="n"/>
     </row>
     <row r="302">
       <c r="B302" s="26" t="n"/>
@@ -6179,7 +5883,6 @@
       <c r="O302" s="27" t="n"/>
       <c r="Q302" s="27" t="n"/>
       <c r="T302" s="26" t="n"/>
-      <c r="U302" s="26" t="n"/>
     </row>
     <row r="303">
       <c r="B303" s="26" t="n"/>
@@ -6197,7 +5900,6 @@
       <c r="O303" s="27" t="n"/>
       <c r="Q303" s="27" t="n"/>
       <c r="T303" s="26" t="n"/>
-      <c r="U303" s="26" t="n"/>
     </row>
     <row r="304">
       <c r="B304" s="26" t="n"/>
@@ -6215,7 +5917,6 @@
       <c r="O304" s="27" t="n"/>
       <c r="Q304" s="27" t="n"/>
       <c r="T304" s="26" t="n"/>
-      <c r="U304" s="26" t="n"/>
     </row>
     <row r="305">
       <c r="B305" s="26" t="n"/>
@@ -6233,7 +5934,6 @@
       <c r="O305" s="27" t="n"/>
       <c r="Q305" s="27" t="n"/>
       <c r="T305" s="26" t="n"/>
-      <c r="U305" s="26" t="n"/>
     </row>
     <row r="306">
       <c r="B306" s="26" t="n"/>
@@ -6251,7 +5951,6 @@
       <c r="O306" s="27" t="n"/>
       <c r="Q306" s="27" t="n"/>
       <c r="T306" s="26" t="n"/>
-      <c r="U306" s="26" t="n"/>
     </row>
     <row r="307">
       <c r="B307" s="26" t="n"/>
@@ -6269,7 +5968,6 @@
       <c r="O307" s="27" t="n"/>
       <c r="Q307" s="27" t="n"/>
       <c r="T307" s="26" t="n"/>
-      <c r="U307" s="26" t="n"/>
     </row>
     <row r="308">
       <c r="B308" s="26" t="n"/>
@@ -6287,7 +5985,6 @@
       <c r="O308" s="27" t="n"/>
       <c r="Q308" s="27" t="n"/>
       <c r="T308" s="26" t="n"/>
-      <c r="U308" s="26" t="n"/>
     </row>
     <row r="309">
       <c r="B309" s="26" t="n"/>
@@ -6305,7 +6002,6 @@
       <c r="O309" s="27" t="n"/>
       <c r="Q309" s="27" t="n"/>
       <c r="T309" s="26" t="n"/>
-      <c r="U309" s="26" t="n"/>
     </row>
     <row r="310">
       <c r="B310" s="26" t="n"/>
@@ -6323,7 +6019,6 @@
       <c r="O310" s="27" t="n"/>
       <c r="Q310" s="27" t="n"/>
       <c r="T310" s="26" t="n"/>
-      <c r="U310" s="26" t="n"/>
     </row>
     <row r="311">
       <c r="B311" s="26" t="n"/>
@@ -6341,7 +6036,6 @@
       <c r="O311" s="27" t="n"/>
       <c r="Q311" s="27" t="n"/>
       <c r="T311" s="26" t="n"/>
-      <c r="U311" s="26" t="n"/>
     </row>
     <row r="312">
       <c r="B312" s="26" t="n"/>
@@ -6359,7 +6053,6 @@
       <c r="O312" s="27" t="n"/>
       <c r="Q312" s="27" t="n"/>
       <c r="T312" s="26" t="n"/>
-      <c r="U312" s="26" t="n"/>
     </row>
     <row r="313">
       <c r="B313" s="26" t="n"/>
@@ -6377,7 +6070,6 @@
       <c r="O313" s="27" t="n"/>
       <c r="Q313" s="27" t="n"/>
       <c r="T313" s="26" t="n"/>
-      <c r="U313" s="26" t="n"/>
     </row>
     <row r="314">
       <c r="B314" s="26" t="n"/>
@@ -6395,7 +6087,6 @@
       <c r="O314" s="27" t="n"/>
       <c r="Q314" s="27" t="n"/>
       <c r="T314" s="26" t="n"/>
-      <c r="U314" s="26" t="n"/>
     </row>
     <row r="315">
       <c r="B315" s="26" t="n"/>
@@ -6413,7 +6104,6 @@
       <c r="O315" s="27" t="n"/>
       <c r="Q315" s="27" t="n"/>
       <c r="T315" s="26" t="n"/>
-      <c r="U315" s="26" t="n"/>
     </row>
     <row r="316">
       <c r="B316" s="26" t="n"/>
@@ -6431,7 +6121,6 @@
       <c r="O316" s="27" t="n"/>
       <c r="Q316" s="27" t="n"/>
       <c r="T316" s="26" t="n"/>
-      <c r="U316" s="26" t="n"/>
     </row>
     <row r="317">
       <c r="B317" s="26" t="n"/>
@@ -6449,7 +6138,6 @@
       <c r="O317" s="27" t="n"/>
       <c r="Q317" s="27" t="n"/>
       <c r="T317" s="26" t="n"/>
-      <c r="U317" s="26" t="n"/>
     </row>
     <row r="318">
       <c r="B318" s="26" t="n"/>
@@ -6467,7 +6155,6 @@
       <c r="O318" s="27" t="n"/>
       <c r="Q318" s="27" t="n"/>
       <c r="T318" s="26" t="n"/>
-      <c r="U318" s="26" t="n"/>
     </row>
     <row r="319">
       <c r="B319" s="26" t="n"/>
@@ -6485,7 +6172,6 @@
       <c r="O319" s="27" t="n"/>
       <c r="Q319" s="27" t="n"/>
       <c r="T319" s="26" t="n"/>
-      <c r="U319" s="26" t="n"/>
     </row>
     <row r="320">
       <c r="B320" s="26" t="n"/>
@@ -6503,7 +6189,6 @@
       <c r="O320" s="27" t="n"/>
       <c r="Q320" s="27" t="n"/>
       <c r="T320" s="26" t="n"/>
-      <c r="U320" s="26" t="n"/>
     </row>
     <row r="321">
       <c r="B321" s="26" t="n"/>
@@ -6521,7 +6206,6 @@
       <c r="O321" s="27" t="n"/>
       <c r="Q321" s="27" t="n"/>
       <c r="T321" s="26" t="n"/>
-      <c r="U321" s="26" t="n"/>
     </row>
     <row r="322">
       <c r="B322" s="26" t="n"/>
@@ -6539,7 +6223,6 @@
       <c r="O322" s="27" t="n"/>
       <c r="Q322" s="27" t="n"/>
       <c r="T322" s="26" t="n"/>
-      <c r="U322" s="26" t="n"/>
     </row>
     <row r="323">
       <c r="B323" s="26" t="n"/>
@@ -6557,7 +6240,6 @@
       <c r="O323" s="27" t="n"/>
       <c r="Q323" s="27" t="n"/>
       <c r="T323" s="26" t="n"/>
-      <c r="U323" s="26" t="n"/>
     </row>
     <row r="324">
       <c r="B324" s="26" t="n"/>
@@ -6575,7 +6257,6 @@
       <c r="O324" s="27" t="n"/>
       <c r="Q324" s="27" t="n"/>
       <c r="T324" s="26" t="n"/>
-      <c r="U324" s="26" t="n"/>
     </row>
     <row r="325">
       <c r="B325" s="26" t="n"/>
@@ -6593,7 +6274,6 @@
       <c r="O325" s="27" t="n"/>
       <c r="Q325" s="27" t="n"/>
       <c r="T325" s="26" t="n"/>
-      <c r="U325" s="26" t="n"/>
     </row>
     <row r="326">
       <c r="B326" s="26" t="n"/>
@@ -6611,7 +6291,6 @@
       <c r="O326" s="27" t="n"/>
       <c r="Q326" s="27" t="n"/>
       <c r="T326" s="26" t="n"/>
-      <c r="U326" s="26" t="n"/>
     </row>
     <row r="327">
       <c r="B327" s="26" t="n"/>
@@ -6629,7 +6308,6 @@
       <c r="O327" s="27" t="n"/>
       <c r="Q327" s="27" t="n"/>
       <c r="T327" s="26" t="n"/>
-      <c r="U327" s="26" t="n"/>
     </row>
     <row r="328">
       <c r="B328" s="26" t="n"/>
@@ -6647,7 +6325,6 @@
       <c r="O328" s="27" t="n"/>
       <c r="Q328" s="27" t="n"/>
       <c r="T328" s="26" t="n"/>
-      <c r="U328" s="26" t="n"/>
     </row>
     <row r="329">
       <c r="B329" s="26" t="n"/>
@@ -6665,7 +6342,6 @@
       <c r="O329" s="27" t="n"/>
       <c r="Q329" s="27" t="n"/>
       <c r="T329" s="26" t="n"/>
-      <c r="U329" s="26" t="n"/>
     </row>
     <row r="330">
       <c r="B330" s="26" t="n"/>
@@ -6683,7 +6359,6 @@
       <c r="O330" s="27" t="n"/>
       <c r="Q330" s="27" t="n"/>
       <c r="T330" s="26" t="n"/>
-      <c r="U330" s="26" t="n"/>
     </row>
     <row r="331">
       <c r="B331" s="26" t="n"/>
@@ -6701,7 +6376,6 @@
       <c r="O331" s="27" t="n"/>
       <c r="Q331" s="27" t="n"/>
       <c r="T331" s="26" t="n"/>
-      <c r="U331" s="26" t="n"/>
     </row>
     <row r="332">
       <c r="B332" s="26" t="n"/>
@@ -6719,7 +6393,6 @@
       <c r="O332" s="27" t="n"/>
       <c r="Q332" s="27" t="n"/>
       <c r="T332" s="26" t="n"/>
-      <c r="U332" s="26" t="n"/>
     </row>
     <row r="333">
       <c r="B333" s="26" t="n"/>
@@ -6737,7 +6410,6 @@
       <c r="O333" s="27" t="n"/>
       <c r="Q333" s="27" t="n"/>
       <c r="T333" s="26" t="n"/>
-      <c r="U333" s="26" t="n"/>
     </row>
     <row r="334">
       <c r="B334" s="26" t="n"/>
@@ -6755,7 +6427,6 @@
       <c r="O334" s="27" t="n"/>
       <c r="Q334" s="27" t="n"/>
       <c r="T334" s="26" t="n"/>
-      <c r="U334" s="26" t="n"/>
     </row>
     <row r="335">
       <c r="B335" s="26" t="n"/>
@@ -6773,7 +6444,6 @@
       <c r="O335" s="27" t="n"/>
       <c r="Q335" s="27" t="n"/>
       <c r="T335" s="26" t="n"/>
-      <c r="U335" s="26" t="n"/>
     </row>
     <row r="336">
       <c r="B336" s="26" t="n"/>
@@ -6791,7 +6461,6 @@
       <c r="O336" s="27" t="n"/>
       <c r="Q336" s="27" t="n"/>
       <c r="T336" s="26" t="n"/>
-      <c r="U336" s="26" t="n"/>
     </row>
     <row r="337">
       <c r="B337" s="26" t="n"/>
@@ -6809,7 +6478,6 @@
       <c r="O337" s="27" t="n"/>
       <c r="Q337" s="27" t="n"/>
       <c r="T337" s="26" t="n"/>
-      <c r="U337" s="26" t="n"/>
     </row>
     <row r="338">
       <c r="B338" s="26" t="n"/>
@@ -6827,7 +6495,6 @@
       <c r="O338" s="27" t="n"/>
       <c r="Q338" s="27" t="n"/>
       <c r="T338" s="26" t="n"/>
-      <c r="U338" s="26" t="n"/>
     </row>
     <row r="339">
       <c r="B339" s="26" t="n"/>
@@ -6845,7 +6512,6 @@
       <c r="O339" s="27" t="n"/>
       <c r="Q339" s="27" t="n"/>
       <c r="T339" s="26" t="n"/>
-      <c r="U339" s="26" t="n"/>
     </row>
     <row r="340">
       <c r="B340" s="26" t="n"/>
@@ -6863,7 +6529,6 @@
       <c r="O340" s="27" t="n"/>
       <c r="Q340" s="27" t="n"/>
       <c r="T340" s="26" t="n"/>
-      <c r="U340" s="26" t="n"/>
     </row>
     <row r="341">
       <c r="B341" s="26" t="n"/>
@@ -6881,7 +6546,6 @@
       <c r="O341" s="27" t="n"/>
       <c r="Q341" s="27" t="n"/>
       <c r="T341" s="26" t="n"/>
-      <c r="U341" s="26" t="n"/>
     </row>
     <row r="342">
       <c r="B342" s="26" t="n"/>
@@ -6899,7 +6563,6 @@
       <c r="O342" s="27" t="n"/>
       <c r="Q342" s="27" t="n"/>
       <c r="T342" s="26" t="n"/>
-      <c r="U342" s="26" t="n"/>
     </row>
     <row r="343">
       <c r="B343" s="26" t="n"/>
@@ -6917,7 +6580,6 @@
       <c r="O343" s="27" t="n"/>
       <c r="Q343" s="27" t="n"/>
       <c r="T343" s="26" t="n"/>
-      <c r="U343" s="26" t="n"/>
     </row>
     <row r="344">
       <c r="B344" s="26" t="n"/>
@@ -6935,7 +6597,6 @@
       <c r="O344" s="27" t="n"/>
       <c r="Q344" s="27" t="n"/>
       <c r="T344" s="26" t="n"/>
-      <c r="U344" s="26" t="n"/>
     </row>
     <row r="345">
       <c r="B345" s="26" t="n"/>
@@ -6953,7 +6614,6 @@
       <c r="O345" s="27" t="n"/>
       <c r="Q345" s="27" t="n"/>
       <c r="T345" s="26" t="n"/>
-      <c r="U345" s="26" t="n"/>
     </row>
     <row r="346">
       <c r="B346" s="26" t="n"/>
@@ -6971,7 +6631,6 @@
       <c r="O346" s="27" t="n"/>
       <c r="Q346" s="27" t="n"/>
       <c r="T346" s="26" t="n"/>
-      <c r="U346" s="26" t="n"/>
     </row>
     <row r="347">
       <c r="B347" s="26" t="n"/>
@@ -6989,7 +6648,6 @@
       <c r="O347" s="27" t="n"/>
       <c r="Q347" s="27" t="n"/>
       <c r="T347" s="26" t="n"/>
-      <c r="U347" s="26" t="n"/>
     </row>
     <row r="348">
       <c r="B348" s="26" t="n"/>
@@ -7007,7 +6665,6 @@
       <c r="O348" s="27" t="n"/>
       <c r="Q348" s="27" t="n"/>
       <c r="T348" s="26" t="n"/>
-      <c r="U348" s="26" t="n"/>
     </row>
     <row r="349">
       <c r="B349" s="26" t="n"/>
@@ -7025,7 +6682,6 @@
       <c r="O349" s="27" t="n"/>
       <c r="Q349" s="27" t="n"/>
       <c r="T349" s="26" t="n"/>
-      <c r="U349" s="26" t="n"/>
     </row>
     <row r="350">
       <c r="B350" s="26" t="n"/>
@@ -7043,7 +6699,6 @@
       <c r="O350" s="27" t="n"/>
       <c r="Q350" s="27" t="n"/>
       <c r="T350" s="26" t="n"/>
-      <c r="U350" s="26" t="n"/>
     </row>
     <row r="351">
       <c r="B351" s="26" t="n"/>
@@ -7061,7 +6716,6 @@
       <c r="O351" s="27" t="n"/>
       <c r="Q351" s="27" t="n"/>
       <c r="T351" s="26" t="n"/>
-      <c r="U351" s="26" t="n"/>
     </row>
     <row r="352">
       <c r="B352" s="26" t="n"/>
@@ -7079,7 +6733,6 @@
       <c r="O352" s="27" t="n"/>
       <c r="Q352" s="27" t="n"/>
       <c r="T352" s="26" t="n"/>
-      <c r="U352" s="26" t="n"/>
     </row>
     <row r="353">
       <c r="B353" s="26" t="n"/>
@@ -7097,7 +6750,6 @@
       <c r="O353" s="27" t="n"/>
       <c r="Q353" s="27" t="n"/>
       <c r="T353" s="26" t="n"/>
-      <c r="U353" s="26" t="n"/>
     </row>
     <row r="354">
       <c r="B354" s="26" t="n"/>
@@ -7115,7 +6767,6 @@
       <c r="O354" s="27" t="n"/>
       <c r="Q354" s="27" t="n"/>
       <c r="T354" s="26" t="n"/>
-      <c r="U354" s="26" t="n"/>
     </row>
     <row r="355">
       <c r="B355" s="26" t="n"/>
@@ -7133,7 +6784,6 @@
       <c r="O355" s="27" t="n"/>
       <c r="Q355" s="27" t="n"/>
       <c r="T355" s="26" t="n"/>
-      <c r="U355" s="26" t="n"/>
     </row>
     <row r="356">
       <c r="B356" s="26" t="n"/>
@@ -7151,7 +6801,6 @@
       <c r="O356" s="27" t="n"/>
       <c r="Q356" s="27" t="n"/>
       <c r="T356" s="26" t="n"/>
-      <c r="U356" s="26" t="n"/>
     </row>
     <row r="357">
       <c r="B357" s="26" t="n"/>
@@ -7169,7 +6818,6 @@
       <c r="O357" s="27" t="n"/>
       <c r="Q357" s="27" t="n"/>
       <c r="T357" s="26" t="n"/>
-      <c r="U357" s="26" t="n"/>
     </row>
     <row r="358">
       <c r="B358" s="26" t="n"/>
@@ -7187,7 +6835,6 @@
       <c r="O358" s="27" t="n"/>
       <c r="Q358" s="27" t="n"/>
       <c r="T358" s="26" t="n"/>
-      <c r="U358" s="26" t="n"/>
     </row>
     <row r="359">
       <c r="B359" s="26" t="n"/>
@@ -7205,7 +6852,6 @@
       <c r="O359" s="27" t="n"/>
       <c r="Q359" s="27" t="n"/>
       <c r="T359" s="26" t="n"/>
-      <c r="U359" s="26" t="n"/>
     </row>
     <row r="360">
       <c r="B360" s="26" t="n"/>
@@ -7223,7 +6869,6 @@
       <c r="O360" s="27" t="n"/>
       <c r="Q360" s="27" t="n"/>
       <c r="T360" s="26" t="n"/>
-      <c r="U360" s="26" t="n"/>
     </row>
     <row r="361">
       <c r="B361" s="26" t="n"/>
@@ -7241,7 +6886,6 @@
       <c r="O361" s="27" t="n"/>
       <c r="Q361" s="27" t="n"/>
       <c r="T361" s="26" t="n"/>
-      <c r="U361" s="26" t="n"/>
     </row>
     <row r="362">
       <c r="B362" s="26" t="n"/>
@@ -7259,7 +6903,6 @@
       <c r="O362" s="27" t="n"/>
       <c r="Q362" s="27" t="n"/>
       <c r="T362" s="26" t="n"/>
-      <c r="U362" s="26" t="n"/>
     </row>
     <row r="363">
       <c r="B363" s="26" t="n"/>
@@ -7277,7 +6920,6 @@
       <c r="O363" s="27" t="n"/>
       <c r="Q363" s="27" t="n"/>
       <c r="T363" s="26" t="n"/>
-      <c r="U363" s="26" t="n"/>
     </row>
     <row r="364">
       <c r="B364" s="26" t="n"/>
@@ -7295,7 +6937,6 @@
       <c r="O364" s="27" t="n"/>
       <c r="Q364" s="27" t="n"/>
       <c r="T364" s="26" t="n"/>
-      <c r="U364" s="26" t="n"/>
     </row>
     <row r="365">
       <c r="B365" s="26" t="n"/>
@@ -7313,7 +6954,6 @@
       <c r="O365" s="27" t="n"/>
       <c r="Q365" s="27" t="n"/>
       <c r="T365" s="26" t="n"/>
-      <c r="U365" s="26" t="n"/>
     </row>
     <row r="366">
       <c r="B366" s="26" t="n"/>
@@ -7331,7 +6971,6 @@
       <c r="O366" s="27" t="n"/>
       <c r="Q366" s="27" t="n"/>
       <c r="T366" s="26" t="n"/>
-      <c r="U366" s="26" t="n"/>
     </row>
     <row r="367">
       <c r="B367" s="26" t="n"/>
@@ -7349,7 +6988,6 @@
       <c r="O367" s="27" t="n"/>
       <c r="Q367" s="27" t="n"/>
       <c r="T367" s="26" t="n"/>
-      <c r="U367" s="26" t="n"/>
     </row>
     <row r="368">
       <c r="B368" s="26" t="n"/>
@@ -7367,7 +7005,6 @@
       <c r="O368" s="27" t="n"/>
       <c r="Q368" s="27" t="n"/>
       <c r="T368" s="26" t="n"/>
-      <c r="U368" s="26" t="n"/>
     </row>
     <row r="369">
       <c r="B369" s="26" t="n"/>
@@ -7385,7 +7022,6 @@
       <c r="O369" s="27" t="n"/>
       <c r="Q369" s="27" t="n"/>
       <c r="T369" s="26" t="n"/>
-      <c r="U369" s="26" t="n"/>
     </row>
     <row r="370">
       <c r="B370" s="26" t="n"/>
@@ -7403,7 +7039,6 @@
       <c r="O370" s="27" t="n"/>
       <c r="Q370" s="27" t="n"/>
       <c r="T370" s="26" t="n"/>
-      <c r="U370" s="26" t="n"/>
     </row>
     <row r="371">
       <c r="B371" s="26" t="n"/>
@@ -7421,7 +7056,6 @@
       <c r="O371" s="27" t="n"/>
       <c r="Q371" s="27" t="n"/>
       <c r="T371" s="26" t="n"/>
-      <c r="U371" s="26" t="n"/>
     </row>
     <row r="372">
       <c r="B372" s="26" t="n"/>
@@ -7439,7 +7073,6 @@
       <c r="O372" s="27" t="n"/>
       <c r="Q372" s="27" t="n"/>
       <c r="T372" s="26" t="n"/>
-      <c r="U372" s="26" t="n"/>
     </row>
     <row r="373">
       <c r="B373" s="26" t="n"/>
@@ -7457,7 +7090,6 @@
       <c r="O373" s="27" t="n"/>
       <c r="Q373" s="27" t="n"/>
       <c r="T373" s="26" t="n"/>
-      <c r="U373" s="26" t="n"/>
     </row>
     <row r="374">
       <c r="B374" s="26" t="n"/>
@@ -7475,7 +7107,6 @@
       <c r="O374" s="27" t="n"/>
       <c r="Q374" s="27" t="n"/>
       <c r="T374" s="26" t="n"/>
-      <c r="U374" s="26" t="n"/>
     </row>
     <row r="375">
       <c r="B375" s="26" t="n"/>
@@ -7493,7 +7124,6 @@
       <c r="O375" s="27" t="n"/>
       <c r="Q375" s="27" t="n"/>
       <c r="T375" s="26" t="n"/>
-      <c r="U375" s="26" t="n"/>
     </row>
     <row r="376">
       <c r="B376" s="26" t="n"/>
@@ -7511,7 +7141,6 @@
       <c r="O376" s="27" t="n"/>
       <c r="Q376" s="27" t="n"/>
       <c r="T376" s="26" t="n"/>
-      <c r="U376" s="26" t="n"/>
     </row>
     <row r="377">
       <c r="B377" s="26" t="n"/>
@@ -7529,7 +7158,6 @@
       <c r="O377" s="27" t="n"/>
       <c r="Q377" s="27" t="n"/>
       <c r="T377" s="26" t="n"/>
-      <c r="U377" s="26" t="n"/>
     </row>
     <row r="378">
       <c r="B378" s="26" t="n"/>
@@ -7547,7 +7175,6 @@
       <c r="O378" s="27" t="n"/>
       <c r="Q378" s="27" t="n"/>
       <c r="T378" s="26" t="n"/>
-      <c r="U378" s="26" t="n"/>
     </row>
     <row r="379">
       <c r="B379" s="26" t="n"/>
@@ -7565,7 +7192,6 @@
       <c r="O379" s="27" t="n"/>
       <c r="Q379" s="27" t="n"/>
       <c r="T379" s="26" t="n"/>
-      <c r="U379" s="26" t="n"/>
     </row>
     <row r="380">
       <c r="B380" s="26" t="n"/>
@@ -7583,7 +7209,6 @@
       <c r="O380" s="27" t="n"/>
       <c r="Q380" s="27" t="n"/>
       <c r="T380" s="26" t="n"/>
-      <c r="U380" s="26" t="n"/>
     </row>
     <row r="381">
       <c r="B381" s="26" t="n"/>
@@ -7601,7 +7226,6 @@
       <c r="O381" s="27" t="n"/>
       <c r="Q381" s="27" t="n"/>
       <c r="T381" s="26" t="n"/>
-      <c r="U381" s="26" t="n"/>
     </row>
     <row r="382">
       <c r="B382" s="26" t="n"/>
@@ -7619,7 +7243,6 @@
       <c r="O382" s="27" t="n"/>
       <c r="Q382" s="27" t="n"/>
       <c r="T382" s="26" t="n"/>
-      <c r="U382" s="26" t="n"/>
     </row>
     <row r="383">
       <c r="B383" s="26" t="n"/>
@@ -7637,7 +7260,6 @@
       <c r="O383" s="27" t="n"/>
       <c r="Q383" s="27" t="n"/>
       <c r="T383" s="26" t="n"/>
-      <c r="U383" s="26" t="n"/>
     </row>
     <row r="384">
       <c r="B384" s="26" t="n"/>
@@ -7655,7 +7277,6 @@
       <c r="O384" s="27" t="n"/>
       <c r="Q384" s="27" t="n"/>
       <c r="T384" s="26" t="n"/>
-      <c r="U384" s="26" t="n"/>
     </row>
     <row r="385">
       <c r="B385" s="26" t="n"/>
@@ -7673,7 +7294,6 @@
       <c r="O385" s="27" t="n"/>
       <c r="Q385" s="27" t="n"/>
       <c r="T385" s="26" t="n"/>
-      <c r="U385" s="26" t="n"/>
     </row>
     <row r="386">
       <c r="B386" s="26" t="n"/>
@@ -7691,7 +7311,6 @@
       <c r="O386" s="27" t="n"/>
       <c r="Q386" s="27" t="n"/>
       <c r="T386" s="26" t="n"/>
-      <c r="U386" s="26" t="n"/>
     </row>
     <row r="387">
       <c r="B387" s="26" t="n"/>
@@ -7709,7 +7328,6 @@
       <c r="O387" s="27" t="n"/>
       <c r="Q387" s="27" t="n"/>
       <c r="T387" s="26" t="n"/>
-      <c r="U387" s="26" t="n"/>
     </row>
     <row r="388">
       <c r="B388" s="26" t="n"/>
@@ -7727,7 +7345,6 @@
       <c r="O388" s="27" t="n"/>
       <c r="Q388" s="27" t="n"/>
       <c r="T388" s="26" t="n"/>
-      <c r="U388" s="26" t="n"/>
     </row>
     <row r="389">
       <c r="B389" s="26" t="n"/>
@@ -7745,7 +7362,6 @@
       <c r="O389" s="27" t="n"/>
       <c r="Q389" s="27" t="n"/>
       <c r="T389" s="26" t="n"/>
-      <c r="U389" s="26" t="n"/>
     </row>
     <row r="390">
       <c r="B390" s="26" t="n"/>
@@ -7763,7 +7379,6 @@
       <c r="O390" s="27" t="n"/>
       <c r="Q390" s="27" t="n"/>
       <c r="T390" s="26" t="n"/>
-      <c r="U390" s="26" t="n"/>
     </row>
     <row r="391">
       <c r="B391" s="26" t="n"/>
@@ -7781,7 +7396,6 @@
       <c r="O391" s="27" t="n"/>
       <c r="Q391" s="27" t="n"/>
       <c r="T391" s="26" t="n"/>
-      <c r="U391" s="26" t="n"/>
     </row>
     <row r="392">
       <c r="B392" s="26" t="n"/>
@@ -7799,7 +7413,6 @@
       <c r="O392" s="27" t="n"/>
       <c r="Q392" s="27" t="n"/>
       <c r="T392" s="26" t="n"/>
-      <c r="U392" s="26" t="n"/>
     </row>
     <row r="393">
       <c r="B393" s="26" t="n"/>
@@ -7817,7 +7430,6 @@
       <c r="O393" s="27" t="n"/>
       <c r="Q393" s="27" t="n"/>
       <c r="T393" s="26" t="n"/>
-      <c r="U393" s="26" t="n"/>
     </row>
     <row r="394">
       <c r="B394" s="26" t="n"/>
@@ -7835,7 +7447,6 @@
       <c r="O394" s="27" t="n"/>
       <c r="Q394" s="27" t="n"/>
       <c r="T394" s="26" t="n"/>
-      <c r="U394" s="26" t="n"/>
     </row>
     <row r="395">
       <c r="B395" s="26" t="n"/>
@@ -7853,7 +7464,6 @@
       <c r="O395" s="27" t="n"/>
       <c r="Q395" s="27" t="n"/>
       <c r="T395" s="26" t="n"/>
-      <c r="U395" s="26" t="n"/>
     </row>
     <row r="396">
       <c r="B396" s="26" t="n"/>
@@ -7871,7 +7481,6 @@
       <c r="O396" s="27" t="n"/>
       <c r="Q396" s="27" t="n"/>
       <c r="T396" s="26" t="n"/>
-      <c r="U396" s="26" t="n"/>
     </row>
     <row r="397">
       <c r="B397" s="26" t="n"/>
@@ -7889,7 +7498,6 @@
       <c r="O397" s="27" t="n"/>
       <c r="Q397" s="27" t="n"/>
       <c r="T397" s="26" t="n"/>
-      <c r="U397" s="26" t="n"/>
     </row>
     <row r="398">
       <c r="B398" s="26" t="n"/>
@@ -7907,7 +7515,6 @@
       <c r="O398" s="27" t="n"/>
       <c r="Q398" s="27" t="n"/>
       <c r="T398" s="26" t="n"/>
-      <c r="U398" s="26" t="n"/>
     </row>
     <row r="399">
       <c r="B399" s="26" t="n"/>
@@ -7925,7 +7532,6 @@
       <c r="O399" s="27" t="n"/>
       <c r="Q399" s="27" t="n"/>
       <c r="T399" s="26" t="n"/>
-      <c r="U399" s="26" t="n"/>
     </row>
     <row r="400">
       <c r="B400" s="26" t="n"/>
@@ -7943,7 +7549,6 @@
       <c r="O400" s="27" t="n"/>
       <c r="Q400" s="27" t="n"/>
       <c r="T400" s="26" t="n"/>
-      <c r="U400" s="26" t="n"/>
     </row>
     <row r="401">
       <c r="B401" s="26" t="n"/>
@@ -7961,7 +7566,6 @@
       <c r="O401" s="27" t="n"/>
       <c r="Q401" s="27" t="n"/>
       <c r="T401" s="26" t="n"/>
-      <c r="U401" s="26" t="n"/>
     </row>
     <row r="402">
       <c r="B402" s="26" t="n"/>
@@ -7979,7 +7583,6 @@
       <c r="O402" s="27" t="n"/>
       <c r="Q402" s="27" t="n"/>
       <c r="T402" s="26" t="n"/>
-      <c r="U402" s="26" t="n"/>
     </row>
     <row r="403">
       <c r="B403" s="26" t="n"/>
@@ -7997,7 +7600,6 @@
       <c r="O403" s="27" t="n"/>
       <c r="Q403" s="27" t="n"/>
       <c r="T403" s="26" t="n"/>
-      <c r="U403" s="26" t="n"/>
     </row>
     <row r="404">
       <c r="B404" s="26" t="n"/>
@@ -8015,7 +7617,6 @@
       <c r="O404" s="27" t="n"/>
       <c r="Q404" s="27" t="n"/>
       <c r="T404" s="26" t="n"/>
-      <c r="U404" s="26" t="n"/>
     </row>
     <row r="405">
       <c r="B405" s="26" t="n"/>
@@ -8033,7 +7634,6 @@
       <c r="O405" s="27" t="n"/>
       <c r="Q405" s="27" t="n"/>
       <c r="T405" s="26" t="n"/>
-      <c r="U405" s="26" t="n"/>
     </row>
     <row r="406">
       <c r="B406" s="26" t="n"/>
@@ -8051,7 +7651,6 @@
       <c r="O406" s="27" t="n"/>
       <c r="Q406" s="27" t="n"/>
       <c r="T406" s="26" t="n"/>
-      <c r="U406" s="26" t="n"/>
     </row>
     <row r="407">
       <c r="B407" s="26" t="n"/>
@@ -8069,7 +7668,6 @@
       <c r="O407" s="27" t="n"/>
       <c r="Q407" s="27" t="n"/>
       <c r="T407" s="26" t="n"/>
-      <c r="U407" s="26" t="n"/>
     </row>
     <row r="408">
       <c r="B408" s="26" t="n"/>
@@ -8087,7 +7685,6 @@
       <c r="O408" s="27" t="n"/>
       <c r="Q408" s="27" t="n"/>
       <c r="T408" s="26" t="n"/>
-      <c r="U408" s="26" t="n"/>
     </row>
     <row r="409">
       <c r="B409" s="26" t="n"/>
@@ -8105,7 +7702,6 @@
       <c r="O409" s="27" t="n"/>
       <c r="Q409" s="27" t="n"/>
       <c r="T409" s="26" t="n"/>
-      <c r="U409" s="26" t="n"/>
     </row>
     <row r="410">
       <c r="B410" s="26" t="n"/>
@@ -8123,7 +7719,6 @@
       <c r="O410" s="27" t="n"/>
       <c r="Q410" s="27" t="n"/>
       <c r="T410" s="26" t="n"/>
-      <c r="U410" s="26" t="n"/>
     </row>
     <row r="411">
       <c r="B411" s="26" t="n"/>
@@ -8141,7 +7736,6 @@
       <c r="O411" s="27" t="n"/>
       <c r="Q411" s="27" t="n"/>
       <c r="T411" s="26" t="n"/>
-      <c r="U411" s="26" t="n"/>
     </row>
     <row r="412">
       <c r="B412" s="26" t="n"/>
@@ -8159,7 +7753,6 @@
       <c r="O412" s="27" t="n"/>
       <c r="Q412" s="27" t="n"/>
       <c r="T412" s="26" t="n"/>
-      <c r="U412" s="26" t="n"/>
     </row>
     <row r="413">
       <c r="B413" s="26" t="n"/>
@@ -8177,7 +7770,6 @@
       <c r="O413" s="27" t="n"/>
       <c r="Q413" s="27" t="n"/>
       <c r="T413" s="26" t="n"/>
-      <c r="U413" s="26" t="n"/>
     </row>
     <row r="414">
       <c r="B414" s="26" t="n"/>
@@ -8195,7 +7787,6 @@
       <c r="O414" s="27" t="n"/>
       <c r="Q414" s="27" t="n"/>
       <c r="T414" s="26" t="n"/>
-      <c r="U414" s="26" t="n"/>
     </row>
     <row r="415">
       <c r="B415" s="26" t="n"/>
@@ -8213,7 +7804,6 @@
       <c r="O415" s="27" t="n"/>
       <c r="Q415" s="27" t="n"/>
       <c r="T415" s="26" t="n"/>
-      <c r="U415" s="26" t="n"/>
     </row>
     <row r="416">
       <c r="B416" s="26" t="n"/>
@@ -8231,7 +7821,6 @@
       <c r="O416" s="27" t="n"/>
       <c r="Q416" s="27" t="n"/>
       <c r="T416" s="26" t="n"/>
-      <c r="U416" s="26" t="n"/>
     </row>
     <row r="417">
       <c r="B417" s="26" t="n"/>
@@ -8249,7 +7838,6 @@
       <c r="O417" s="27" t="n"/>
       <c r="Q417" s="27" t="n"/>
       <c r="T417" s="26" t="n"/>
-      <c r="U417" s="26" t="n"/>
     </row>
     <row r="418">
       <c r="B418" s="26" t="n"/>
@@ -8267,7 +7855,6 @@
       <c r="O418" s="27" t="n"/>
       <c r="Q418" s="27" t="n"/>
       <c r="T418" s="26" t="n"/>
-      <c r="U418" s="26" t="n"/>
     </row>
     <row r="419">
       <c r="B419" s="26" t="n"/>
@@ -8285,7 +7872,6 @@
       <c r="O419" s="27" t="n"/>
       <c r="Q419" s="27" t="n"/>
       <c r="T419" s="26" t="n"/>
-      <c r="U419" s="26" t="n"/>
     </row>
     <row r="420">
       <c r="B420" s="26" t="n"/>
@@ -8303,7 +7889,6 @@
       <c r="O420" s="27" t="n"/>
       <c r="Q420" s="27" t="n"/>
       <c r="T420" s="26" t="n"/>
-      <c r="U420" s="26" t="n"/>
     </row>
     <row r="421">
       <c r="B421" s="26" t="n"/>
@@ -8321,7 +7906,6 @@
       <c r="O421" s="27" t="n"/>
       <c r="Q421" s="27" t="n"/>
       <c r="T421" s="26" t="n"/>
-      <c r="U421" s="26" t="n"/>
     </row>
     <row r="422">
       <c r="B422" s="26" t="n"/>
@@ -8339,7 +7923,6 @@
       <c r="O422" s="27" t="n"/>
       <c r="Q422" s="27" t="n"/>
       <c r="T422" s="26" t="n"/>
-      <c r="U422" s="26" t="n"/>
     </row>
     <row r="423">
       <c r="B423" s="26" t="n"/>
@@ -8357,7 +7940,6 @@
       <c r="O423" s="27" t="n"/>
       <c r="Q423" s="27" t="n"/>
       <c r="T423" s="26" t="n"/>
-      <c r="U423" s="26" t="n"/>
     </row>
     <row r="424">
       <c r="B424" s="26" t="n"/>
@@ -8375,7 +7957,6 @@
       <c r="O424" s="27" t="n"/>
       <c r="Q424" s="27" t="n"/>
       <c r="T424" s="26" t="n"/>
-      <c r="U424" s="26" t="n"/>
     </row>
     <row r="425">
       <c r="B425" s="26" t="n"/>
@@ -8393,7 +7974,6 @@
       <c r="O425" s="27" t="n"/>
       <c r="Q425" s="27" t="n"/>
       <c r="T425" s="26" t="n"/>
-      <c r="U425" s="26" t="n"/>
     </row>
     <row r="426">
       <c r="B426" s="26" t="n"/>
@@ -8411,7 +7991,6 @@
       <c r="O426" s="27" t="n"/>
       <c r="Q426" s="27" t="n"/>
       <c r="T426" s="26" t="n"/>
-      <c r="U426" s="26" t="n"/>
     </row>
     <row r="427">
       <c r="B427" s="26" t="n"/>
@@ -8429,7 +8008,6 @@
       <c r="O427" s="27" t="n"/>
       <c r="Q427" s="27" t="n"/>
       <c r="T427" s="26" t="n"/>
-      <c r="U427" s="26" t="n"/>
     </row>
     <row r="428">
       <c r="B428" s="26" t="n"/>
@@ -8447,7 +8025,6 @@
       <c r="O428" s="27" t="n"/>
       <c r="Q428" s="27" t="n"/>
       <c r="T428" s="26" t="n"/>
-      <c r="U428" s="26" t="n"/>
     </row>
     <row r="429">
       <c r="B429" s="26" t="n"/>
@@ -8465,7 +8042,6 @@
       <c r="O429" s="27" t="n"/>
       <c r="Q429" s="27" t="n"/>
       <c r="T429" s="26" t="n"/>
-      <c r="U429" s="26" t="n"/>
     </row>
     <row r="430">
       <c r="B430" s="26" t="n"/>
@@ -8483,7 +8059,6 @@
       <c r="O430" s="27" t="n"/>
       <c r="Q430" s="27" t="n"/>
       <c r="T430" s="26" t="n"/>
-      <c r="U430" s="26" t="n"/>
     </row>
     <row r="431">
       <c r="B431" s="26" t="n"/>
@@ -8501,7 +8076,6 @@
       <c r="O431" s="27" t="n"/>
       <c r="Q431" s="27" t="n"/>
       <c r="T431" s="26" t="n"/>
-      <c r="U431" s="26" t="n"/>
     </row>
     <row r="432">
       <c r="B432" s="26" t="n"/>
@@ -8519,7 +8093,6 @@
       <c r="O432" s="27" t="n"/>
       <c r="Q432" s="27" t="n"/>
       <c r="T432" s="26" t="n"/>
-      <c r="U432" s="26" t="n"/>
     </row>
     <row r="433">
       <c r="B433" s="26" t="n"/>
@@ -8537,7 +8110,6 @@
       <c r="O433" s="27" t="n"/>
       <c r="Q433" s="27" t="n"/>
       <c r="T433" s="26" t="n"/>
-      <c r="U433" s="26" t="n"/>
     </row>
     <row r="434">
       <c r="B434" s="26" t="n"/>
@@ -8555,7 +8127,6 @@
       <c r="O434" s="27" t="n"/>
       <c r="Q434" s="27" t="n"/>
       <c r="T434" s="26" t="n"/>
-      <c r="U434" s="26" t="n"/>
     </row>
     <row r="435">
       <c r="B435" s="26" t="n"/>
@@ -8573,7 +8144,6 @@
       <c r="O435" s="27" t="n"/>
       <c r="Q435" s="27" t="n"/>
       <c r="T435" s="26" t="n"/>
-      <c r="U435" s="26" t="n"/>
     </row>
     <row r="436">
       <c r="B436" s="26" t="n"/>
@@ -8591,7 +8161,6 @@
       <c r="O436" s="27" t="n"/>
       <c r="Q436" s="27" t="n"/>
       <c r="T436" s="26" t="n"/>
-      <c r="U436" s="26" t="n"/>
     </row>
     <row r="437">
       <c r="B437" s="26" t="n"/>
@@ -8609,7 +8178,6 @@
       <c r="O437" s="27" t="n"/>
       <c r="Q437" s="27" t="n"/>
       <c r="T437" s="26" t="n"/>
-      <c r="U437" s="26" t="n"/>
     </row>
     <row r="438">
       <c r="B438" s="26" t="n"/>
@@ -8627,7 +8195,6 @@
       <c r="O438" s="27" t="n"/>
       <c r="Q438" s="27" t="n"/>
       <c r="T438" s="26" t="n"/>
-      <c r="U438" s="26" t="n"/>
     </row>
     <row r="439">
       <c r="B439" s="26" t="n"/>
@@ -8645,7 +8212,6 @@
       <c r="O439" s="27" t="n"/>
       <c r="Q439" s="27" t="n"/>
       <c r="T439" s="26" t="n"/>
-      <c r="U439" s="26" t="n"/>
     </row>
     <row r="440">
       <c r="B440" s="26" t="n"/>
@@ -8663,7 +8229,6 @@
       <c r="O440" s="27" t="n"/>
       <c r="Q440" s="27" t="n"/>
       <c r="T440" s="26" t="n"/>
-      <c r="U440" s="26" t="n"/>
     </row>
     <row r="441">
       <c r="B441" s="26" t="n"/>
@@ -8681,7 +8246,6 @@
       <c r="O441" s="27" t="n"/>
       <c r="Q441" s="27" t="n"/>
       <c r="T441" s="26" t="n"/>
-      <c r="U441" s="26" t="n"/>
     </row>
     <row r="442">
       <c r="B442" s="26" t="n"/>
@@ -8699,7 +8263,6 @@
       <c r="O442" s="27" t="n"/>
       <c r="Q442" s="27" t="n"/>
       <c r="T442" s="26" t="n"/>
-      <c r="U442" s="26" t="n"/>
     </row>
     <row r="443">
       <c r="B443" s="26" t="n"/>
@@ -8717,7 +8280,6 @@
       <c r="O443" s="27" t="n"/>
       <c r="Q443" s="27" t="n"/>
       <c r="T443" s="26" t="n"/>
-      <c r="U443" s="26" t="n"/>
     </row>
     <row r="444">
       <c r="B444" s="26" t="n"/>
@@ -8735,7 +8297,6 @@
       <c r="O444" s="27" t="n"/>
       <c r="Q444" s="27" t="n"/>
       <c r="T444" s="26" t="n"/>
-      <c r="U444" s="26" t="n"/>
     </row>
     <row r="445">
       <c r="B445" s="26" t="n"/>
@@ -8753,7 +8314,6 @@
       <c r="O445" s="27" t="n"/>
       <c r="Q445" s="27" t="n"/>
       <c r="T445" s="26" t="n"/>
-      <c r="U445" s="26" t="n"/>
     </row>
     <row r="446">
       <c r="B446" s="26" t="n"/>
@@ -8771,7 +8331,6 @@
       <c r="O446" s="27" t="n"/>
       <c r="Q446" s="27" t="n"/>
       <c r="T446" s="26" t="n"/>
-      <c r="U446" s="26" t="n"/>
     </row>
     <row r="447">
       <c r="B447" s="26" t="n"/>
@@ -8789,7 +8348,6 @@
       <c r="O447" s="27" t="n"/>
       <c r="Q447" s="27" t="n"/>
       <c r="T447" s="26" t="n"/>
-      <c r="U447" s="26" t="n"/>
     </row>
     <row r="448">
       <c r="B448" s="26" t="n"/>
@@ -8807,7 +8365,6 @@
       <c r="O448" s="27" t="n"/>
       <c r="Q448" s="27" t="n"/>
       <c r="T448" s="26" t="n"/>
-      <c r="U448" s="26" t="n"/>
     </row>
     <row r="449">
       <c r="B449" s="26" t="n"/>
@@ -8825,7 +8382,6 @@
       <c r="O449" s="27" t="n"/>
       <c r="Q449" s="27" t="n"/>
       <c r="T449" s="26" t="n"/>
-      <c r="U449" s="26" t="n"/>
     </row>
     <row r="450">
       <c r="B450" s="26" t="n"/>
@@ -8843,7 +8399,6 @@
       <c r="O450" s="27" t="n"/>
       <c r="Q450" s="27" t="n"/>
       <c r="T450" s="26" t="n"/>
-      <c r="U450" s="26" t="n"/>
     </row>
     <row r="451">
       <c r="B451" s="26" t="n"/>
@@ -8861,7 +8416,6 @@
       <c r="O451" s="27" t="n"/>
       <c r="Q451" s="27" t="n"/>
       <c r="T451" s="26" t="n"/>
-      <c r="U451" s="26" t="n"/>
     </row>
     <row r="452">
       <c r="B452" s="26" t="n"/>
@@ -8879,7 +8433,6 @@
       <c r="O452" s="27" t="n"/>
       <c r="Q452" s="27" t="n"/>
       <c r="T452" s="26" t="n"/>
-      <c r="U452" s="26" t="n"/>
     </row>
     <row r="453">
       <c r="B453" s="26" t="n"/>
@@ -8897,7 +8450,6 @@
       <c r="O453" s="27" t="n"/>
       <c r="Q453" s="27" t="n"/>
       <c r="T453" s="26" t="n"/>
-      <c r="U453" s="26" t="n"/>
     </row>
     <row r="454">
       <c r="B454" s="26" t="n"/>
@@ -8915,7 +8467,6 @@
       <c r="O454" s="27" t="n"/>
       <c r="Q454" s="27" t="n"/>
       <c r="T454" s="26" t="n"/>
-      <c r="U454" s="26" t="n"/>
     </row>
     <row r="455">
       <c r="B455" s="26" t="n"/>
@@ -8933,7 +8484,6 @@
       <c r="O455" s="27" t="n"/>
       <c r="Q455" s="27" t="n"/>
       <c r="T455" s="26" t="n"/>
-      <c r="U455" s="26" t="n"/>
     </row>
     <row r="456">
       <c r="B456" s="26" t="n"/>
@@ -8951,7 +8501,6 @@
       <c r="O456" s="27" t="n"/>
       <c r="Q456" s="27" t="n"/>
       <c r="T456" s="26" t="n"/>
-      <c r="U456" s="26" t="n"/>
     </row>
     <row r="457">
       <c r="B457" s="26" t="n"/>
@@ -8969,7 +8518,6 @@
       <c r="O457" s="27" t="n"/>
       <c r="Q457" s="27" t="n"/>
       <c r="T457" s="26" t="n"/>
-      <c r="U457" s="26" t="n"/>
     </row>
     <row r="458">
       <c r="B458" s="26" t="n"/>
@@ -8987,7 +8535,6 @@
       <c r="O458" s="27" t="n"/>
       <c r="Q458" s="27" t="n"/>
       <c r="T458" s="26" t="n"/>
-      <c r="U458" s="26" t="n"/>
     </row>
     <row r="459">
       <c r="B459" s="26" t="n"/>
@@ -9005,7 +8552,6 @@
       <c r="O459" s="27" t="n"/>
       <c r="Q459" s="27" t="n"/>
       <c r="T459" s="26" t="n"/>
-      <c r="U459" s="26" t="n"/>
     </row>
     <row r="460">
       <c r="B460" s="26" t="n"/>
@@ -9023,7 +8569,6 @@
       <c r="O460" s="27" t="n"/>
       <c r="Q460" s="27" t="n"/>
       <c r="T460" s="26" t="n"/>
-      <c r="U460" s="26" t="n"/>
     </row>
     <row r="461">
       <c r="B461" s="26" t="n"/>
@@ -9041,7 +8586,6 @@
       <c r="O461" s="27" t="n"/>
       <c r="Q461" s="27" t="n"/>
       <c r="T461" s="26" t="n"/>
-      <c r="U461" s="26" t="n"/>
     </row>
     <row r="462">
       <c r="B462" s="26" t="n"/>
@@ -9059,7 +8603,6 @@
       <c r="O462" s="27" t="n"/>
       <c r="Q462" s="27" t="n"/>
       <c r="T462" s="26" t="n"/>
-      <c r="U462" s="26" t="n"/>
     </row>
     <row r="463">
       <c r="B463" s="26" t="n"/>
@@ -9077,7 +8620,6 @@
       <c r="O463" s="27" t="n"/>
       <c r="Q463" s="27" t="n"/>
       <c r="T463" s="26" t="n"/>
-      <c r="U463" s="26" t="n"/>
     </row>
     <row r="464">
       <c r="B464" s="26" t="n"/>
@@ -9095,7 +8637,6 @@
       <c r="O464" s="27" t="n"/>
       <c r="Q464" s="27" t="n"/>
       <c r="T464" s="26" t="n"/>
-      <c r="U464" s="26" t="n"/>
     </row>
     <row r="465">
       <c r="B465" s="26" t="n"/>
@@ -9113,7 +8654,6 @@
       <c r="O465" s="27" t="n"/>
       <c r="Q465" s="27" t="n"/>
       <c r="T465" s="26" t="n"/>
-      <c r="U465" s="26" t="n"/>
     </row>
     <row r="466">
       <c r="B466" s="26" t="n"/>
@@ -9131,7 +8671,6 @@
       <c r="O466" s="27" t="n"/>
       <c r="Q466" s="27" t="n"/>
       <c r="T466" s="26" t="n"/>
-      <c r="U466" s="26" t="n"/>
     </row>
     <row r="467">
       <c r="B467" s="26" t="n"/>
@@ -9149,7 +8688,6 @@
       <c r="O467" s="27" t="n"/>
       <c r="Q467" s="27" t="n"/>
       <c r="T467" s="26" t="n"/>
-      <c r="U467" s="26" t="n"/>
     </row>
     <row r="468">
       <c r="B468" s="26" t="n"/>
@@ -9167,7 +8705,6 @@
       <c r="O468" s="27" t="n"/>
       <c r="Q468" s="27" t="n"/>
       <c r="T468" s="26" t="n"/>
-      <c r="U468" s="26" t="n"/>
     </row>
     <row r="469">
       <c r="B469" s="26" t="n"/>
@@ -9185,7 +8722,6 @@
       <c r="O469" s="27" t="n"/>
       <c r="Q469" s="27" t="n"/>
       <c r="T469" s="26" t="n"/>
-      <c r="U469" s="26" t="n"/>
     </row>
     <row r="470">
       <c r="B470" s="26" t="n"/>
@@ -9203,7 +8739,6 @@
       <c r="O470" s="27" t="n"/>
       <c r="Q470" s="27" t="n"/>
       <c r="T470" s="26" t="n"/>
-      <c r="U470" s="26" t="n"/>
     </row>
     <row r="471">
       <c r="B471" s="26" t="n"/>
@@ -9221,7 +8756,6 @@
       <c r="O471" s="27" t="n"/>
       <c r="Q471" s="27" t="n"/>
       <c r="T471" s="26" t="n"/>
-      <c r="U471" s="26" t="n"/>
     </row>
     <row r="472">
       <c r="B472" s="26" t="n"/>
@@ -9239,7 +8773,6 @@
       <c r="O472" s="27" t="n"/>
       <c r="Q472" s="27" t="n"/>
       <c r="T472" s="26" t="n"/>
-      <c r="U472" s="26" t="n"/>
     </row>
     <row r="473">
       <c r="B473" s="26" t="n"/>
@@ -9257,7 +8790,6 @@
       <c r="O473" s="27" t="n"/>
       <c r="Q473" s="27" t="n"/>
       <c r="T473" s="26" t="n"/>
-      <c r="U473" s="26" t="n"/>
     </row>
     <row r="474">
       <c r="B474" s="26" t="n"/>
@@ -9275,7 +8807,6 @@
       <c r="O474" s="27" t="n"/>
       <c r="Q474" s="27" t="n"/>
       <c r="T474" s="26" t="n"/>
-      <c r="U474" s="26" t="n"/>
     </row>
     <row r="475">
       <c r="B475" s="26" t="n"/>
@@ -9293,7 +8824,6 @@
       <c r="O475" s="27" t="n"/>
       <c r="Q475" s="27" t="n"/>
       <c r="T475" s="26" t="n"/>
-      <c r="U475" s="26" t="n"/>
     </row>
     <row r="476">
       <c r="B476" s="26" t="n"/>
@@ -9311,7 +8841,6 @@
       <c r="O476" s="27" t="n"/>
       <c r="Q476" s="27" t="n"/>
       <c r="T476" s="26" t="n"/>
-      <c r="U476" s="26" t="n"/>
     </row>
     <row r="477">
       <c r="B477" s="26" t="n"/>
@@ -9329,7 +8858,6 @@
       <c r="O477" s="27" t="n"/>
       <c r="Q477" s="27" t="n"/>
       <c r="T477" s="26" t="n"/>
-      <c r="U477" s="26" t="n"/>
     </row>
     <row r="478">
       <c r="B478" s="26" t="n"/>
@@ -9347,7 +8875,6 @@
       <c r="O478" s="27" t="n"/>
       <c r="Q478" s="27" t="n"/>
       <c r="T478" s="26" t="n"/>
-      <c r="U478" s="26" t="n"/>
     </row>
     <row r="479">
       <c r="B479" s="26" t="n"/>
@@ -9365,7 +8892,6 @@
       <c r="O479" s="27" t="n"/>
       <c r="Q479" s="27" t="n"/>
       <c r="T479" s="26" t="n"/>
-      <c r="U479" s="26" t="n"/>
     </row>
     <row r="480">
       <c r="B480" s="26" t="n"/>
@@ -9383,7 +8909,6 @@
       <c r="O480" s="27" t="n"/>
       <c r="Q480" s="27" t="n"/>
       <c r="T480" s="26" t="n"/>
-      <c r="U480" s="26" t="n"/>
     </row>
     <row r="481">
       <c r="B481" s="26" t="n"/>
@@ -9401,7 +8926,6 @@
       <c r="O481" s="27" t="n"/>
       <c r="Q481" s="27" t="n"/>
       <c r="T481" s="26" t="n"/>
-      <c r="U481" s="26" t="n"/>
     </row>
     <row r="482">
       <c r="B482" s="26" t="n"/>
@@ -9419,7 +8943,6 @@
       <c r="O482" s="27" t="n"/>
       <c r="Q482" s="27" t="n"/>
       <c r="T482" s="26" t="n"/>
-      <c r="U482" s="26" t="n"/>
     </row>
     <row r="483">
       <c r="B483" s="26" t="n"/>
@@ -9437,7 +8960,6 @@
       <c r="O483" s="27" t="n"/>
       <c r="Q483" s="27" t="n"/>
       <c r="T483" s="26" t="n"/>
-      <c r="U483" s="26" t="n"/>
     </row>
     <row r="484">
       <c r="B484" s="26" t="n"/>
@@ -9455,7 +8977,6 @@
       <c r="O484" s="27" t="n"/>
       <c r="Q484" s="27" t="n"/>
       <c r="T484" s="26" t="n"/>
-      <c r="U484" s="26" t="n"/>
     </row>
     <row r="485">
       <c r="B485" s="26" t="n"/>
@@ -9473,7 +8994,6 @@
       <c r="O485" s="27" t="n"/>
       <c r="Q485" s="27" t="n"/>
       <c r="T485" s="26" t="n"/>
-      <c r="U485" s="26" t="n"/>
     </row>
     <row r="486">
       <c r="B486" s="26" t="n"/>
@@ -9491,7 +9011,6 @@
       <c r="O486" s="27" t="n"/>
       <c r="Q486" s="27" t="n"/>
       <c r="T486" s="26" t="n"/>
-      <c r="U486" s="26" t="n"/>
     </row>
     <row r="487">
       <c r="B487" s="26" t="n"/>
@@ -9509,7 +9028,6 @@
       <c r="O487" s="27" t="n"/>
       <c r="Q487" s="27" t="n"/>
       <c r="T487" s="26" t="n"/>
-      <c r="U487" s="26" t="n"/>
     </row>
     <row r="488">
       <c r="B488" s="26" t="n"/>
@@ -9527,7 +9045,6 @@
       <c r="O488" s="27" t="n"/>
       <c r="Q488" s="27" t="n"/>
       <c r="T488" s="26" t="n"/>
-      <c r="U488" s="26" t="n"/>
     </row>
     <row r="489">
       <c r="B489" s="26" t="n"/>
@@ -9545,7 +9062,6 @@
       <c r="O489" s="27" t="n"/>
       <c r="Q489" s="27" t="n"/>
       <c r="T489" s="26" t="n"/>
-      <c r="U489" s="26" t="n"/>
     </row>
     <row r="490">
       <c r="B490" s="26" t="n"/>
@@ -9563,7 +9079,6 @@
       <c r="O490" s="27" t="n"/>
       <c r="Q490" s="27" t="n"/>
       <c r="T490" s="26" t="n"/>
-      <c r="U490" s="26" t="n"/>
     </row>
     <row r="491">
       <c r="B491" s="26" t="n"/>
@@ -9581,7 +9096,6 @@
       <c r="O491" s="27" t="n"/>
       <c r="Q491" s="27" t="n"/>
       <c r="T491" s="26" t="n"/>
-      <c r="U491" s="26" t="n"/>
     </row>
     <row r="492">
       <c r="B492" s="26" t="n"/>
@@ -9599,7 +9113,6 @@
       <c r="O492" s="27" t="n"/>
       <c r="Q492" s="27" t="n"/>
       <c r="T492" s="26" t="n"/>
-      <c r="U492" s="26" t="n"/>
     </row>
     <row r="493">
       <c r="B493" s="26" t="n"/>
@@ -9617,7 +9130,6 @@
       <c r="O493" s="27" t="n"/>
       <c r="Q493" s="27" t="n"/>
       <c r="T493" s="26" t="n"/>
-      <c r="U493" s="26" t="n"/>
     </row>
     <row r="494">
       <c r="B494" s="26" t="n"/>
@@ -9635,7 +9147,6 @@
       <c r="O494" s="27" t="n"/>
       <c r="Q494" s="27" t="n"/>
       <c r="T494" s="26" t="n"/>
-      <c r="U494" s="26" t="n"/>
     </row>
     <row r="495">
       <c r="B495" s="26" t="n"/>
@@ -9653,7 +9164,6 @@
       <c r="O495" s="27" t="n"/>
       <c r="Q495" s="27" t="n"/>
       <c r="T495" s="26" t="n"/>
-      <c r="U495" s="26" t="n"/>
     </row>
     <row r="496">
       <c r="B496" s="26" t="n"/>
@@ -9671,7 +9181,6 @@
       <c r="O496" s="27" t="n"/>
       <c r="Q496" s="27" t="n"/>
       <c r="T496" s="26" t="n"/>
-      <c r="U496" s="26" t="n"/>
     </row>
     <row r="497">
       <c r="B497" s="26" t="n"/>
@@ -9689,7 +9198,6 @@
       <c r="O497" s="27" t="n"/>
       <c r="Q497" s="27" t="n"/>
       <c r="T497" s="26" t="n"/>
-      <c r="U497" s="26" t="n"/>
     </row>
     <row r="498">
       <c r="B498" s="26" t="n"/>
@@ -9707,7 +9215,6 @@
       <c r="O498" s="27" t="n"/>
       <c r="Q498" s="27" t="n"/>
       <c r="T498" s="26" t="n"/>
-      <c r="U498" s="26" t="n"/>
     </row>
     <row r="499">
       <c r="B499" s="26" t="n"/>
@@ -9725,7 +9232,6 @@
       <c r="O499" s="27" t="n"/>
       <c r="Q499" s="27" t="n"/>
       <c r="T499" s="26" t="n"/>
-      <c r="U499" s="26" t="n"/>
     </row>
     <row r="500">
       <c r="B500" s="26" t="n"/>
@@ -9743,7 +9249,6 @@
       <c r="O500" s="27" t="n"/>
       <c r="Q500" s="27" t="n"/>
       <c r="T500" s="26" t="n"/>
-      <c r="U500" s="26" t="n"/>
     </row>
     <row r="501">
       <c r="B501" s="26" t="n"/>
@@ -9761,7 +9266,6 @@
       <c r="O501" s="27" t="n"/>
       <c r="Q501" s="27" t="n"/>
       <c r="T501" s="26" t="n"/>
-      <c r="U501" s="26" t="n"/>
     </row>
     <row r="502">
       <c r="B502" s="26" t="n"/>
@@ -9779,7 +9283,6 @@
       <c r="O502" s="27" t="n"/>
       <c r="Q502" s="27" t="n"/>
       <c r="T502" s="26" t="n"/>
-      <c r="U502" s="26" t="n"/>
     </row>
     <row r="503">
       <c r="B503" s="26" t="n"/>
@@ -9797,7 +9300,6 @@
       <c r="O503" s="27" t="n"/>
       <c r="Q503" s="27" t="n"/>
       <c r="T503" s="26" t="n"/>
-      <c r="U503" s="26" t="n"/>
     </row>
     <row r="504">
       <c r="B504" s="26" t="n"/>
@@ -9815,7 +9317,6 @@
       <c r="O504" s="27" t="n"/>
       <c r="Q504" s="27" t="n"/>
       <c r="T504" s="26" t="n"/>
-      <c r="U504" s="26" t="n"/>
     </row>
     <row r="505">
       <c r="B505" s="26" t="n"/>
@@ -9833,7 +9334,6 @@
       <c r="O505" s="27" t="n"/>
       <c r="Q505" s="27" t="n"/>
       <c r="T505" s="26" t="n"/>
-      <c r="U505" s="26" t="n"/>
     </row>
     <row r="506">
       <c r="B506" s="26" t="n"/>
@@ -9851,7 +9351,6 @@
       <c r="O506" s="27" t="n"/>
       <c r="Q506" s="27" t="n"/>
       <c r="T506" s="26" t="n"/>
-      <c r="U506" s="26" t="n"/>
     </row>
     <row r="507">
       <c r="B507" s="26" t="n"/>
@@ -9869,7 +9368,6 @@
       <c r="O507" s="27" t="n"/>
       <c r="Q507" s="27" t="n"/>
       <c r="T507" s="26" t="n"/>
-      <c r="U507" s="26" t="n"/>
     </row>
     <row r="508">
       <c r="B508" s="26" t="n"/>
@@ -9887,7 +9385,6 @@
       <c r="O508" s="27" t="n"/>
       <c r="Q508" s="27" t="n"/>
       <c r="T508" s="26" t="n"/>
-      <c r="U508" s="26" t="n"/>
     </row>
     <row r="509">
       <c r="B509" s="26" t="n"/>
@@ -9905,7 +9402,6 @@
       <c r="O509" s="27" t="n"/>
       <c r="Q509" s="27" t="n"/>
       <c r="T509" s="26" t="n"/>
-      <c r="U509" s="26" t="n"/>
     </row>
     <row r="510">
       <c r="B510" s="26" t="n"/>
@@ -9923,7 +9419,6 @@
       <c r="O510" s="27" t="n"/>
       <c r="Q510" s="27" t="n"/>
       <c r="T510" s="26" t="n"/>
-      <c r="U510" s="26" t="n"/>
     </row>
     <row r="511">
       <c r="B511" s="26" t="n"/>
@@ -9941,7 +9436,6 @@
       <c r="O511" s="27" t="n"/>
       <c r="Q511" s="27" t="n"/>
       <c r="T511" s="26" t="n"/>
-      <c r="U511" s="26" t="n"/>
     </row>
     <row r="512">
       <c r="B512" s="26" t="n"/>
@@ -9959,7 +9453,6 @@
       <c r="O512" s="27" t="n"/>
       <c r="Q512" s="27" t="n"/>
       <c r="T512" s="26" t="n"/>
-      <c r="U512" s="26" t="n"/>
     </row>
     <row r="513">
       <c r="B513" s="26" t="n"/>
@@ -9977,7 +9470,6 @@
       <c r="O513" s="27" t="n"/>
       <c r="Q513" s="27" t="n"/>
       <c r="T513" s="26" t="n"/>
-      <c r="U513" s="26" t="n"/>
     </row>
     <row r="514">
       <c r="B514" s="26" t="n"/>
@@ -9995,7 +9487,6 @@
       <c r="O514" s="27" t="n"/>
       <c r="Q514" s="27" t="n"/>
       <c r="T514" s="26" t="n"/>
-      <c r="U514" s="26" t="n"/>
     </row>
     <row r="515">
       <c r="B515" s="26" t="n"/>
@@ -10013,7 +9504,6 @@
       <c r="O515" s="27" t="n"/>
       <c r="Q515" s="27" t="n"/>
       <c r="T515" s="26" t="n"/>
-      <c r="U515" s="26" t="n"/>
     </row>
     <row r="516">
       <c r="B516" s="26" t="n"/>
@@ -10031,7 +9521,6 @@
       <c r="O516" s="27" t="n"/>
       <c r="Q516" s="27" t="n"/>
       <c r="T516" s="26" t="n"/>
-      <c r="U516" s="26" t="n"/>
     </row>
     <row r="517">
       <c r="B517" s="26" t="n"/>
@@ -10049,7 +9538,6 @@
       <c r="O517" s="27" t="n"/>
       <c r="Q517" s="27" t="n"/>
       <c r="T517" s="26" t="n"/>
-      <c r="U517" s="26" t="n"/>
     </row>
     <row r="518">
       <c r="B518" s="26" t="n"/>
@@ -10067,7 +9555,6 @@
       <c r="O518" s="27" t="n"/>
       <c r="Q518" s="27" t="n"/>
       <c r="T518" s="26" t="n"/>
-      <c r="U518" s="26" t="n"/>
     </row>
     <row r="519">
       <c r="B519" s="26" t="n"/>
@@ -10085,7 +9572,6 @@
       <c r="O519" s="27" t="n"/>
       <c r="Q519" s="27" t="n"/>
       <c r="T519" s="26" t="n"/>
-      <c r="U519" s="26" t="n"/>
     </row>
     <row r="520">
       <c r="B520" s="26" t="n"/>
@@ -10103,7 +9589,6 @@
       <c r="O520" s="27" t="n"/>
       <c r="Q520" s="27" t="n"/>
       <c r="T520" s="26" t="n"/>
-      <c r="U520" s="26" t="n"/>
     </row>
     <row r="521">
       <c r="B521" s="26" t="n"/>
@@ -10121,7 +9606,6 @@
       <c r="O521" s="27" t="n"/>
       <c r="Q521" s="27" t="n"/>
       <c r="T521" s="26" t="n"/>
-      <c r="U521" s="26" t="n"/>
     </row>
     <row r="522">
       <c r="B522" s="26" t="n"/>
@@ -10139,7 +9623,6 @@
       <c r="O522" s="27" t="n"/>
       <c r="Q522" s="27" t="n"/>
       <c r="T522" s="26" t="n"/>
-      <c r="U522" s="26" t="n"/>
     </row>
     <row r="523">
       <c r="B523" s="26" t="n"/>
@@ -10157,7 +9640,6 @@
       <c r="O523" s="27" t="n"/>
       <c r="Q523" s="27" t="n"/>
       <c r="T523" s="26" t="n"/>
-      <c r="U523" s="26" t="n"/>
     </row>
     <row r="524">
       <c r="B524" s="26" t="n"/>
@@ -10175,7 +9657,6 @@
       <c r="O524" s="27" t="n"/>
       <c r="Q524" s="27" t="n"/>
       <c r="T524" s="26" t="n"/>
-      <c r="U524" s="26" t="n"/>
     </row>
     <row r="525">
       <c r="B525" s="26" t="n"/>
@@ -10193,7 +9674,6 @@
       <c r="O525" s="27" t="n"/>
       <c r="Q525" s="27" t="n"/>
       <c r="T525" s="26" t="n"/>
-      <c r="U525" s="26" t="n"/>
     </row>
     <row r="526">
       <c r="B526" s="26" t="n"/>
@@ -10211,7 +9691,6 @@
       <c r="O526" s="27" t="n"/>
       <c r="Q526" s="27" t="n"/>
       <c r="T526" s="26" t="n"/>
-      <c r="U526" s="26" t="n"/>
     </row>
     <row r="527">
       <c r="B527" s="26" t="n"/>
@@ -10229,7 +9708,6 @@
       <c r="O527" s="27" t="n"/>
       <c r="Q527" s="27" t="n"/>
       <c r="T527" s="26" t="n"/>
-      <c r="U527" s="26" t="n"/>
     </row>
     <row r="528">
       <c r="B528" s="26" t="n"/>
@@ -10247,7 +9725,6 @@
       <c r="O528" s="27" t="n"/>
       <c r="Q528" s="27" t="n"/>
       <c r="T528" s="26" t="n"/>
-      <c r="U528" s="26" t="n"/>
     </row>
     <row r="529">
       <c r="B529" s="26" t="n"/>
@@ -10265,7 +9742,6 @@
       <c r="O529" s="27" t="n"/>
       <c r="Q529" s="27" t="n"/>
       <c r="T529" s="26" t="n"/>
-      <c r="U529" s="26" t="n"/>
     </row>
     <row r="530">
       <c r="B530" s="26" t="n"/>
@@ -10283,7 +9759,6 @@
       <c r="O530" s="27" t="n"/>
       <c r="Q530" s="27" t="n"/>
       <c r="T530" s="26" t="n"/>
-      <c r="U530" s="26" t="n"/>
     </row>
     <row r="531">
       <c r="B531" s="26" t="n"/>
@@ -10301,7 +9776,6 @@
       <c r="O531" s="27" t="n"/>
       <c r="Q531" s="27" t="n"/>
       <c r="T531" s="26" t="n"/>
-      <c r="U531" s="26" t="n"/>
     </row>
     <row r="532">
       <c r="B532" s="26" t="n"/>
@@ -10319,7 +9793,6 @@
       <c r="O532" s="27" t="n"/>
       <c r="Q532" s="27" t="n"/>
       <c r="T532" s="26" t="n"/>
-      <c r="U532" s="26" t="n"/>
     </row>
     <row r="533">
       <c r="B533" s="26" t="n"/>
@@ -10337,7 +9810,6 @@
       <c r="O533" s="27" t="n"/>
       <c r="Q533" s="27" t="n"/>
       <c r="T533" s="26" t="n"/>
-      <c r="U533" s="26" t="n"/>
     </row>
     <row r="534">
       <c r="B534" s="26" t="n"/>
@@ -10355,7 +9827,6 @@
       <c r="O534" s="27" t="n"/>
       <c r="Q534" s="27" t="n"/>
       <c r="T534" s="26" t="n"/>
-      <c r="U534" s="26" t="n"/>
     </row>
     <row r="535">
       <c r="B535" s="26" t="n"/>
@@ -10373,7 +9844,6 @@
       <c r="O535" s="27" t="n"/>
       <c r="Q535" s="27" t="n"/>
       <c r="T535" s="26" t="n"/>
-      <c r="U535" s="26" t="n"/>
     </row>
     <row r="536">
       <c r="B536" s="26" t="n"/>
@@ -10391,7 +9861,6 @@
       <c r="O536" s="27" t="n"/>
       <c r="Q536" s="27" t="n"/>
       <c r="T536" s="26" t="n"/>
-      <c r="U536" s="26" t="n"/>
     </row>
     <row r="537">
       <c r="B537" s="26" t="n"/>
@@ -10409,7 +9878,6 @@
       <c r="O537" s="27" t="n"/>
       <c r="Q537" s="27" t="n"/>
       <c r="T537" s="26" t="n"/>
-      <c r="U537" s="26" t="n"/>
     </row>
     <row r="538">
       <c r="B538" s="26" t="n"/>
@@ -10427,7 +9895,6 @@
       <c r="O538" s="27" t="n"/>
       <c r="Q538" s="27" t="n"/>
       <c r="T538" s="26" t="n"/>
-      <c r="U538" s="26" t="n"/>
     </row>
     <row r="539">
       <c r="B539" s="26" t="n"/>
@@ -10445,7 +9912,6 @@
       <c r="O539" s="27" t="n"/>
       <c r="Q539" s="27" t="n"/>
       <c r="T539" s="26" t="n"/>
-      <c r="U539" s="26" t="n"/>
     </row>
     <row r="540">
       <c r="B540" s="26" t="n"/>
@@ -10463,7 +9929,6 @@
       <c r="O540" s="27" t="n"/>
       <c r="Q540" s="27" t="n"/>
       <c r="T540" s="26" t="n"/>
-      <c r="U540" s="26" t="n"/>
     </row>
     <row r="541">
       <c r="B541" s="26" t="n"/>
@@ -10481,7 +9946,6 @@
       <c r="O541" s="27" t="n"/>
       <c r="Q541" s="27" t="n"/>
       <c r="T541" s="26" t="n"/>
-      <c r="U541" s="26" t="n"/>
     </row>
     <row r="542">
       <c r="B542" s="26" t="n"/>
@@ -10499,7 +9963,6 @@
       <c r="O542" s="27" t="n"/>
       <c r="Q542" s="27" t="n"/>
       <c r="T542" s="26" t="n"/>
-      <c r="U542" s="26" t="n"/>
     </row>
     <row r="543">
       <c r="B543" s="26" t="n"/>
@@ -10517,7 +9980,6 @@
       <c r="O543" s="27" t="n"/>
       <c r="Q543" s="27" t="n"/>
       <c r="T543" s="26" t="n"/>
-      <c r="U543" s="26" t="n"/>
     </row>
     <row r="544">
       <c r="B544" s="26" t="n"/>
@@ -10535,7 +9997,6 @@
       <c r="O544" s="27" t="n"/>
       <c r="Q544" s="27" t="n"/>
       <c r="T544" s="26" t="n"/>
-      <c r="U544" s="26" t="n"/>
     </row>
     <row r="545">
       <c r="B545" s="26" t="n"/>
@@ -10553,7 +10014,6 @@
       <c r="O545" s="27" t="n"/>
       <c r="Q545" s="27" t="n"/>
       <c r="T545" s="26" t="n"/>
-      <c r="U545" s="26" t="n"/>
     </row>
     <row r="546">
       <c r="B546" s="26" t="n"/>
@@ -10571,7 +10031,6 @@
       <c r="O546" s="27" t="n"/>
       <c r="Q546" s="27" t="n"/>
       <c r="T546" s="26" t="n"/>
-      <c r="U546" s="26" t="n"/>
     </row>
     <row r="547">
       <c r="B547" s="26" t="n"/>
@@ -10589,7 +10048,6 @@
       <c r="O547" s="27" t="n"/>
       <c r="Q547" s="27" t="n"/>
       <c r="T547" s="26" t="n"/>
-      <c r="U547" s="26" t="n"/>
     </row>
     <row r="548">
       <c r="B548" s="26" t="n"/>
@@ -10607,7 +10065,6 @@
       <c r="O548" s="27" t="n"/>
       <c r="Q548" s="27" t="n"/>
       <c r="T548" s="26" t="n"/>
-      <c r="U548" s="26" t="n"/>
     </row>
     <row r="549">
       <c r="B549" s="26" t="n"/>
@@ -10625,7 +10082,6 @@
       <c r="O549" s="27" t="n"/>
       <c r="Q549" s="27" t="n"/>
       <c r="T549" s="26" t="n"/>
-      <c r="U549" s="26" t="n"/>
     </row>
     <row r="550">
       <c r="B550" s="26" t="n"/>
@@ -10643,7 +10099,6 @@
       <c r="O550" s="27" t="n"/>
       <c r="Q550" s="27" t="n"/>
       <c r="T550" s="26" t="n"/>
-      <c r="U550" s="26" t="n"/>
     </row>
     <row r="551">
       <c r="B551" s="26" t="n"/>
@@ -10661,7 +10116,6 @@
       <c r="O551" s="27" t="n"/>
       <c r="Q551" s="27" t="n"/>
       <c r="T551" s="26" t="n"/>
-      <c r="U551" s="26" t="n"/>
     </row>
     <row r="552">
       <c r="B552" s="26" t="n"/>
@@ -10679,7 +10133,6 @@
       <c r="O552" s="27" t="n"/>
       <c r="Q552" s="27" t="n"/>
       <c r="T552" s="26" t="n"/>
-      <c r="U552" s="26" t="n"/>
     </row>
     <row r="553">
       <c r="B553" s="26" t="n"/>
@@ -10697,7 +10150,6 @@
       <c r="O553" s="27" t="n"/>
       <c r="Q553" s="27" t="n"/>
       <c r="T553" s="26" t="n"/>
-      <c r="U553" s="26" t="n"/>
     </row>
     <row r="554">
       <c r="B554" s="26" t="n"/>
@@ -10715,7 +10167,6 @@
       <c r="O554" s="27" t="n"/>
       <c r="Q554" s="27" t="n"/>
       <c r="T554" s="26" t="n"/>
-      <c r="U554" s="26" t="n"/>
     </row>
     <row r="555">
       <c r="B555" s="26" t="n"/>
@@ -10733,7 +10184,6 @@
       <c r="O555" s="27" t="n"/>
       <c r="Q555" s="27" t="n"/>
       <c r="T555" s="26" t="n"/>
-      <c r="U555" s="26" t="n"/>
     </row>
     <row r="556">
       <c r="B556" s="26" t="n"/>
@@ -10751,7 +10201,6 @@
       <c r="O556" s="27" t="n"/>
       <c r="Q556" s="27" t="n"/>
       <c r="T556" s="26" t="n"/>
-      <c r="U556" s="26" t="n"/>
     </row>
     <row r="557">
       <c r="B557" s="26" t="n"/>
@@ -10769,7 +10218,6 @@
       <c r="O557" s="27" t="n"/>
       <c r="Q557" s="27" t="n"/>
       <c r="T557" s="26" t="n"/>
-      <c r="U557" s="26" t="n"/>
     </row>
     <row r="558">
       <c r="B558" s="26" t="n"/>
@@ -10787,7 +10235,6 @@
       <c r="O558" s="27" t="n"/>
       <c r="Q558" s="27" t="n"/>
       <c r="T558" s="26" t="n"/>
-      <c r="U558" s="26" t="n"/>
     </row>
     <row r="559">
       <c r="B559" s="26" t="n"/>
@@ -10805,7 +10252,6 @@
       <c r="O559" s="27" t="n"/>
       <c r="Q559" s="27" t="n"/>
       <c r="T559" s="26" t="n"/>
-      <c r="U559" s="26" t="n"/>
     </row>
     <row r="560">
       <c r="B560" s="26" t="n"/>
@@ -10823,7 +10269,6 @@
       <c r="O560" s="27" t="n"/>
       <c r="Q560" s="27" t="n"/>
       <c r="T560" s="26" t="n"/>
-      <c r="U560" s="26" t="n"/>
     </row>
     <row r="561">
       <c r="B561" s="26" t="n"/>
@@ -10841,7 +10286,6 @@
       <c r="O561" s="27" t="n"/>
       <c r="Q561" s="27" t="n"/>
       <c r="T561" s="26" t="n"/>
-      <c r="U561" s="26" t="n"/>
     </row>
     <row r="562">
       <c r="B562" s="26" t="n"/>
@@ -10859,7 +10303,6 @@
       <c r="O562" s="27" t="n"/>
       <c r="Q562" s="27" t="n"/>
       <c r="T562" s="26" t="n"/>
-      <c r="U562" s="26" t="n"/>
     </row>
     <row r="563">
       <c r="B563" s="26" t="n"/>
@@ -10877,7 +10320,6 @@
       <c r="O563" s="27" t="n"/>
       <c r="Q563" s="27" t="n"/>
       <c r="T563" s="26" t="n"/>
-      <c r="U563" s="26" t="n"/>
     </row>
     <row r="564">
       <c r="B564" s="26" t="n"/>
@@ -10895,7 +10337,6 @@
       <c r="O564" s="27" t="n"/>
       <c r="Q564" s="27" t="n"/>
       <c r="T564" s="26" t="n"/>
-      <c r="U564" s="26" t="n"/>
     </row>
     <row r="565">
       <c r="B565" s="26" t="n"/>
@@ -10913,7 +10354,6 @@
       <c r="O565" s="27" t="n"/>
       <c r="Q565" s="27" t="n"/>
       <c r="T565" s="26" t="n"/>
-      <c r="U565" s="26" t="n"/>
     </row>
     <row r="566">
       <c r="B566" s="26" t="n"/>
@@ -10931,7 +10371,6 @@
       <c r="O566" s="27" t="n"/>
       <c r="Q566" s="27" t="n"/>
       <c r="T566" s="26" t="n"/>
-      <c r="U566" s="26" t="n"/>
     </row>
     <row r="567">
       <c r="B567" s="26" t="n"/>
@@ -10949,7 +10388,6 @@
       <c r="O567" s="27" t="n"/>
       <c r="Q567" s="27" t="n"/>
       <c r="T567" s="26" t="n"/>
-      <c r="U567" s="26" t="n"/>
     </row>
     <row r="568">
       <c r="B568" s="26" t="n"/>
@@ -10967,7 +10405,6 @@
       <c r="O568" s="27" t="n"/>
       <c r="Q568" s="27" t="n"/>
       <c r="T568" s="26" t="n"/>
-      <c r="U568" s="26" t="n"/>
     </row>
     <row r="569">
       <c r="B569" s="26" t="n"/>
@@ -10985,7 +10422,6 @@
       <c r="O569" s="27" t="n"/>
       <c r="Q569" s="27" t="n"/>
       <c r="T569" s="26" t="n"/>
-      <c r="U569" s="26" t="n"/>
     </row>
     <row r="570">
       <c r="B570" s="26" t="n"/>
@@ -11003,7 +10439,6 @@
       <c r="O570" s="27" t="n"/>
       <c r="Q570" s="27" t="n"/>
       <c r="T570" s="26" t="n"/>
-      <c r="U570" s="26" t="n"/>
     </row>
     <row r="571">
       <c r="B571" s="26" t="n"/>
@@ -11021,7 +10456,6 @@
       <c r="O571" s="27" t="n"/>
       <c r="Q571" s="27" t="n"/>
       <c r="T571" s="26" t="n"/>
-      <c r="U571" s="26" t="n"/>
     </row>
     <row r="572">
       <c r="B572" s="26" t="n"/>
@@ -11039,7 +10473,6 @@
       <c r="O572" s="27" t="n"/>
       <c r="Q572" s="27" t="n"/>
       <c r="T572" s="26" t="n"/>
-      <c r="U572" s="26" t="n"/>
     </row>
     <row r="573">
       <c r="B573" s="26" t="n"/>
@@ -11057,7 +10490,6 @@
       <c r="O573" s="27" t="n"/>
       <c r="Q573" s="27" t="n"/>
       <c r="T573" s="26" t="n"/>
-      <c r="U573" s="26" t="n"/>
     </row>
     <row r="574">
       <c r="B574" s="26" t="n"/>
@@ -11075,7 +10507,6 @@
       <c r="O574" s="27" t="n"/>
       <c r="Q574" s="27" t="n"/>
       <c r="T574" s="26" t="n"/>
-      <c r="U574" s="26" t="n"/>
     </row>
     <row r="575">
       <c r="B575" s="26" t="n"/>
@@ -11093,7 +10524,6 @@
       <c r="O575" s="27" t="n"/>
       <c r="Q575" s="27" t="n"/>
       <c r="T575" s="26" t="n"/>
-      <c r="U575" s="26" t="n"/>
     </row>
     <row r="576">
       <c r="B576" s="26" t="n"/>
@@ -11111,7 +10541,6 @@
       <c r="O576" s="27" t="n"/>
       <c r="Q576" s="27" t="n"/>
       <c r="T576" s="26" t="n"/>
-      <c r="U576" s="26" t="n"/>
     </row>
     <row r="577">
       <c r="B577" s="26" t="n"/>
@@ -11129,7 +10558,6 @@
       <c r="O577" s="27" t="n"/>
       <c r="Q577" s="27" t="n"/>
       <c r="T577" s="26" t="n"/>
-      <c r="U577" s="26" t="n"/>
     </row>
     <row r="578">
       <c r="B578" s="26" t="n"/>
@@ -11147,7 +10575,6 @@
       <c r="O578" s="27" t="n"/>
       <c r="Q578" s="27" t="n"/>
       <c r="T578" s="26" t="n"/>
-      <c r="U578" s="26" t="n"/>
     </row>
     <row r="579">
       <c r="B579" s="26" t="n"/>
@@ -11165,7 +10592,6 @@
       <c r="O579" s="27" t="n"/>
       <c r="Q579" s="27" t="n"/>
       <c r="T579" s="26" t="n"/>
-      <c r="U579" s="26" t="n"/>
     </row>
     <row r="580">
       <c r="B580" s="26" t="n"/>
@@ -11183,7 +10609,6 @@
       <c r="O580" s="27" t="n"/>
       <c r="Q580" s="27" t="n"/>
       <c r="T580" s="26" t="n"/>
-      <c r="U580" s="26" t="n"/>
     </row>
     <row r="581">
       <c r="B581" s="26" t="n"/>
@@ -11201,7 +10626,6 @@
       <c r="O581" s="27" t="n"/>
       <c r="Q581" s="27" t="n"/>
       <c r="T581" s="26" t="n"/>
-      <c r="U581" s="26" t="n"/>
     </row>
     <row r="582">
       <c r="B582" s="26" t="n"/>
@@ -11219,7 +10643,6 @@
       <c r="O582" s="27" t="n"/>
       <c r="Q582" s="27" t="n"/>
       <c r="T582" s="26" t="n"/>
-      <c r="U582" s="26" t="n"/>
     </row>
     <row r="583">
       <c r="B583" s="26" t="n"/>
@@ -11237,7 +10660,6 @@
       <c r="O583" s="27" t="n"/>
       <c r="Q583" s="27" t="n"/>
       <c r="T583" s="26" t="n"/>
-      <c r="U583" s="26" t="n"/>
     </row>
     <row r="584">
       <c r="B584" s="26" t="n"/>
@@ -11255,7 +10677,6 @@
       <c r="O584" s="27" t="n"/>
       <c r="Q584" s="27" t="n"/>
       <c r="T584" s="26" t="n"/>
-      <c r="U584" s="26" t="n"/>
     </row>
     <row r="585">
       <c r="B585" s="26" t="n"/>
@@ -11273,7 +10694,6 @@
       <c r="O585" s="27" t="n"/>
       <c r="Q585" s="27" t="n"/>
       <c r="T585" s="26" t="n"/>
-      <c r="U585" s="26" t="n"/>
     </row>
     <row r="586">
       <c r="B586" s="26" t="n"/>
@@ -11291,7 +10711,6 @@
       <c r="O586" s="27" t="n"/>
       <c r="Q586" s="27" t="n"/>
       <c r="T586" s="26" t="n"/>
-      <c r="U586" s="26" t="n"/>
     </row>
     <row r="587">
       <c r="B587" s="26" t="n"/>
@@ -11309,7 +10728,6 @@
       <c r="O587" s="27" t="n"/>
       <c r="Q587" s="27" t="n"/>
       <c r="T587" s="26" t="n"/>
-      <c r="U587" s="26" t="n"/>
     </row>
     <row r="588">
       <c r="B588" s="26" t="n"/>
@@ -11327,7 +10745,6 @@
       <c r="O588" s="27" t="n"/>
       <c r="Q588" s="27" t="n"/>
       <c r="T588" s="26" t="n"/>
-      <c r="U588" s="26" t="n"/>
     </row>
     <row r="589">
       <c r="B589" s="26" t="n"/>
@@ -11345,7 +10762,6 @@
       <c r="O589" s="27" t="n"/>
       <c r="Q589" s="27" t="n"/>
       <c r="T589" s="26" t="n"/>
-      <c r="U589" s="26" t="n"/>
     </row>
     <row r="590">
       <c r="B590" s="26" t="n"/>
@@ -11363,7 +10779,6 @@
       <c r="O590" s="27" t="n"/>
       <c r="Q590" s="27" t="n"/>
       <c r="T590" s="26" t="n"/>
-      <c r="U590" s="26" t="n"/>
     </row>
     <row r="591">
       <c r="B591" s="26" t="n"/>
@@ -11381,7 +10796,6 @@
       <c r="O591" s="27" t="n"/>
       <c r="Q591" s="27" t="n"/>
       <c r="T591" s="26" t="n"/>
-      <c r="U591" s="26" t="n"/>
     </row>
     <row r="592">
       <c r="B592" s="26" t="n"/>
@@ -11399,7 +10813,6 @@
       <c r="O592" s="27" t="n"/>
       <c r="Q592" s="27" t="n"/>
       <c r="T592" s="26" t="n"/>
-      <c r="U592" s="26" t="n"/>
     </row>
     <row r="593">
       <c r="B593" s="26" t="n"/>
@@ -11417,7 +10830,6 @@
       <c r="O593" s="27" t="n"/>
       <c r="Q593" s="27" t="n"/>
       <c r="T593" s="26" t="n"/>
-      <c r="U593" s="26" t="n"/>
     </row>
     <row r="594">
       <c r="B594" s="26" t="n"/>
@@ -11435,7 +10847,6 @@
       <c r="O594" s="27" t="n"/>
       <c r="Q594" s="27" t="n"/>
       <c r="T594" s="26" t="n"/>
-      <c r="U594" s="26" t="n"/>
     </row>
     <row r="595">
       <c r="B595" s="26" t="n"/>
@@ -11453,7 +10864,6 @@
       <c r="O595" s="27" t="n"/>
       <c r="Q595" s="27" t="n"/>
       <c r="T595" s="26" t="n"/>
-      <c r="U595" s="26" t="n"/>
     </row>
     <row r="596">
       <c r="B596" s="26" t="n"/>
@@ -11471,7 +10881,6 @@
       <c r="O596" s="27" t="n"/>
       <c r="Q596" s="27" t="n"/>
       <c r="T596" s="26" t="n"/>
-      <c r="U596" s="26" t="n"/>
     </row>
     <row r="597">
       <c r="B597" s="26" t="n"/>
@@ -11489,7 +10898,6 @@
       <c r="O597" s="27" t="n"/>
       <c r="Q597" s="27" t="n"/>
       <c r="T597" s="26" t="n"/>
-      <c r="U597" s="26" t="n"/>
     </row>
     <row r="598">
       <c r="B598" s="26" t="n"/>
@@ -11507,7 +10915,6 @@
       <c r="O598" s="27" t="n"/>
       <c r="Q598" s="27" t="n"/>
       <c r="T598" s="26" t="n"/>
-      <c r="U598" s="26" t="n"/>
     </row>
     <row r="599">
       <c r="B599" s="26" t="n"/>
@@ -11525,7 +10932,6 @@
       <c r="O599" s="27" t="n"/>
       <c r="Q599" s="27" t="n"/>
       <c r="T599" s="26" t="n"/>
-      <c r="U599" s="26" t="n"/>
     </row>
     <row r="600">
       <c r="B600" s="26" t="n"/>
@@ -11543,7 +10949,6 @@
       <c r="O600" s="27" t="n"/>
       <c r="Q600" s="27" t="n"/>
       <c r="T600" s="26" t="n"/>
-      <c r="U600" s="26" t="n"/>
     </row>
     <row r="601">
       <c r="B601" s="26" t="n"/>
@@ -11561,7 +10966,6 @@
       <c r="O601" s="27" t="n"/>
       <c r="Q601" s="27" t="n"/>
       <c r="T601" s="26" t="n"/>
-      <c r="U601" s="26" t="n"/>
     </row>
     <row r="602">
       <c r="B602" s="26" t="n"/>
@@ -11579,7 +10983,6 @@
       <c r="O602" s="27" t="n"/>
       <c r="Q602" s="27" t="n"/>
       <c r="T602" s="26" t="n"/>
-      <c r="U602" s="26" t="n"/>
     </row>
     <row r="603">
       <c r="B603" s="26" t="n"/>
@@ -11597,7 +11000,6 @@
       <c r="O603" s="27" t="n"/>
       <c r="Q603" s="27" t="n"/>
       <c r="T603" s="26" t="n"/>
-      <c r="U603" s="26" t="n"/>
     </row>
     <row r="604">
       <c r="B604" s="26" t="n"/>
@@ -11615,7 +11017,6 @@
       <c r="O604" s="27" t="n"/>
       <c r="Q604" s="27" t="n"/>
       <c r="T604" s="26" t="n"/>
-      <c r="U604" s="26" t="n"/>
     </row>
     <row r="605">
       <c r="B605" s="26" t="n"/>
@@ -11633,7 +11034,6 @@
       <c r="O605" s="27" t="n"/>
       <c r="Q605" s="27" t="n"/>
       <c r="T605" s="26" t="n"/>
-      <c r="U605" s="26" t="n"/>
     </row>
     <row r="606">
       <c r="B606" s="26" t="n"/>
@@ -11651,7 +11051,6 @@
       <c r="O606" s="27" t="n"/>
       <c r="Q606" s="27" t="n"/>
       <c r="T606" s="26" t="n"/>
-      <c r="U606" s="26" t="n"/>
     </row>
     <row r="607">
       <c r="B607" s="26" t="n"/>
@@ -11669,7 +11068,6 @@
       <c r="O607" s="27" t="n"/>
       <c r="Q607" s="27" t="n"/>
       <c r="T607" s="26" t="n"/>
-      <c r="U607" s="26" t="n"/>
     </row>
     <row r="608">
       <c r="B608" s="26" t="n"/>
@@ -11687,7 +11085,6 @@
       <c r="O608" s="27" t="n"/>
       <c r="Q608" s="27" t="n"/>
       <c r="T608" s="26" t="n"/>
-      <c r="U608" s="26" t="n"/>
     </row>
     <row r="609">
       <c r="B609" s="26" t="n"/>
@@ -11705,7 +11102,6 @@
       <c r="O609" s="27" t="n"/>
       <c r="Q609" s="27" t="n"/>
       <c r="T609" s="26" t="n"/>
-      <c r="U609" s="26" t="n"/>
     </row>
     <row r="610">
       <c r="B610" s="26" t="n"/>
@@ -11723,7 +11119,6 @@
       <c r="O610" s="27" t="n"/>
       <c r="Q610" s="27" t="n"/>
       <c r="T610" s="26" t="n"/>
-      <c r="U610" s="26" t="n"/>
     </row>
     <row r="611">
       <c r="B611" s="26" t="n"/>
@@ -11741,7 +11136,6 @@
       <c r="O611" s="27" t="n"/>
       <c r="Q611" s="27" t="n"/>
       <c r="T611" s="26" t="n"/>
-      <c r="U611" s="26" t="n"/>
     </row>
     <row r="612">
       <c r="B612" s="26" t="n"/>
@@ -11759,7 +11153,6 @@
       <c r="O612" s="27" t="n"/>
       <c r="Q612" s="27" t="n"/>
       <c r="T612" s="26" t="n"/>
-      <c r="U612" s="26" t="n"/>
     </row>
     <row r="613">
       <c r="B613" s="26" t="n"/>
@@ -11777,7 +11170,6 @@
       <c r="O613" s="27" t="n"/>
       <c r="Q613" s="27" t="n"/>
       <c r="T613" s="26" t="n"/>
-      <c r="U613" s="26" t="n"/>
     </row>
     <row r="614">
       <c r="B614" s="26" t="n"/>
@@ -11795,7 +11187,6 @@
       <c r="O614" s="27" t="n"/>
       <c r="Q614" s="27" t="n"/>
       <c r="T614" s="26" t="n"/>
-      <c r="U614" s="26" t="n"/>
     </row>
     <row r="615">
       <c r="B615" s="26" t="n"/>
@@ -11813,7 +11204,6 @@
       <c r="O615" s="27" t="n"/>
       <c r="Q615" s="27" t="n"/>
       <c r="T615" s="26" t="n"/>
-      <c r="U615" s="26" t="n"/>
     </row>
     <row r="616">
       <c r="B616" s="26" t="n"/>
@@ -11831,7 +11221,6 @@
       <c r="O616" s="27" t="n"/>
       <c r="Q616" s="27" t="n"/>
       <c r="T616" s="26" t="n"/>
-      <c r="U616" s="26" t="n"/>
     </row>
     <row r="617">
       <c r="B617" s="26" t="n"/>
@@ -11849,7 +11238,6 @@
       <c r="O617" s="27" t="n"/>
       <c r="Q617" s="27" t="n"/>
       <c r="T617" s="26" t="n"/>
-      <c r="U617" s="26" t="n"/>
     </row>
     <row r="618">
       <c r="B618" s="26" t="n"/>
@@ -11867,7 +11255,6 @@
       <c r="O618" s="27" t="n"/>
       <c r="Q618" s="27" t="n"/>
       <c r="T618" s="26" t="n"/>
-      <c r="U618" s="26" t="n"/>
     </row>
     <row r="619">
       <c r="B619" s="26" t="n"/>
@@ -11885,7 +11272,6 @@
       <c r="O619" s="27" t="n"/>
       <c r="Q619" s="27" t="n"/>
       <c r="T619" s="26" t="n"/>
-      <c r="U619" s="26" t="n"/>
     </row>
     <row r="620">
       <c r="B620" s="26" t="n"/>
@@ -11903,7 +11289,6 @@
       <c r="O620" s="27" t="n"/>
       <c r="Q620" s="27" t="n"/>
       <c r="T620" s="26" t="n"/>
-      <c r="U620" s="26" t="n"/>
     </row>
     <row r="621">
       <c r="B621" s="26" t="n"/>
@@ -11921,7 +11306,6 @@
       <c r="O621" s="27" t="n"/>
       <c r="Q621" s="27" t="n"/>
       <c r="T621" s="26" t="n"/>
-      <c r="U621" s="26" t="n"/>
     </row>
     <row r="622">
       <c r="B622" s="26" t="n"/>
@@ -11939,7 +11323,6 @@
       <c r="O622" s="27" t="n"/>
       <c r="Q622" s="27" t="n"/>
       <c r="T622" s="26" t="n"/>
-      <c r="U622" s="26" t="n"/>
     </row>
     <row r="623">
       <c r="B623" s="26" t="n"/>
@@ -11957,7 +11340,6 @@
       <c r="O623" s="27" t="n"/>
       <c r="Q623" s="27" t="n"/>
       <c r="T623" s="26" t="n"/>
-      <c r="U623" s="26" t="n"/>
     </row>
     <row r="624">
       <c r="B624" s="26" t="n"/>
@@ -11975,7 +11357,6 @@
       <c r="O624" s="27" t="n"/>
       <c r="Q624" s="27" t="n"/>
       <c r="T624" s="26" t="n"/>
-      <c r="U624" s="26" t="n"/>
     </row>
     <row r="625">
       <c r="B625" s="26" t="n"/>
@@ -11993,7 +11374,6 @@
       <c r="O625" s="27" t="n"/>
       <c r="Q625" s="27" t="n"/>
       <c r="T625" s="26" t="n"/>
-      <c r="U625" s="26" t="n"/>
     </row>
     <row r="626">
       <c r="B626" s="26" t="n"/>
@@ -12011,7 +11391,6 @@
       <c r="O626" s="27" t="n"/>
       <c r="Q626" s="27" t="n"/>
       <c r="T626" s="26" t="n"/>
-      <c r="U626" s="26" t="n"/>
     </row>
     <row r="627">
       <c r="B627" s="26" t="n"/>
@@ -12029,7 +11408,6 @@
       <c r="O627" s="27" t="n"/>
       <c r="Q627" s="27" t="n"/>
       <c r="T627" s="26" t="n"/>
-      <c r="U627" s="26" t="n"/>
     </row>
     <row r="628">
       <c r="B628" s="26" t="n"/>
@@ -12047,7 +11425,6 @@
       <c r="O628" s="27" t="n"/>
       <c r="Q628" s="27" t="n"/>
       <c r="T628" s="26" t="n"/>
-      <c r="U628" s="26" t="n"/>
     </row>
     <row r="629">
       <c r="B629" s="26" t="n"/>
@@ -12065,7 +11442,6 @@
       <c r="O629" s="27" t="n"/>
       <c r="Q629" s="27" t="n"/>
       <c r="T629" s="26" t="n"/>
-      <c r="U629" s="26" t="n"/>
     </row>
     <row r="630">
       <c r="B630" s="26" t="n"/>
@@ -12083,7 +11459,6 @@
       <c r="O630" s="27" t="n"/>
       <c r="Q630" s="27" t="n"/>
       <c r="T630" s="26" t="n"/>
-      <c r="U630" s="26" t="n"/>
     </row>
     <row r="631">
       <c r="B631" s="26" t="n"/>
@@ -12101,7 +11476,6 @@
       <c r="O631" s="27" t="n"/>
       <c r="Q631" s="27" t="n"/>
       <c r="T631" s="26" t="n"/>
-      <c r="U631" s="26" t="n"/>
     </row>
     <row r="632">
       <c r="B632" s="26" t="n"/>
@@ -12119,7 +11493,6 @@
       <c r="O632" s="27" t="n"/>
       <c r="Q632" s="27" t="n"/>
       <c r="T632" s="26" t="n"/>
-      <c r="U632" s="26" t="n"/>
     </row>
     <row r="633">
       <c r="B633" s="26" t="n"/>
@@ -12137,7 +11510,6 @@
       <c r="O633" s="27" t="n"/>
       <c r="Q633" s="27" t="n"/>
       <c r="T633" s="26" t="n"/>
-      <c r="U633" s="26" t="n"/>
     </row>
     <row r="634">
       <c r="B634" s="26" t="n"/>
@@ -12155,7 +11527,6 @@
       <c r="O634" s="27" t="n"/>
       <c r="Q634" s="27" t="n"/>
       <c r="T634" s="26" t="n"/>
-      <c r="U634" s="26" t="n"/>
     </row>
     <row r="635">
       <c r="B635" s="26" t="n"/>
@@ -12173,7 +11544,6 @@
       <c r="O635" s="27" t="n"/>
       <c r="Q635" s="27" t="n"/>
       <c r="T635" s="26" t="n"/>
-      <c r="U635" s="26" t="n"/>
     </row>
     <row r="636">
       <c r="B636" s="26" t="n"/>
@@ -12191,7 +11561,6 @@
       <c r="O636" s="27" t="n"/>
       <c r="Q636" s="27" t="n"/>
       <c r="T636" s="26" t="n"/>
-      <c r="U636" s="26" t="n"/>
     </row>
     <row r="637">
       <c r="B637" s="26" t="n"/>
@@ -12209,7 +11578,6 @@
       <c r="O637" s="27" t="n"/>
       <c r="Q637" s="27" t="n"/>
       <c r="T637" s="26" t="n"/>
-      <c r="U637" s="26" t="n"/>
     </row>
     <row r="638">
       <c r="B638" s="26" t="n"/>
@@ -12227,7 +11595,6 @@
       <c r="O638" s="27" t="n"/>
       <c r="Q638" s="27" t="n"/>
       <c r="T638" s="26" t="n"/>
-      <c r="U638" s="26" t="n"/>
     </row>
     <row r="639">
       <c r="B639" s="26" t="n"/>
@@ -12245,7 +11612,6 @@
       <c r="O639" s="27" t="n"/>
       <c r="Q639" s="27" t="n"/>
       <c r="T639" s="26" t="n"/>
-      <c r="U639" s="26" t="n"/>
     </row>
     <row r="640">
       <c r="B640" s="26" t="n"/>
@@ -12263,7 +11629,6 @@
       <c r="O640" s="27" t="n"/>
       <c r="Q640" s="27" t="n"/>
       <c r="T640" s="26" t="n"/>
-      <c r="U640" s="26" t="n"/>
     </row>
     <row r="641">
       <c r="B641" s="26" t="n"/>
@@ -12281,7 +11646,6 @@
       <c r="O641" s="27" t="n"/>
       <c r="Q641" s="27" t="n"/>
       <c r="T641" s="26" t="n"/>
-      <c r="U641" s="26" t="n"/>
     </row>
     <row r="642">
       <c r="B642" s="26" t="n"/>
@@ -12299,7 +11663,6 @@
       <c r="O642" s="27" t="n"/>
       <c r="Q642" s="27" t="n"/>
       <c r="T642" s="26" t="n"/>
-      <c r="U642" s="26" t="n"/>
     </row>
     <row r="643">
       <c r="B643" s="26" t="n"/>
@@ -12317,7 +11680,6 @@
       <c r="O643" s="27" t="n"/>
       <c r="Q643" s="27" t="n"/>
       <c r="T643" s="26" t="n"/>
-      <c r="U643" s="26" t="n"/>
     </row>
     <row r="644">
       <c r="B644" s="26" t="n"/>
@@ -12335,7 +11697,6 @@
       <c r="O644" s="27" t="n"/>
       <c r="Q644" s="27" t="n"/>
       <c r="T644" s="26" t="n"/>
-      <c r="U644" s="26" t="n"/>
     </row>
     <row r="645">
       <c r="B645" s="26" t="n"/>
@@ -12353,7 +11714,6 @@
       <c r="O645" s="27" t="n"/>
       <c r="Q645" s="27" t="n"/>
       <c r="T645" s="26" t="n"/>
-      <c r="U645" s="26" t="n"/>
     </row>
     <row r="646">
       <c r="B646" s="26" t="n"/>
@@ -12371,7 +11731,6 @@
       <c r="O646" s="27" t="n"/>
       <c r="Q646" s="27" t="n"/>
       <c r="T646" s="26" t="n"/>
-      <c r="U646" s="26" t="n"/>
     </row>
     <row r="647">
       <c r="B647" s="26" t="n"/>
@@ -12389,7 +11748,6 @@
       <c r="O647" s="27" t="n"/>
       <c r="Q647" s="27" t="n"/>
       <c r="T647" s="26" t="n"/>
-      <c r="U647" s="26" t="n"/>
     </row>
     <row r="648">
       <c r="B648" s="26" t="n"/>
@@ -12407,7 +11765,6 @@
       <c r="O648" s="27" t="n"/>
       <c r="Q648" s="27" t="n"/>
       <c r="T648" s="26" t="n"/>
-      <c r="U648" s="26" t="n"/>
     </row>
     <row r="649">
       <c r="B649" s="26" t="n"/>
@@ -12425,7 +11782,6 @@
       <c r="O649" s="27" t="n"/>
       <c r="Q649" s="27" t="n"/>
       <c r="T649" s="26" t="n"/>
-      <c r="U649" s="26" t="n"/>
     </row>
     <row r="650">
       <c r="B650" s="26" t="n"/>
@@ -12443,7 +11799,6 @@
       <c r="O650" s="27" t="n"/>
       <c r="Q650" s="27" t="n"/>
       <c r="T650" s="26" t="n"/>
-      <c r="U650" s="26" t="n"/>
     </row>
     <row r="651">
       <c r="B651" s="26" t="n"/>
@@ -12461,7 +11816,6 @@
       <c r="O651" s="27" t="n"/>
       <c r="Q651" s="27" t="n"/>
       <c r="T651" s="26" t="n"/>
-      <c r="U651" s="26" t="n"/>
     </row>
     <row r="652">
       <c r="B652" s="26" t="n"/>
@@ -12479,7 +11833,6 @@
       <c r="O652" s="27" t="n"/>
       <c r="Q652" s="27" t="n"/>
       <c r="T652" s="26" t="n"/>
-      <c r="U652" s="26" t="n"/>
     </row>
     <row r="653">
       <c r="B653" s="26" t="n"/>
@@ -12497,7 +11850,6 @@
       <c r="O653" s="27" t="n"/>
       <c r="Q653" s="27" t="n"/>
       <c r="T653" s="26" t="n"/>
-      <c r="U653" s="26" t="n"/>
     </row>
     <row r="654">
       <c r="B654" s="26" t="n"/>
@@ -12515,7 +11867,6 @@
       <c r="O654" s="27" t="n"/>
       <c r="Q654" s="27" t="n"/>
       <c r="T654" s="26" t="n"/>
-      <c r="U654" s="26" t="n"/>
     </row>
     <row r="655">
       <c r="B655" s="26" t="n"/>
@@ -12533,7 +11884,6 @@
       <c r="O655" s="27" t="n"/>
       <c r="Q655" s="27" t="n"/>
       <c r="T655" s="26" t="n"/>
-      <c r="U655" s="26" t="n"/>
     </row>
     <row r="656">
       <c r="B656" s="26" t="n"/>
@@ -12551,7 +11901,6 @@
       <c r="O656" s="27" t="n"/>
       <c r="Q656" s="27" t="n"/>
       <c r="T656" s="26" t="n"/>
-      <c r="U656" s="26" t="n"/>
     </row>
     <row r="657">
       <c r="B657" s="26" t="n"/>
@@ -12569,7 +11918,6 @@
       <c r="O657" s="27" t="n"/>
       <c r="Q657" s="27" t="n"/>
       <c r="T657" s="26" t="n"/>
-      <c r="U657" s="26" t="n"/>
     </row>
     <row r="658">
       <c r="B658" s="26" t="n"/>
@@ -12587,7 +11935,6 @@
       <c r="O658" s="27" t="n"/>
       <c r="Q658" s="27" t="n"/>
       <c r="T658" s="26" t="n"/>
-      <c r="U658" s="26" t="n"/>
     </row>
     <row r="659">
       <c r="B659" s="26" t="n"/>
@@ -12605,7 +11952,6 @@
       <c r="O659" s="27" t="n"/>
       <c r="Q659" s="27" t="n"/>
       <c r="T659" s="26" t="n"/>
-      <c r="U659" s="26" t="n"/>
     </row>
     <row r="660">
       <c r="B660" s="26" t="n"/>
@@ -12623,7 +11969,6 @@
       <c r="O660" s="27" t="n"/>
       <c r="Q660" s="27" t="n"/>
       <c r="T660" s="26" t="n"/>
-      <c r="U660" s="26" t="n"/>
     </row>
     <row r="661">
       <c r="B661" s="26" t="n"/>
@@ -12641,7 +11986,6 @@
       <c r="O661" s="27" t="n"/>
       <c r="Q661" s="27" t="n"/>
       <c r="T661" s="26" t="n"/>
-      <c r="U661" s="26" t="n"/>
     </row>
     <row r="662">
       <c r="B662" s="26" t="n"/>
@@ -12659,7 +12003,6 @@
       <c r="O662" s="27" t="n"/>
       <c r="Q662" s="27" t="n"/>
       <c r="T662" s="26" t="n"/>
-      <c r="U662" s="26" t="n"/>
     </row>
     <row r="663">
       <c r="B663" s="26" t="n"/>
@@ -12677,7 +12020,6 @@
       <c r="O663" s="27" t="n"/>
       <c r="Q663" s="27" t="n"/>
       <c r="T663" s="26" t="n"/>
-      <c r="U663" s="26" t="n"/>
     </row>
     <row r="664">
       <c r="B664" s="26" t="n"/>
@@ -12695,7 +12037,6 @@
       <c r="O664" s="27" t="n"/>
       <c r="Q664" s="27" t="n"/>
       <c r="T664" s="26" t="n"/>
-      <c r="U664" s="26" t="n"/>
     </row>
     <row r="665">
       <c r="B665" s="26" t="n"/>
@@ -12713,7 +12054,6 @@
       <c r="O665" s="27" t="n"/>
       <c r="Q665" s="27" t="n"/>
       <c r="T665" s="26" t="n"/>
-      <c r="U665" s="26" t="n"/>
     </row>
     <row r="666">
       <c r="B666" s="26" t="n"/>
@@ -12731,7 +12071,6 @@
       <c r="O666" s="27" t="n"/>
       <c r="Q666" s="27" t="n"/>
       <c r="T666" s="26" t="n"/>
-      <c r="U666" s="26" t="n"/>
     </row>
     <row r="667">
       <c r="B667" s="26" t="n"/>
@@ -12749,7 +12088,6 @@
       <c r="O667" s="27" t="n"/>
       <c r="Q667" s="27" t="n"/>
       <c r="T667" s="26" t="n"/>
-      <c r="U667" s="26" t="n"/>
     </row>
     <row r="668">
       <c r="B668" s="26" t="n"/>
@@ -12767,7 +12105,6 @@
       <c r="O668" s="27" t="n"/>
       <c r="Q668" s="27" t="n"/>
       <c r="T668" s="26" t="n"/>
-      <c r="U668" s="26" t="n"/>
     </row>
     <row r="669">
       <c r="B669" s="26" t="n"/>
@@ -12785,7 +12122,6 @@
       <c r="O669" s="27" t="n"/>
       <c r="Q669" s="27" t="n"/>
       <c r="T669" s="26" t="n"/>
-      <c r="U669" s="26" t="n"/>
     </row>
     <row r="670">
       <c r="B670" s="26" t="n"/>
@@ -12803,7 +12139,6 @@
       <c r="O670" s="27" t="n"/>
       <c r="Q670" s="27" t="n"/>
       <c r="T670" s="26" t="n"/>
-      <c r="U670" s="26" t="n"/>
     </row>
     <row r="671">
       <c r="B671" s="26" t="n"/>
@@ -12821,7 +12156,6 @@
       <c r="O671" s="27" t="n"/>
       <c r="Q671" s="27" t="n"/>
       <c r="T671" s="26" t="n"/>
-      <c r="U671" s="26" t="n"/>
     </row>
     <row r="672">
       <c r="B672" s="26" t="n"/>
@@ -12839,7 +12173,6 @@
       <c r="O672" s="27" t="n"/>
       <c r="Q672" s="27" t="n"/>
       <c r="T672" s="26" t="n"/>
-      <c r="U672" s="26" t="n"/>
     </row>
     <row r="673">
       <c r="B673" s="26" t="n"/>
@@ -12857,7 +12190,6 @@
       <c r="O673" s="27" t="n"/>
       <c r="Q673" s="27" t="n"/>
       <c r="T673" s="26" t="n"/>
-      <c r="U673" s="26" t="n"/>
     </row>
     <row r="674">
       <c r="B674" s="26" t="n"/>
@@ -12875,7 +12207,6 @@
       <c r="O674" s="27" t="n"/>
       <c r="Q674" s="27" t="n"/>
       <c r="T674" s="26" t="n"/>
-      <c r="U674" s="26" t="n"/>
     </row>
     <row r="675">
       <c r="B675" s="26" t="n"/>
@@ -12893,7 +12224,6 @@
       <c r="O675" s="27" t="n"/>
       <c r="Q675" s="27" t="n"/>
       <c r="T675" s="26" t="n"/>
-      <c r="U675" s="26" t="n"/>
     </row>
     <row r="676">
       <c r="B676" s="26" t="n"/>
@@ -12911,7 +12241,6 @@
       <c r="O676" s="27" t="n"/>
       <c r="Q676" s="27" t="n"/>
       <c r="T676" s="26" t="n"/>
-      <c r="U676" s="26" t="n"/>
     </row>
     <row r="677">
       <c r="B677" s="26" t="n"/>
@@ -12929,7 +12258,6 @@
       <c r="O677" s="27" t="n"/>
       <c r="Q677" s="27" t="n"/>
       <c r="T677" s="26" t="n"/>
-      <c r="U677" s="26" t="n"/>
     </row>
     <row r="678">
       <c r="B678" s="26" t="n"/>
@@ -12947,7 +12275,6 @@
       <c r="O678" s="27" t="n"/>
       <c r="Q678" s="27" t="n"/>
       <c r="T678" s="26" t="n"/>
-      <c r="U678" s="26" t="n"/>
     </row>
     <row r="679">
       <c r="B679" s="26" t="n"/>
@@ -12965,7 +12292,6 @@
       <c r="O679" s="27" t="n"/>
       <c r="Q679" s="27" t="n"/>
       <c r="T679" s="26" t="n"/>
-      <c r="U679" s="26" t="n"/>
     </row>
     <row r="680">
       <c r="B680" s="26" t="n"/>
@@ -12983,7 +12309,6 @@
       <c r="O680" s="27" t="n"/>
       <c r="Q680" s="27" t="n"/>
       <c r="T680" s="26" t="n"/>
-      <c r="U680" s="26" t="n"/>
     </row>
     <row r="681">
       <c r="B681" s="26" t="n"/>
@@ -13001,7 +12326,6 @@
       <c r="O681" s="27" t="n"/>
       <c r="Q681" s="27" t="n"/>
       <c r="T681" s="26" t="n"/>
-      <c r="U681" s="26" t="n"/>
     </row>
     <row r="682">
       <c r="B682" s="26" t="n"/>
@@ -13019,7 +12343,6 @@
       <c r="O682" s="27" t="n"/>
       <c r="Q682" s="27" t="n"/>
       <c r="T682" s="26" t="n"/>
-      <c r="U682" s="26" t="n"/>
     </row>
     <row r="683">
       <c r="B683" s="26" t="n"/>
@@ -13037,7 +12360,6 @@
       <c r="O683" s="27" t="n"/>
       <c r="Q683" s="27" t="n"/>
       <c r="T683" s="26" t="n"/>
-      <c r="U683" s="26" t="n"/>
     </row>
     <row r="684">
       <c r="B684" s="26" t="n"/>
@@ -13055,7 +12377,6 @@
       <c r="O684" s="27" t="n"/>
       <c r="Q684" s="27" t="n"/>
       <c r="T684" s="26" t="n"/>
-      <c r="U684" s="26" t="n"/>
     </row>
     <row r="685">
       <c r="B685" s="26" t="n"/>
@@ -13073,7 +12394,6 @@
       <c r="O685" s="27" t="n"/>
       <c r="Q685" s="27" t="n"/>
       <c r="T685" s="26" t="n"/>
-      <c r="U685" s="26" t="n"/>
     </row>
     <row r="686">
       <c r="B686" s="26" t="n"/>
@@ -13091,7 +12411,6 @@
       <c r="O686" s="27" t="n"/>
       <c r="Q686" s="27" t="n"/>
       <c r="T686" s="26" t="n"/>
-      <c r="U686" s="26" t="n"/>
     </row>
     <row r="687">
       <c r="B687" s="26" t="n"/>
@@ -13109,7 +12428,6 @@
       <c r="O687" s="27" t="n"/>
       <c r="Q687" s="27" t="n"/>
       <c r="T687" s="26" t="n"/>
-      <c r="U687" s="26" t="n"/>
     </row>
     <row r="688">
       <c r="B688" s="26" t="n"/>
@@ -13127,7 +12445,6 @@
       <c r="O688" s="27" t="n"/>
       <c r="Q688" s="27" t="n"/>
       <c r="T688" s="26" t="n"/>
-      <c r="U688" s="26" t="n"/>
     </row>
     <row r="689">
       <c r="B689" s="26" t="n"/>
@@ -13145,7 +12462,6 @@
       <c r="O689" s="27" t="n"/>
       <c r="Q689" s="27" t="n"/>
       <c r="T689" s="26" t="n"/>
-      <c r="U689" s="26" t="n"/>
     </row>
     <row r="690">
       <c r="B690" s="26" t="n"/>
@@ -13163,7 +12479,6 @@
       <c r="O690" s="27" t="n"/>
       <c r="Q690" s="27" t="n"/>
       <c r="T690" s="26" t="n"/>
-      <c r="U690" s="26" t="n"/>
     </row>
     <row r="691">
       <c r="B691" s="26" t="n"/>
@@ -13181,7 +12496,6 @@
       <c r="O691" s="27" t="n"/>
       <c r="Q691" s="27" t="n"/>
       <c r="T691" s="26" t="n"/>
-      <c r="U691" s="26" t="n"/>
     </row>
     <row r="692">
       <c r="B692" s="26" t="n"/>
@@ -13199,7 +12513,6 @@
       <c r="O692" s="27" t="n"/>
       <c r="Q692" s="27" t="n"/>
       <c r="T692" s="26" t="n"/>
-      <c r="U692" s="26" t="n"/>
     </row>
     <row r="693">
       <c r="B693" s="26" t="n"/>
@@ -13217,7 +12530,6 @@
       <c r="O693" s="27" t="n"/>
       <c r="Q693" s="27" t="n"/>
       <c r="T693" s="26" t="n"/>
-      <c r="U693" s="26" t="n"/>
     </row>
     <row r="694">
       <c r="B694" s="26" t="n"/>
@@ -13235,7 +12547,6 @@
       <c r="O694" s="27" t="n"/>
       <c r="Q694" s="27" t="n"/>
       <c r="T694" s="26" t="n"/>
-      <c r="U694" s="26" t="n"/>
     </row>
     <row r="695">
       <c r="B695" s="26" t="n"/>
@@ -13253,7 +12564,6 @@
       <c r="O695" s="27" t="n"/>
       <c r="Q695" s="27" t="n"/>
       <c r="T695" s="26" t="n"/>
-      <c r="U695" s="26" t="n"/>
     </row>
     <row r="696">
       <c r="B696" s="26" t="n"/>
@@ -13271,7 +12581,6 @@
       <c r="O696" s="27" t="n"/>
       <c r="Q696" s="27" t="n"/>
       <c r="T696" s="26" t="n"/>
-      <c r="U696" s="26" t="n"/>
     </row>
     <row r="697">
       <c r="B697" s="26" t="n"/>
@@ -13289,7 +12598,6 @@
       <c r="O697" s="27" t="n"/>
       <c r="Q697" s="27" t="n"/>
       <c r="T697" s="26" t="n"/>
-      <c r="U697" s="26" t="n"/>
     </row>
     <row r="698">
       <c r="B698" s="26" t="n"/>
@@ -13307,7 +12615,6 @@
       <c r="O698" s="27" t="n"/>
       <c r="Q698" s="27" t="n"/>
       <c r="T698" s="26" t="n"/>
-      <c r="U698" s="26" t="n"/>
     </row>
     <row r="699">
       <c r="B699" s="26" t="n"/>
@@ -13325,7 +12632,6 @@
       <c r="O699" s="27" t="n"/>
       <c r="Q699" s="27" t="n"/>
       <c r="T699" s="26" t="n"/>
-      <c r="U699" s="26" t="n"/>
     </row>
     <row r="700">
       <c r="B700" s="26" t="n"/>
@@ -13343,7 +12649,6 @@
       <c r="O700" s="27" t="n"/>
       <c r="Q700" s="27" t="n"/>
       <c r="T700" s="26" t="n"/>
-      <c r="U700" s="26" t="n"/>
     </row>
     <row r="701">
       <c r="B701" s="26" t="n"/>
@@ -13361,7 +12666,6 @@
       <c r="O701" s="27" t="n"/>
       <c r="Q701" s="27" t="n"/>
       <c r="T701" s="26" t="n"/>
-      <c r="U701" s="26" t="n"/>
     </row>
     <row r="702">
       <c r="B702" s="26" t="n"/>
@@ -13379,7 +12683,6 @@
       <c r="O702" s="27" t="n"/>
       <c r="Q702" s="27" t="n"/>
       <c r="T702" s="26" t="n"/>
-      <c r="U702" s="26" t="n"/>
     </row>
     <row r="703">
       <c r="B703" s="26" t="n"/>
@@ -13397,7 +12700,6 @@
       <c r="O703" s="27" t="n"/>
       <c r="Q703" s="27" t="n"/>
       <c r="T703" s="26" t="n"/>
-      <c r="U703" s="26" t="n"/>
     </row>
     <row r="704">
       <c r="B704" s="26" t="n"/>
@@ -13415,7 +12717,6 @@
       <c r="O704" s="27" t="n"/>
       <c r="Q704" s="27" t="n"/>
       <c r="T704" s="26" t="n"/>
-      <c r="U704" s="26" t="n"/>
     </row>
     <row r="705">
       <c r="B705" s="26" t="n"/>
@@ -13433,7 +12734,6 @@
       <c r="O705" s="27" t="n"/>
       <c r="Q705" s="27" t="n"/>
       <c r="T705" s="26" t="n"/>
-      <c r="U705" s="26" t="n"/>
     </row>
     <row r="706">
       <c r="B706" s="26" t="n"/>
@@ -13451,7 +12751,6 @@
       <c r="O706" s="27" t="n"/>
       <c r="Q706" s="27" t="n"/>
       <c r="T706" s="26" t="n"/>
-      <c r="U706" s="26" t="n"/>
     </row>
     <row r="707">
       <c r="B707" s="26" t="n"/>
@@ -13469,7 +12768,6 @@
       <c r="O707" s="27" t="n"/>
       <c r="Q707" s="27" t="n"/>
       <c r="T707" s="26" t="n"/>
-      <c r="U707" s="26" t="n"/>
     </row>
     <row r="708">
       <c r="B708" s="26" t="n"/>
@@ -13487,7 +12785,6 @@
       <c r="O708" s="27" t="n"/>
       <c r="Q708" s="27" t="n"/>
       <c r="T708" s="26" t="n"/>
-      <c r="U708" s="26" t="n"/>
     </row>
     <row r="709">
       <c r="B709" s="26" t="n"/>
@@ -13505,7 +12802,6 @@
       <c r="O709" s="27" t="n"/>
       <c r="Q709" s="27" t="n"/>
       <c r="T709" s="26" t="n"/>
-      <c r="U709" s="26" t="n"/>
     </row>
     <row r="710">
       <c r="B710" s="26" t="n"/>
@@ -13523,7 +12819,6 @@
       <c r="O710" s="27" t="n"/>
       <c r="Q710" s="27" t="n"/>
       <c r="T710" s="26" t="n"/>
-      <c r="U710" s="26" t="n"/>
     </row>
     <row r="711">
       <c r="B711" s="26" t="n"/>
@@ -13541,7 +12836,6 @@
       <c r="O711" s="27" t="n"/>
       <c r="Q711" s="27" t="n"/>
       <c r="T711" s="26" t="n"/>
-      <c r="U711" s="26" t="n"/>
     </row>
     <row r="712">
       <c r="B712" s="26" t="n"/>
@@ -13559,7 +12853,6 @@
       <c r="O712" s="27" t="n"/>
       <c r="Q712" s="27" t="n"/>
       <c r="T712" s="26" t="n"/>
-      <c r="U712" s="26" t="n"/>
     </row>
     <row r="713">
       <c r="B713" s="26" t="n"/>
@@ -13577,7 +12870,6 @@
       <c r="O713" s="27" t="n"/>
       <c r="Q713" s="27" t="n"/>
       <c r="T713" s="26" t="n"/>
-      <c r="U713" s="26" t="n"/>
     </row>
     <row r="714">
       <c r="B714" s="26" t="n"/>
@@ -13595,7 +12887,6 @@
       <c r="O714" s="27" t="n"/>
       <c r="Q714" s="27" t="n"/>
       <c r="T714" s="26" t="n"/>
-      <c r="U714" s="26" t="n"/>
     </row>
     <row r="715">
       <c r="B715" s="26" t="n"/>
@@ -13613,7 +12904,6 @@
       <c r="O715" s="27" t="n"/>
       <c r="Q715" s="27" t="n"/>
       <c r="T715" s="26" t="n"/>
-      <c r="U715" s="26" t="n"/>
     </row>
     <row r="716">
       <c r="B716" s="26" t="n"/>
@@ -13631,7 +12921,6 @@
       <c r="O716" s="27" t="n"/>
       <c r="Q716" s="27" t="n"/>
       <c r="T716" s="26" t="n"/>
-      <c r="U716" s="26" t="n"/>
     </row>
     <row r="717">
       <c r="B717" s="26" t="n"/>
@@ -13649,7 +12938,6 @@
       <c r="O717" s="27" t="n"/>
       <c r="Q717" s="27" t="n"/>
       <c r="T717" s="26" t="n"/>
-      <c r="U717" s="26" t="n"/>
     </row>
     <row r="718">
       <c r="B718" s="26" t="n"/>
@@ -13667,7 +12955,6 @@
       <c r="O718" s="27" t="n"/>
       <c r="Q718" s="27" t="n"/>
       <c r="T718" s="26" t="n"/>
-      <c r="U718" s="26" t="n"/>
     </row>
     <row r="719">
       <c r="B719" s="26" t="n"/>
@@ -13685,7 +12972,6 @@
       <c r="O719" s="27" t="n"/>
       <c r="Q719" s="27" t="n"/>
       <c r="T719" s="26" t="n"/>
-      <c r="U719" s="26" t="n"/>
     </row>
     <row r="720">
       <c r="B720" s="26" t="n"/>
@@ -13703,7 +12989,6 @@
       <c r="O720" s="27" t="n"/>
       <c r="Q720" s="27" t="n"/>
       <c r="T720" s="26" t="n"/>
-      <c r="U720" s="26" t="n"/>
     </row>
     <row r="721">
       <c r="B721" s="26" t="n"/>
@@ -13721,7 +13006,6 @@
       <c r="O721" s="27" t="n"/>
       <c r="Q721" s="27" t="n"/>
       <c r="T721" s="26" t="n"/>
-      <c r="U721" s="26" t="n"/>
     </row>
     <row r="722">
       <c r="B722" s="26" t="n"/>
@@ -13739,7 +13023,6 @@
       <c r="O722" s="27" t="n"/>
       <c r="Q722" s="27" t="n"/>
       <c r="T722" s="26" t="n"/>
-      <c r="U722" s="26" t="n"/>
     </row>
     <row r="723">
       <c r="B723" s="26" t="n"/>
@@ -13757,7 +13040,6 @@
       <c r="O723" s="27" t="n"/>
       <c r="Q723" s="27" t="n"/>
       <c r="T723" s="26" t="n"/>
-      <c r="U723" s="26" t="n"/>
     </row>
     <row r="724">
       <c r="B724" s="26" t="n"/>
@@ -13775,7 +13057,6 @@
       <c r="O724" s="27" t="n"/>
       <c r="Q724" s="27" t="n"/>
       <c r="T724" s="26" t="n"/>
-      <c r="U724" s="26" t="n"/>
     </row>
     <row r="725">
       <c r="B725" s="26" t="n"/>
@@ -13793,7 +13074,6 @@
       <c r="O725" s="27" t="n"/>
       <c r="Q725" s="27" t="n"/>
       <c r="T725" s="26" t="n"/>
-      <c r="U725" s="26" t="n"/>
     </row>
     <row r="726">
       <c r="B726" s="26" t="n"/>
@@ -13811,7 +13091,6 @@
       <c r="O726" s="27" t="n"/>
       <c r="Q726" s="27" t="n"/>
       <c r="T726" s="26" t="n"/>
-      <c r="U726" s="26" t="n"/>
     </row>
     <row r="727">
       <c r="B727" s="26" t="n"/>
@@ -13829,7 +13108,6 @@
       <c r="O727" s="27" t="n"/>
       <c r="Q727" s="27" t="n"/>
       <c r="T727" s="26" t="n"/>
-      <c r="U727" s="26" t="n"/>
     </row>
     <row r="728">
       <c r="B728" s="26" t="n"/>
@@ -13847,7 +13125,6 @@
       <c r="O728" s="27" t="n"/>
       <c r="Q728" s="27" t="n"/>
       <c r="T728" s="26" t="n"/>
-      <c r="U728" s="26" t="n"/>
     </row>
     <row r="729">
       <c r="B729" s="26" t="n"/>
@@ -13865,7 +13142,6 @@
       <c r="O729" s="27" t="n"/>
       <c r="Q729" s="27" t="n"/>
       <c r="T729" s="26" t="n"/>
-      <c r="U729" s="26" t="n"/>
     </row>
     <row r="730">
       <c r="B730" s="26" t="n"/>
@@ -13883,7 +13159,6 @@
       <c r="O730" s="27" t="n"/>
       <c r="Q730" s="27" t="n"/>
       <c r="T730" s="26" t="n"/>
-      <c r="U730" s="26" t="n"/>
     </row>
     <row r="731">
       <c r="B731" s="26" t="n"/>
@@ -13901,7 +13176,6 @@
       <c r="O731" s="27" t="n"/>
       <c r="Q731" s="27" t="n"/>
       <c r="T731" s="26" t="n"/>
-      <c r="U731" s="26" t="n"/>
     </row>
     <row r="732">
       <c r="B732" s="26" t="n"/>
@@ -13919,7 +13193,6 @@
       <c r="O732" s="27" t="n"/>
       <c r="Q732" s="27" t="n"/>
       <c r="T732" s="26" t="n"/>
-      <c r="U732" s="26" t="n"/>
     </row>
     <row r="733">
       <c r="B733" s="26" t="n"/>
@@ -13937,7 +13210,6 @@
       <c r="O733" s="27" t="n"/>
       <c r="Q733" s="27" t="n"/>
       <c r="T733" s="26" t="n"/>
-      <c r="U733" s="26" t="n"/>
     </row>
     <row r="734">
       <c r="B734" s="26" t="n"/>
@@ -13955,7 +13227,6 @@
       <c r="O734" s="27" t="n"/>
       <c r="Q734" s="27" t="n"/>
       <c r="T734" s="26" t="n"/>
-      <c r="U734" s="26" t="n"/>
     </row>
     <row r="735">
       <c r="B735" s="26" t="n"/>
@@ -13973,7 +13244,6 @@
       <c r="O735" s="27" t="n"/>
       <c r="Q735" s="27" t="n"/>
       <c r="T735" s="26" t="n"/>
-      <c r="U735" s="26" t="n"/>
     </row>
     <row r="736">
       <c r="B736" s="26" t="n"/>
@@ -13991,7 +13261,6 @@
       <c r="O736" s="27" t="n"/>
       <c r="Q736" s="27" t="n"/>
       <c r="T736" s="26" t="n"/>
-      <c r="U736" s="26" t="n"/>
     </row>
     <row r="737">
       <c r="B737" s="26" t="n"/>
@@ -14009,7 +13278,6 @@
       <c r="O737" s="27" t="n"/>
       <c r="Q737" s="27" t="n"/>
       <c r="T737" s="26" t="n"/>
-      <c r="U737" s="26" t="n"/>
     </row>
     <row r="738">
       <c r="B738" s="26" t="n"/>
@@ -14027,7 +13295,6 @@
       <c r="O738" s="27" t="n"/>
       <c r="Q738" s="27" t="n"/>
       <c r="T738" s="26" t="n"/>
-      <c r="U738" s="26" t="n"/>
     </row>
     <row r="739">
       <c r="B739" s="26" t="n"/>
@@ -14045,7 +13312,6 @@
       <c r="O739" s="27" t="n"/>
       <c r="Q739" s="27" t="n"/>
       <c r="T739" s="26" t="n"/>
-      <c r="U739" s="26" t="n"/>
     </row>
     <row r="740">
       <c r="B740" s="26" t="n"/>
@@ -14063,7 +13329,6 @@
       <c r="O740" s="27" t="n"/>
       <c r="Q740" s="27" t="n"/>
       <c r="T740" s="26" t="n"/>
-      <c r="U740" s="26" t="n"/>
     </row>
     <row r="741">
       <c r="B741" s="26" t="n"/>
@@ -14081,7 +13346,6 @@
       <c r="O741" s="27" t="n"/>
       <c r="Q741" s="27" t="n"/>
       <c r="T741" s="26" t="n"/>
-      <c r="U741" s="26" t="n"/>
     </row>
     <row r="742">
       <c r="B742" s="26" t="n"/>
@@ -14099,7 +13363,6 @@
       <c r="O742" s="27" t="n"/>
       <c r="Q742" s="27" t="n"/>
       <c r="T742" s="26" t="n"/>
-      <c r="U742" s="26" t="n"/>
     </row>
     <row r="743">
       <c r="B743" s="26" t="n"/>
@@ -14117,7 +13380,6 @@
       <c r="O743" s="27" t="n"/>
       <c r="Q743" s="27" t="n"/>
       <c r="T743" s="26" t="n"/>
-      <c r="U743" s="26" t="n"/>
     </row>
     <row r="744">
       <c r="B744" s="26" t="n"/>
@@ -14135,7 +13397,6 @@
       <c r="O744" s="27" t="n"/>
       <c r="Q744" s="27" t="n"/>
       <c r="T744" s="26" t="n"/>
-      <c r="U744" s="26" t="n"/>
     </row>
     <row r="745">
       <c r="B745" s="26" t="n"/>
@@ -14153,7 +13414,6 @@
       <c r="O745" s="27" t="n"/>
       <c r="Q745" s="27" t="n"/>
       <c r="T745" s="26" t="n"/>
-      <c r="U745" s="26" t="n"/>
     </row>
     <row r="746">
       <c r="B746" s="26" t="n"/>
@@ -14171,7 +13431,6 @@
       <c r="O746" s="27" t="n"/>
       <c r="Q746" s="27" t="n"/>
       <c r="T746" s="26" t="n"/>
-      <c r="U746" s="26" t="n"/>
     </row>
     <row r="747">
       <c r="B747" s="26" t="n"/>
@@ -14189,7 +13448,6 @@
       <c r="O747" s="27" t="n"/>
       <c r="Q747" s="27" t="n"/>
       <c r="T747" s="26" t="n"/>
-      <c r="U747" s="26" t="n"/>
     </row>
     <row r="748">
       <c r="B748" s="26" t="n"/>
@@ -14207,7 +13465,6 @@
       <c r="O748" s="27" t="n"/>
       <c r="Q748" s="27" t="n"/>
       <c r="T748" s="26" t="n"/>
-      <c r="U748" s="26" t="n"/>
     </row>
     <row r="749">
       <c r="B749" s="26" t="n"/>
@@ -14225,7 +13482,6 @@
       <c r="O749" s="27" t="n"/>
       <c r="Q749" s="27" t="n"/>
       <c r="T749" s="26" t="n"/>
-      <c r="U749" s="26" t="n"/>
     </row>
     <row r="750">
       <c r="B750" s="26" t="n"/>
@@ -14243,7 +13499,6 @@
       <c r="O750" s="27" t="n"/>
       <c r="Q750" s="27" t="n"/>
       <c r="T750" s="26" t="n"/>
-      <c r="U750" s="26" t="n"/>
     </row>
     <row r="751">
       <c r="B751" s="26" t="n"/>
@@ -14261,7 +13516,6 @@
       <c r="O751" s="27" t="n"/>
       <c r="Q751" s="27" t="n"/>
       <c r="T751" s="26" t="n"/>
-      <c r="U751" s="26" t="n"/>
     </row>
     <row r="752">
       <c r="B752" s="26" t="n"/>
@@ -14279,7 +13533,6 @@
       <c r="O752" s="27" t="n"/>
       <c r="Q752" s="27" t="n"/>
       <c r="T752" s="26" t="n"/>
-      <c r="U752" s="26" t="n"/>
     </row>
     <row r="753">
       <c r="B753" s="26" t="n"/>
@@ -14297,7 +13550,6 @@
       <c r="O753" s="27" t="n"/>
       <c r="Q753" s="27" t="n"/>
       <c r="T753" s="26" t="n"/>
-      <c r="U753" s="26" t="n"/>
     </row>
     <row r="754">
       <c r="B754" s="26" t="n"/>
@@ -14315,7 +13567,6 @@
       <c r="O754" s="27" t="n"/>
       <c r="Q754" s="27" t="n"/>
       <c r="T754" s="26" t="n"/>
-      <c r="U754" s="26" t="n"/>
     </row>
     <row r="755">
       <c r="B755" s="26" t="n"/>
@@ -14333,7 +13584,6 @@
       <c r="O755" s="27" t="n"/>
       <c r="Q755" s="27" t="n"/>
       <c r="T755" s="26" t="n"/>
-      <c r="U755" s="26" t="n"/>
     </row>
     <row r="756">
       <c r="B756" s="26" t="n"/>
@@ -14351,7 +13601,6 @@
       <c r="O756" s="27" t="n"/>
       <c r="Q756" s="27" t="n"/>
       <c r="T756" s="26" t="n"/>
-      <c r="U756" s="26" t="n"/>
     </row>
     <row r="757">
       <c r="B757" s="26" t="n"/>
@@ -14369,7 +13618,6 @@
       <c r="O757" s="27" t="n"/>
       <c r="Q757" s="27" t="n"/>
       <c r="T757" s="26" t="n"/>
-      <c r="U757" s="26" t="n"/>
     </row>
     <row r="758">
       <c r="B758" s="26" t="n"/>
@@ -14387,7 +13635,6 @@
       <c r="O758" s="27" t="n"/>
       <c r="Q758" s="27" t="n"/>
       <c r="T758" s="26" t="n"/>
-      <c r="U758" s="26" t="n"/>
     </row>
     <row r="759">
       <c r="B759" s="26" t="n"/>
@@ -14405,7 +13652,6 @@
       <c r="O759" s="27" t="n"/>
       <c r="Q759" s="27" t="n"/>
       <c r="T759" s="26" t="n"/>
-      <c r="U759" s="26" t="n"/>
     </row>
     <row r="760">
       <c r="B760" s="26" t="n"/>
@@ -14423,7 +13669,6 @@
       <c r="O760" s="27" t="n"/>
       <c r="Q760" s="27" t="n"/>
       <c r="T760" s="26" t="n"/>
-      <c r="U760" s="26" t="n"/>
     </row>
     <row r="761">
       <c r="B761" s="26" t="n"/>
@@ -14441,7 +13686,6 @@
       <c r="O761" s="27" t="n"/>
       <c r="Q761" s="27" t="n"/>
       <c r="T761" s="26" t="n"/>
-      <c r="U761" s="26" t="n"/>
     </row>
     <row r="762">
       <c r="B762" s="26" t="n"/>
@@ -14459,7 +13703,6 @@
       <c r="O762" s="27" t="n"/>
       <c r="Q762" s="27" t="n"/>
       <c r="T762" s="26" t="n"/>
-      <c r="U762" s="26" t="n"/>
     </row>
     <row r="763">
       <c r="B763" s="26" t="n"/>
@@ -14477,7 +13720,6 @@
       <c r="O763" s="27" t="n"/>
       <c r="Q763" s="27" t="n"/>
       <c r="T763" s="26" t="n"/>
-      <c r="U763" s="26" t="n"/>
     </row>
     <row r="764">
       <c r="B764" s="26" t="n"/>
@@ -14495,7 +13737,6 @@
       <c r="O764" s="27" t="n"/>
       <c r="Q764" s="27" t="n"/>
       <c r="T764" s="26" t="n"/>
-      <c r="U764" s="26" t="n"/>
     </row>
     <row r="765">
       <c r="B765" s="26" t="n"/>
@@ -14513,7 +13754,6 @@
       <c r="O765" s="27" t="n"/>
       <c r="Q765" s="27" t="n"/>
       <c r="T765" s="26" t="n"/>
-      <c r="U765" s="26" t="n"/>
     </row>
     <row r="766">
       <c r="B766" s="26" t="n"/>
@@ -14531,7 +13771,6 @@
       <c r="O766" s="27" t="n"/>
       <c r="Q766" s="27" t="n"/>
       <c r="T766" s="26" t="n"/>
-      <c r="U766" s="26" t="n"/>
     </row>
     <row r="767">
       <c r="B767" s="26" t="n"/>
@@ -14549,7 +13788,6 @@
       <c r="O767" s="27" t="n"/>
       <c r="Q767" s="27" t="n"/>
       <c r="T767" s="26" t="n"/>
-      <c r="U767" s="26" t="n"/>
     </row>
     <row r="768">
       <c r="B768" s="26" t="n"/>
@@ -14567,7 +13805,6 @@
       <c r="O768" s="27" t="n"/>
       <c r="Q768" s="27" t="n"/>
       <c r="T768" s="26" t="n"/>
-      <c r="U768" s="26" t="n"/>
     </row>
     <row r="769">
       <c r="B769" s="26" t="n"/>
@@ -14585,7 +13822,6 @@
       <c r="O769" s="27" t="n"/>
       <c r="Q769" s="27" t="n"/>
       <c r="T769" s="26" t="n"/>
-      <c r="U769" s="26" t="n"/>
     </row>
     <row r="770">
       <c r="B770" s="26" t="n"/>
@@ -14603,7 +13839,6 @@
       <c r="O770" s="27" t="n"/>
       <c r="Q770" s="27" t="n"/>
       <c r="T770" s="26" t="n"/>
-      <c r="U770" s="26" t="n"/>
     </row>
     <row r="771">
       <c r="B771" s="26" t="n"/>
@@ -14621,7 +13856,6 @@
       <c r="O771" s="27" t="n"/>
       <c r="Q771" s="27" t="n"/>
       <c r="T771" s="26" t="n"/>
-      <c r="U771" s="26" t="n"/>
     </row>
     <row r="772">
       <c r="B772" s="26" t="n"/>
@@ -14639,7 +13873,6 @@
       <c r="O772" s="27" t="n"/>
       <c r="Q772" s="27" t="n"/>
       <c r="T772" s="26" t="n"/>
-      <c r="U772" s="26" t="n"/>
     </row>
     <row r="773">
       <c r="B773" s="26" t="n"/>
@@ -14657,7 +13890,6 @@
       <c r="O773" s="27" t="n"/>
       <c r="Q773" s="27" t="n"/>
       <c r="T773" s="26" t="n"/>
-      <c r="U773" s="26" t="n"/>
     </row>
     <row r="774">
       <c r="B774" s="26" t="n"/>
@@ -14675,7 +13907,6 @@
       <c r="O774" s="27" t="n"/>
       <c r="Q774" s="27" t="n"/>
       <c r="T774" s="26" t="n"/>
-      <c r="U774" s="26" t="n"/>
     </row>
     <row r="775">
       <c r="B775" s="26" t="n"/>
@@ -14693,7 +13924,6 @@
       <c r="O775" s="27" t="n"/>
       <c r="Q775" s="27" t="n"/>
       <c r="T775" s="26" t="n"/>
-      <c r="U775" s="26" t="n"/>
     </row>
     <row r="776">
       <c r="B776" s="26" t="n"/>
@@ -14711,7 +13941,6 @@
       <c r="O776" s="27" t="n"/>
       <c r="Q776" s="27" t="n"/>
       <c r="T776" s="26" t="n"/>
-      <c r="U776" s="26" t="n"/>
     </row>
     <row r="777">
       <c r="B777" s="26" t="n"/>
@@ -14729,7 +13958,6 @@
       <c r="O777" s="27" t="n"/>
       <c r="Q777" s="27" t="n"/>
       <c r="T777" s="26" t="n"/>
-      <c r="U777" s="26" t="n"/>
     </row>
     <row r="778">
       <c r="B778" s="26" t="n"/>
@@ -14747,7 +13975,6 @@
       <c r="O778" s="27" t="n"/>
       <c r="Q778" s="27" t="n"/>
       <c r="T778" s="26" t="n"/>
-      <c r="U778" s="26" t="n"/>
     </row>
     <row r="779">
       <c r="B779" s="26" t="n"/>
@@ -14765,7 +13992,6 @@
       <c r="O779" s="27" t="n"/>
       <c r="Q779" s="27" t="n"/>
       <c r="T779" s="26" t="n"/>
-      <c r="U779" s="26" t="n"/>
     </row>
     <row r="780">
       <c r="B780" s="26" t="n"/>
@@ -14783,7 +14009,6 @@
       <c r="O780" s="27" t="n"/>
       <c r="Q780" s="27" t="n"/>
       <c r="T780" s="26" t="n"/>
-      <c r="U780" s="26" t="n"/>
     </row>
     <row r="781">
       <c r="B781" s="26" t="n"/>
@@ -14801,7 +14026,6 @@
       <c r="O781" s="27" t="n"/>
       <c r="Q781" s="27" t="n"/>
       <c r="T781" s="26" t="n"/>
-      <c r="U781" s="26" t="n"/>
     </row>
     <row r="782">
       <c r="B782" s="26" t="n"/>
@@ -14819,7 +14043,6 @@
       <c r="O782" s="27" t="n"/>
       <c r="Q782" s="27" t="n"/>
       <c r="T782" s="26" t="n"/>
-      <c r="U782" s="26" t="n"/>
     </row>
     <row r="783">
       <c r="B783" s="26" t="n"/>
@@ -14837,7 +14060,6 @@
       <c r="O783" s="27" t="n"/>
       <c r="Q783" s="27" t="n"/>
       <c r="T783" s="26" t="n"/>
-      <c r="U783" s="26" t="n"/>
     </row>
     <row r="784">
       <c r="B784" s="26" t="n"/>
@@ -14855,7 +14077,6 @@
       <c r="O784" s="27" t="n"/>
       <c r="Q784" s="27" t="n"/>
       <c r="T784" s="26" t="n"/>
-      <c r="U784" s="26" t="n"/>
     </row>
     <row r="785">
       <c r="B785" s="26" t="n"/>
@@ -14873,7 +14094,6 @@
       <c r="O785" s="27" t="n"/>
       <c r="Q785" s="27" t="n"/>
       <c r="T785" s="26" t="n"/>
-      <c r="U785" s="26" t="n"/>
     </row>
     <row r="786">
       <c r="B786" s="26" t="n"/>
@@ -14891,7 +14111,6 @@
       <c r="O786" s="27" t="n"/>
       <c r="Q786" s="27" t="n"/>
       <c r="T786" s="26" t="n"/>
-      <c r="U786" s="26" t="n"/>
     </row>
     <row r="787">
       <c r="B787" s="26" t="n"/>
@@ -14909,7 +14128,6 @@
       <c r="O787" s="27" t="n"/>
       <c r="Q787" s="27" t="n"/>
       <c r="T787" s="26" t="n"/>
-      <c r="U787" s="26" t="n"/>
     </row>
     <row r="788">
       <c r="B788" s="26" t="n"/>
@@ -14927,7 +14145,6 @@
       <c r="O788" s="27" t="n"/>
       <c r="Q788" s="27" t="n"/>
       <c r="T788" s="26" t="n"/>
-      <c r="U788" s="26" t="n"/>
     </row>
     <row r="789">
       <c r="B789" s="26" t="n"/>
@@ -14945,7 +14162,6 @@
       <c r="O789" s="27" t="n"/>
       <c r="Q789" s="27" t="n"/>
       <c r="T789" s="26" t="n"/>
-      <c r="U789" s="26" t="n"/>
     </row>
     <row r="790">
       <c r="B790" s="26" t="n"/>
@@ -14963,7 +14179,6 @@
       <c r="O790" s="27" t="n"/>
       <c r="Q790" s="27" t="n"/>
       <c r="T790" s="26" t="n"/>
-      <c r="U790" s="26" t="n"/>
     </row>
     <row r="791">
       <c r="B791" s="26" t="n"/>
@@ -14981,7 +14196,6 @@
       <c r="O791" s="27" t="n"/>
       <c r="Q791" s="27" t="n"/>
       <c r="T791" s="26" t="n"/>
-      <c r="U791" s="26" t="n"/>
     </row>
     <row r="792">
       <c r="B792" s="26" t="n"/>
@@ -14999,7 +14213,6 @@
       <c r="O792" s="27" t="n"/>
       <c r="Q792" s="27" t="n"/>
       <c r="T792" s="26" t="n"/>
-      <c r="U792" s="26" t="n"/>
     </row>
     <row r="793">
       <c r="B793" s="26" t="n"/>
@@ -15017,7 +14230,6 @@
       <c r="O793" s="27" t="n"/>
       <c r="Q793" s="27" t="n"/>
       <c r="T793" s="26" t="n"/>
-      <c r="U793" s="26" t="n"/>
     </row>
     <row r="794">
       <c r="B794" s="26" t="n"/>
@@ -15035,7 +14247,6 @@
       <c r="O794" s="27" t="n"/>
       <c r="Q794" s="27" t="n"/>
       <c r="T794" s="26" t="n"/>
-      <c r="U794" s="26" t="n"/>
     </row>
     <row r="795">
       <c r="B795" s="26" t="n"/>
@@ -15053,7 +14264,6 @@
       <c r="O795" s="27" t="n"/>
       <c r="Q795" s="27" t="n"/>
       <c r="T795" s="26" t="n"/>
-      <c r="U795" s="26" t="n"/>
     </row>
     <row r="796">
       <c r="B796" s="26" t="n"/>
@@ -15071,7 +14281,6 @@
       <c r="O796" s="27" t="n"/>
       <c r="Q796" s="27" t="n"/>
       <c r="T796" s="26" t="n"/>
-      <c r="U796" s="26" t="n"/>
     </row>
     <row r="797">
       <c r="B797" s="26" t="n"/>
@@ -15089,7 +14298,6 @@
       <c r="O797" s="27" t="n"/>
       <c r="Q797" s="27" t="n"/>
       <c r="T797" s="26" t="n"/>
-      <c r="U797" s="26" t="n"/>
     </row>
     <row r="798">
       <c r="B798" s="26" t="n"/>
@@ -15107,7 +14315,6 @@
       <c r="O798" s="27" t="n"/>
       <c r="Q798" s="27" t="n"/>
       <c r="T798" s="26" t="n"/>
-      <c r="U798" s="26" t="n"/>
     </row>
     <row r="799">
       <c r="B799" s="26" t="n"/>
@@ -15125,7 +14332,6 @@
       <c r="O799" s="27" t="n"/>
       <c r="Q799" s="27" t="n"/>
       <c r="T799" s="26" t="n"/>
-      <c r="U799" s="26" t="n"/>
     </row>
     <row r="800">
       <c r="B800" s="26" t="n"/>
@@ -15143,7 +14349,6 @@
       <c r="O800" s="27" t="n"/>
       <c r="Q800" s="27" t="n"/>
       <c r="T800" s="26" t="n"/>
-      <c r="U800" s="26" t="n"/>
     </row>
     <row r="801">
       <c r="B801" s="26" t="n"/>
@@ -15161,7 +14366,6 @@
       <c r="O801" s="27" t="n"/>
       <c r="Q801" s="27" t="n"/>
       <c r="T801" s="26" t="n"/>
-      <c r="U801" s="26" t="n"/>
     </row>
     <row r="802">
       <c r="B802" s="26" t="n"/>
@@ -15179,7 +14383,6 @@
       <c r="O802" s="27" t="n"/>
       <c r="Q802" s="27" t="n"/>
       <c r="T802" s="26" t="n"/>
-      <c r="U802" s="26" t="n"/>
     </row>
     <row r="803">
       <c r="B803" s="26" t="n"/>
@@ -15197,7 +14400,6 @@
       <c r="O803" s="27" t="n"/>
       <c r="Q803" s="27" t="n"/>
       <c r="T803" s="26" t="n"/>
-      <c r="U803" s="26" t="n"/>
     </row>
     <row r="804">
       <c r="B804" s="26" t="n"/>
@@ -15215,7 +14417,6 @@
       <c r="O804" s="27" t="n"/>
       <c r="Q804" s="27" t="n"/>
       <c r="T804" s="26" t="n"/>
-      <c r="U804" s="26" t="n"/>
     </row>
     <row r="805">
       <c r="B805" s="26" t="n"/>
@@ -15233,7 +14434,6 @@
       <c r="O805" s="27" t="n"/>
       <c r="Q805" s="27" t="n"/>
       <c r="T805" s="26" t="n"/>
-      <c r="U805" s="26" t="n"/>
     </row>
     <row r="806">
       <c r="B806" s="26" t="n"/>
@@ -15251,7 +14451,6 @@
       <c r="O806" s="27" t="n"/>
       <c r="Q806" s="27" t="n"/>
       <c r="T806" s="26" t="n"/>
-      <c r="U806" s="26" t="n"/>
     </row>
     <row r="807">
       <c r="B807" s="26" t="n"/>
@@ -15269,7 +14468,6 @@
       <c r="O807" s="27" t="n"/>
       <c r="Q807" s="27" t="n"/>
       <c r="T807" s="26" t="n"/>
-      <c r="U807" s="26" t="n"/>
     </row>
     <row r="808">
       <c r="B808" s="26" t="n"/>
@@ -15287,7 +14485,6 @@
       <c r="O808" s="27" t="n"/>
       <c r="Q808" s="27" t="n"/>
       <c r="T808" s="26" t="n"/>
-      <c r="U808" s="26" t="n"/>
     </row>
     <row r="809">
       <c r="B809" s="26" t="n"/>
@@ -15305,7 +14502,6 @@
       <c r="O809" s="27" t="n"/>
       <c r="Q809" s="27" t="n"/>
       <c r="T809" s="26" t="n"/>
-      <c r="U809" s="26" t="n"/>
     </row>
     <row r="810">
       <c r="B810" s="26" t="n"/>
@@ -15323,7 +14519,6 @@
       <c r="O810" s="27" t="n"/>
       <c r="Q810" s="27" t="n"/>
       <c r="T810" s="26" t="n"/>
-      <c r="U810" s="26" t="n"/>
     </row>
     <row r="811">
       <c r="B811" s="26" t="n"/>
@@ -15341,7 +14536,6 @@
       <c r="O811" s="27" t="n"/>
       <c r="Q811" s="27" t="n"/>
       <c r="T811" s="26" t="n"/>
-      <c r="U811" s="26" t="n"/>
     </row>
     <row r="812">
       <c r="B812" s="26" t="n"/>
@@ -15359,7 +14553,6 @@
       <c r="O812" s="27" t="n"/>
       <c r="Q812" s="27" t="n"/>
       <c r="T812" s="26" t="n"/>
-      <c r="U812" s="26" t="n"/>
     </row>
     <row r="813">
       <c r="B813" s="26" t="n"/>
@@ -15377,7 +14570,6 @@
       <c r="O813" s="27" t="n"/>
       <c r="Q813" s="27" t="n"/>
       <c r="T813" s="26" t="n"/>
-      <c r="U813" s="26" t="n"/>
     </row>
     <row r="814">
       <c r="B814" s="26" t="n"/>
@@ -15395,7 +14587,6 @@
       <c r="O814" s="27" t="n"/>
       <c r="Q814" s="27" t="n"/>
       <c r="T814" s="26" t="n"/>
-      <c r="U814" s="26" t="n"/>
     </row>
     <row r="815">
       <c r="B815" s="26" t="n"/>
@@ -15413,7 +14604,6 @@
       <c r="O815" s="27" t="n"/>
       <c r="Q815" s="27" t="n"/>
       <c r="T815" s="26" t="n"/>
-      <c r="U815" s="26" t="n"/>
     </row>
     <row r="816">
       <c r="B816" s="26" t="n"/>
@@ -15431,7 +14621,6 @@
       <c r="O816" s="27" t="n"/>
       <c r="Q816" s="27" t="n"/>
       <c r="T816" s="26" t="n"/>
-      <c r="U816" s="26" t="n"/>
     </row>
     <row r="817">
       <c r="B817" s="26" t="n"/>
@@ -15449,7 +14638,6 @@
       <c r="O817" s="27" t="n"/>
       <c r="Q817" s="27" t="n"/>
       <c r="T817" s="26" t="n"/>
-      <c r="U817" s="26" t="n"/>
     </row>
     <row r="818">
       <c r="B818" s="26" t="n"/>
@@ -15467,7 +14655,6 @@
       <c r="O818" s="27" t="n"/>
       <c r="Q818" s="27" t="n"/>
       <c r="T818" s="26" t="n"/>
-      <c r="U818" s="26" t="n"/>
     </row>
     <row r="819">
       <c r="B819" s="26" t="n"/>
@@ -15485,7 +14672,6 @@
       <c r="O819" s="27" t="n"/>
       <c r="Q819" s="27" t="n"/>
       <c r="T819" s="26" t="n"/>
-      <c r="U819" s="26" t="n"/>
     </row>
     <row r="820">
       <c r="B820" s="26" t="n"/>
@@ -15503,7 +14689,6 @@
       <c r="O820" s="27" t="n"/>
       <c r="Q820" s="27" t="n"/>
       <c r="T820" s="26" t="n"/>
-      <c r="U820" s="26" t="n"/>
     </row>
     <row r="821">
       <c r="B821" s="26" t="n"/>
@@ -15521,7 +14706,6 @@
       <c r="O821" s="27" t="n"/>
       <c r="Q821" s="27" t="n"/>
       <c r="T821" s="26" t="n"/>
-      <c r="U821" s="26" t="n"/>
     </row>
     <row r="822">
       <c r="B822" s="26" t="n"/>
@@ -15539,7 +14723,6 @@
       <c r="O822" s="27" t="n"/>
       <c r="Q822" s="27" t="n"/>
       <c r="T822" s="26" t="n"/>
-      <c r="U822" s="26" t="n"/>
     </row>
     <row r="823">
       <c r="B823" s="26" t="n"/>
@@ -15557,7 +14740,6 @@
       <c r="O823" s="27" t="n"/>
       <c r="Q823" s="27" t="n"/>
       <c r="T823" s="26" t="n"/>
-      <c r="U823" s="26" t="n"/>
     </row>
     <row r="824">
       <c r="B824" s="26" t="n"/>
@@ -15575,7 +14757,6 @@
       <c r="O824" s="27" t="n"/>
       <c r="Q824" s="27" t="n"/>
       <c r="T824" s="26" t="n"/>
-      <c r="U824" s="26" t="n"/>
     </row>
     <row r="825">
       <c r="B825" s="26" t="n"/>
@@ -15593,7 +14774,6 @@
       <c r="O825" s="27" t="n"/>
       <c r="Q825" s="27" t="n"/>
       <c r="T825" s="26" t="n"/>
-      <c r="U825" s="26" t="n"/>
     </row>
     <row r="826">
       <c r="B826" s="26" t="n"/>
@@ -15611,7 +14791,6 @@
       <c r="O826" s="27" t="n"/>
       <c r="Q826" s="27" t="n"/>
       <c r="T826" s="26" t="n"/>
-      <c r="U826" s="26" t="n"/>
     </row>
     <row r="827">
       <c r="B827" s="26" t="n"/>
@@ -15629,7 +14808,6 @@
       <c r="O827" s="27" t="n"/>
       <c r="Q827" s="27" t="n"/>
       <c r="T827" s="26" t="n"/>
-      <c r="U827" s="26" t="n"/>
     </row>
     <row r="828">
       <c r="B828" s="26" t="n"/>
@@ -15647,7 +14825,6 @@
       <c r="O828" s="27" t="n"/>
       <c r="Q828" s="27" t="n"/>
       <c r="T828" s="26" t="n"/>
-      <c r="U828" s="26" t="n"/>
     </row>
     <row r="829">
       <c r="B829" s="26" t="n"/>
@@ -15665,7 +14842,6 @@
       <c r="O829" s="27" t="n"/>
       <c r="Q829" s="27" t="n"/>
       <c r="T829" s="26" t="n"/>
-      <c r="U829" s="26" t="n"/>
     </row>
     <row r="830">
       <c r="B830" s="26" t="n"/>
@@ -15683,7 +14859,6 @@
       <c r="O830" s="27" t="n"/>
       <c r="Q830" s="27" t="n"/>
       <c r="T830" s="26" t="n"/>
-      <c r="U830" s="26" t="n"/>
     </row>
     <row r="831">
       <c r="B831" s="26" t="n"/>
@@ -15701,7 +14876,6 @@
       <c r="O831" s="27" t="n"/>
       <c r="Q831" s="27" t="n"/>
       <c r="T831" s="26" t="n"/>
-      <c r="U831" s="26" t="n"/>
     </row>
     <row r="832">
       <c r="B832" s="26" t="n"/>
@@ -15719,7 +14893,6 @@
       <c r="O832" s="27" t="n"/>
       <c r="Q832" s="27" t="n"/>
       <c r="T832" s="26" t="n"/>
-      <c r="U832" s="26" t="n"/>
     </row>
     <row r="833">
       <c r="B833" s="26" t="n"/>
@@ -15737,7 +14910,6 @@
       <c r="O833" s="27" t="n"/>
       <c r="Q833" s="27" t="n"/>
       <c r="T833" s="26" t="n"/>
-      <c r="U833" s="26" t="n"/>
     </row>
     <row r="834">
       <c r="B834" s="26" t="n"/>
@@ -15755,7 +14927,6 @@
       <c r="O834" s="27" t="n"/>
       <c r="Q834" s="27" t="n"/>
       <c r="T834" s="26" t="n"/>
-      <c r="U834" s="26" t="n"/>
     </row>
     <row r="835">
       <c r="B835" s="26" t="n"/>
@@ -15773,7 +14944,6 @@
       <c r="O835" s="27" t="n"/>
       <c r="Q835" s="27" t="n"/>
       <c r="T835" s="26" t="n"/>
-      <c r="U835" s="26" t="n"/>
     </row>
     <row r="836">
       <c r="B836" s="26" t="n"/>
@@ -15791,7 +14961,6 @@
       <c r="O836" s="27" t="n"/>
       <c r="Q836" s="27" t="n"/>
       <c r="T836" s="26" t="n"/>
-      <c r="U836" s="26" t="n"/>
     </row>
     <row r="837">
       <c r="B837" s="26" t="n"/>
@@ -15809,7 +14978,6 @@
       <c r="O837" s="27" t="n"/>
       <c r="Q837" s="27" t="n"/>
       <c r="T837" s="26" t="n"/>
-      <c r="U837" s="26" t="n"/>
     </row>
     <row r="838">
       <c r="B838" s="26" t="n"/>
@@ -15827,7 +14995,6 @@
       <c r="O838" s="27" t="n"/>
       <c r="Q838" s="27" t="n"/>
       <c r="T838" s="26" t="n"/>
-      <c r="U838" s="26" t="n"/>
     </row>
     <row r="839">
       <c r="B839" s="26" t="n"/>
@@ -15845,7 +15012,6 @@
       <c r="O839" s="27" t="n"/>
       <c r="Q839" s="27" t="n"/>
       <c r="T839" s="26" t="n"/>
-      <c r="U839" s="26" t="n"/>
     </row>
     <row r="840">
       <c r="B840" s="26" t="n"/>
@@ -15863,7 +15029,6 @@
       <c r="O840" s="27" t="n"/>
       <c r="Q840" s="27" t="n"/>
       <c r="T840" s="26" t="n"/>
-      <c r="U840" s="26" t="n"/>
     </row>
     <row r="841">
       <c r="B841" s="26" t="n"/>
@@ -15881,7 +15046,6 @@
       <c r="O841" s="27" t="n"/>
       <c r="Q841" s="27" t="n"/>
       <c r="T841" s="26" t="n"/>
-      <c r="U841" s="26" t="n"/>
     </row>
     <row r="842">
       <c r="B842" s="26" t="n"/>
@@ -15899,7 +15063,6 @@
       <c r="O842" s="27" t="n"/>
       <c r="Q842" s="27" t="n"/>
       <c r="T842" s="26" t="n"/>
-      <c r="U842" s="26" t="n"/>
     </row>
     <row r="843">
       <c r="B843" s="26" t="n"/>
@@ -15917,7 +15080,6 @@
       <c r="O843" s="27" t="n"/>
       <c r="Q843" s="27" t="n"/>
       <c r="T843" s="26" t="n"/>
-      <c r="U843" s="26" t="n"/>
     </row>
     <row r="844">
       <c r="B844" s="26" t="n"/>
@@ -15935,7 +15097,6 @@
       <c r="O844" s="27" t="n"/>
       <c r="Q844" s="27" t="n"/>
       <c r="T844" s="26" t="n"/>
-      <c r="U844" s="26" t="n"/>
     </row>
     <row r="845">
       <c r="B845" s="26" t="n"/>
@@ -15953,7 +15114,6 @@
       <c r="O845" s="27" t="n"/>
       <c r="Q845" s="27" t="n"/>
       <c r="T845" s="26" t="n"/>
-      <c r="U845" s="26" t="n"/>
     </row>
     <row r="846">
       <c r="B846" s="26" t="n"/>
@@ -15971,7 +15131,6 @@
       <c r="O846" s="27" t="n"/>
       <c r="Q846" s="27" t="n"/>
       <c r="T846" s="26" t="n"/>
-      <c r="U846" s="26" t="n"/>
     </row>
     <row r="847">
       <c r="B847" s="26" t="n"/>
@@ -15989,7 +15148,6 @@
       <c r="O847" s="27" t="n"/>
       <c r="Q847" s="27" t="n"/>
       <c r="T847" s="26" t="n"/>
-      <c r="U847" s="26" t="n"/>
     </row>
     <row r="848">
       <c r="B848" s="26" t="n"/>
@@ -16007,7 +15165,6 @@
       <c r="O848" s="27" t="n"/>
       <c r="Q848" s="27" t="n"/>
       <c r="T848" s="26" t="n"/>
-      <c r="U848" s="26" t="n"/>
     </row>
     <row r="849">
       <c r="B849" s="26" t="n"/>
@@ -16025,7 +15182,6 @@
       <c r="O849" s="27" t="n"/>
       <c r="Q849" s="27" t="n"/>
       <c r="T849" s="26" t="n"/>
-      <c r="U849" s="26" t="n"/>
     </row>
     <row r="850">
       <c r="B850" s="26" t="n"/>
@@ -16043,7 +15199,6 @@
       <c r="O850" s="27" t="n"/>
       <c r="Q850" s="27" t="n"/>
       <c r="T850" s="26" t="n"/>
-      <c r="U850" s="26" t="n"/>
     </row>
     <row r="851">
       <c r="B851" s="26" t="n"/>
@@ -16061,7 +15216,6 @@
       <c r="O851" s="27" t="n"/>
       <c r="Q851" s="27" t="n"/>
       <c r="T851" s="26" t="n"/>
-      <c r="U851" s="26" t="n"/>
     </row>
     <row r="852">
       <c r="B852" s="26" t="n"/>
@@ -16079,7 +15233,6 @@
       <c r="O852" s="27" t="n"/>
       <c r="Q852" s="27" t="n"/>
       <c r="T852" s="26" t="n"/>
-      <c r="U852" s="26" t="n"/>
     </row>
     <row r="853">
       <c r="B853" s="26" t="n"/>
@@ -16097,7 +15250,6 @@
       <c r="O853" s="27" t="n"/>
       <c r="Q853" s="27" t="n"/>
       <c r="T853" s="26" t="n"/>
-      <c r="U853" s="26" t="n"/>
     </row>
     <row r="854">
       <c r="B854" s="26" t="n"/>
@@ -16115,7 +15267,6 @@
       <c r="O854" s="27" t="n"/>
       <c r="Q854" s="27" t="n"/>
       <c r="T854" s="26" t="n"/>
-      <c r="U854" s="26" t="n"/>
     </row>
     <row r="855">
       <c r="B855" s="26" t="n"/>
@@ -16133,7 +15284,6 @@
       <c r="O855" s="27" t="n"/>
       <c r="Q855" s="27" t="n"/>
       <c r="T855" s="26" t="n"/>
-      <c r="U855" s="26" t="n"/>
     </row>
     <row r="856">
       <c r="B856" s="26" t="n"/>
@@ -16151,7 +15301,6 @@
       <c r="O856" s="27" t="n"/>
       <c r="Q856" s="27" t="n"/>
       <c r="T856" s="26" t="n"/>
-      <c r="U856" s="26" t="n"/>
     </row>
     <row r="857">
       <c r="B857" s="26" t="n"/>
@@ -16169,7 +15318,6 @@
       <c r="O857" s="27" t="n"/>
       <c r="Q857" s="27" t="n"/>
       <c r="T857" s="26" t="n"/>
-      <c r="U857" s="26" t="n"/>
     </row>
     <row r="858">
       <c r="B858" s="26" t="n"/>
@@ -16187,7 +15335,6 @@
       <c r="O858" s="27" t="n"/>
       <c r="Q858" s="27" t="n"/>
       <c r="T858" s="26" t="n"/>
-      <c r="U858" s="26" t="n"/>
     </row>
     <row r="859">
       <c r="B859" s="26" t="n"/>
@@ -16205,7 +15352,6 @@
       <c r="O859" s="27" t="n"/>
       <c r="Q859" s="27" t="n"/>
       <c r="T859" s="26" t="n"/>
-      <c r="U859" s="26" t="n"/>
     </row>
     <row r="860">
       <c r="B860" s="26" t="n"/>
@@ -16223,7 +15369,6 @@
       <c r="O860" s="27" t="n"/>
       <c r="Q860" s="27" t="n"/>
       <c r="T860" s="26" t="n"/>
-      <c r="U860" s="26" t="n"/>
     </row>
     <row r="861">
       <c r="B861" s="26" t="n"/>
@@ -16241,7 +15386,6 @@
       <c r="O861" s="27" t="n"/>
       <c r="Q861" s="27" t="n"/>
       <c r="T861" s="26" t="n"/>
-      <c r="U861" s="26" t="n"/>
     </row>
     <row r="862">
       <c r="B862" s="26" t="n"/>
@@ -16259,7 +15403,6 @@
       <c r="O862" s="27" t="n"/>
       <c r="Q862" s="27" t="n"/>
       <c r="T862" s="26" t="n"/>
-      <c r="U862" s="26" t="n"/>
     </row>
     <row r="863">
       <c r="B863" s="26" t="n"/>
@@ -16277,7 +15420,6 @@
       <c r="O863" s="27" t="n"/>
       <c r="Q863" s="27" t="n"/>
       <c r="T863" s="26" t="n"/>
-      <c r="U863" s="26" t="n"/>
     </row>
     <row r="864">
       <c r="B864" s="26" t="n"/>
@@ -16295,7 +15437,6 @@
       <c r="O864" s="27" t="n"/>
       <c r="Q864" s="27" t="n"/>
       <c r="T864" s="26" t="n"/>
-      <c r="U864" s="26" t="n"/>
     </row>
     <row r="865">
       <c r="B865" s="26" t="n"/>
@@ -16313,7 +15454,6 @@
       <c r="O865" s="27" t="n"/>
       <c r="Q865" s="27" t="n"/>
       <c r="T865" s="26" t="n"/>
-      <c r="U865" s="26" t="n"/>
     </row>
     <row r="866">
       <c r="B866" s="26" t="n"/>
@@ -16331,7 +15471,6 @@
       <c r="O866" s="27" t="n"/>
       <c r="Q866" s="27" t="n"/>
       <c r="T866" s="26" t="n"/>
-      <c r="U866" s="26" t="n"/>
     </row>
     <row r="867">
       <c r="B867" s="26" t="n"/>
@@ -16349,7 +15488,6 @@
       <c r="O867" s="27" t="n"/>
       <c r="Q867" s="27" t="n"/>
       <c r="T867" s="26" t="n"/>
-      <c r="U867" s="26" t="n"/>
     </row>
     <row r="868">
       <c r="B868" s="26" t="n"/>
@@ -16367,7 +15505,6 @@
       <c r="O868" s="27" t="n"/>
       <c r="Q868" s="27" t="n"/>
       <c r="T868" s="26" t="n"/>
-      <c r="U868" s="26" t="n"/>
     </row>
     <row r="869">
       <c r="B869" s="26" t="n"/>
@@ -16385,7 +15522,6 @@
       <c r="O869" s="27" t="n"/>
       <c r="Q869" s="27" t="n"/>
       <c r="T869" s="26" t="n"/>
-      <c r="U869" s="26" t="n"/>
     </row>
     <row r="870">
       <c r="B870" s="26" t="n"/>
@@ -16403,7 +15539,6 @@
       <c r="O870" s="27" t="n"/>
       <c r="Q870" s="27" t="n"/>
       <c r="T870" s="26" t="n"/>
-      <c r="U870" s="26" t="n"/>
     </row>
     <row r="871">
       <c r="B871" s="26" t="n"/>
@@ -16421,7 +15556,6 @@
       <c r="O871" s="27" t="n"/>
       <c r="Q871" s="27" t="n"/>
       <c r="T871" s="26" t="n"/>
-      <c r="U871" s="26" t="n"/>
     </row>
     <row r="872">
       <c r="B872" s="26" t="n"/>
@@ -16439,7 +15573,6 @@
       <c r="O872" s="27" t="n"/>
       <c r="Q872" s="27" t="n"/>
       <c r="T872" s="26" t="n"/>
-      <c r="U872" s="26" t="n"/>
     </row>
     <row r="873">
       <c r="B873" s="26" t="n"/>
@@ -16457,7 +15590,6 @@
       <c r="O873" s="27" t="n"/>
       <c r="Q873" s="27" t="n"/>
       <c r="T873" s="26" t="n"/>
-      <c r="U873" s="26" t="n"/>
     </row>
     <row r="874">
       <c r="B874" s="26" t="n"/>
@@ -16475,7 +15607,6 @@
       <c r="O874" s="27" t="n"/>
       <c r="Q874" s="27" t="n"/>
       <c r="T874" s="26" t="n"/>
-      <c r="U874" s="26" t="n"/>
     </row>
     <row r="875">
       <c r="B875" s="26" t="n"/>
@@ -16493,7 +15624,6 @@
       <c r="O875" s="27" t="n"/>
       <c r="Q875" s="27" t="n"/>
       <c r="T875" s="26" t="n"/>
-      <c r="U875" s="26" t="n"/>
     </row>
     <row r="876">
       <c r="B876" s="26" t="n"/>
@@ -16511,7 +15641,6 @@
       <c r="O876" s="27" t="n"/>
       <c r="Q876" s="27" t="n"/>
       <c r="T876" s="26" t="n"/>
-      <c r="U876" s="26" t="n"/>
     </row>
     <row r="877">
       <c r="B877" s="26" t="n"/>
@@ -16529,7 +15658,6 @@
       <c r="O877" s="27" t="n"/>
       <c r="Q877" s="27" t="n"/>
       <c r="T877" s="26" t="n"/>
-      <c r="U877" s="26" t="n"/>
     </row>
     <row r="878">
       <c r="B878" s="26" t="n"/>
@@ -16547,7 +15675,6 @@
       <c r="O878" s="27" t="n"/>
       <c r="Q878" s="27" t="n"/>
       <c r="T878" s="26" t="n"/>
-      <c r="U878" s="26" t="n"/>
     </row>
     <row r="879">
       <c r="B879" s="26" t="n"/>
@@ -16565,7 +15692,6 @@
       <c r="O879" s="27" t="n"/>
       <c r="Q879" s="27" t="n"/>
       <c r="T879" s="26" t="n"/>
-      <c r="U879" s="26" t="n"/>
     </row>
     <row r="880">
       <c r="B880" s="26" t="n"/>
@@ -16583,7 +15709,6 @@
       <c r="O880" s="27" t="n"/>
       <c r="Q880" s="27" t="n"/>
       <c r="T880" s="26" t="n"/>
-      <c r="U880" s="26" t="n"/>
     </row>
     <row r="881">
       <c r="B881" s="26" t="n"/>
@@ -16601,7 +15726,6 @@
       <c r="O881" s="27" t="n"/>
       <c r="Q881" s="27" t="n"/>
       <c r="T881" s="26" t="n"/>
-      <c r="U881" s="26" t="n"/>
     </row>
     <row r="882">
       <c r="B882" s="26" t="n"/>
@@ -16619,7 +15743,6 @@
       <c r="O882" s="27" t="n"/>
       <c r="Q882" s="27" t="n"/>
       <c r="T882" s="26" t="n"/>
-      <c r="U882" s="26" t="n"/>
     </row>
     <row r="883">
       <c r="B883" s="26" t="n"/>
@@ -16637,7 +15760,6 @@
       <c r="O883" s="27" t="n"/>
       <c r="Q883" s="27" t="n"/>
       <c r="T883" s="26" t="n"/>
-      <c r="U883" s="26" t="n"/>
     </row>
     <row r="884">
       <c r="B884" s="26" t="n"/>
@@ -16655,7 +15777,6 @@
       <c r="O884" s="27" t="n"/>
       <c r="Q884" s="27" t="n"/>
       <c r="T884" s="26" t="n"/>
-      <c r="U884" s="26" t="n"/>
     </row>
     <row r="885">
       <c r="B885" s="26" t="n"/>
@@ -16673,7 +15794,6 @@
       <c r="O885" s="27" t="n"/>
       <c r="Q885" s="27" t="n"/>
       <c r="T885" s="26" t="n"/>
-      <c r="U885" s="26" t="n"/>
     </row>
     <row r="886">
       <c r="B886" s="26" t="n"/>
@@ -16691,7 +15811,6 @@
       <c r="O886" s="27" t="n"/>
       <c r="Q886" s="27" t="n"/>
       <c r="T886" s="26" t="n"/>
-      <c r="U886" s="26" t="n"/>
     </row>
     <row r="887">
       <c r="B887" s="26" t="n"/>
@@ -16709,7 +15828,6 @@
       <c r="O887" s="27" t="n"/>
       <c r="Q887" s="27" t="n"/>
       <c r="T887" s="26" t="n"/>
-      <c r="U887" s="26" t="n"/>
     </row>
     <row r="888">
       <c r="B888" s="26" t="n"/>
@@ -16727,7 +15845,6 @@
       <c r="O888" s="27" t="n"/>
       <c r="Q888" s="27" t="n"/>
       <c r="T888" s="26" t="n"/>
-      <c r="U888" s="26" t="n"/>
     </row>
     <row r="889">
       <c r="B889" s="26" t="n"/>
@@ -16745,7 +15862,6 @@
       <c r="O889" s="27" t="n"/>
       <c r="Q889" s="27" t="n"/>
       <c r="T889" s="26" t="n"/>
-      <c r="U889" s="26" t="n"/>
     </row>
     <row r="890">
       <c r="B890" s="26" t="n"/>
@@ -16763,7 +15879,6 @@
       <c r="O890" s="27" t="n"/>
       <c r="Q890" s="27" t="n"/>
       <c r="T890" s="26" t="n"/>
-      <c r="U890" s="26" t="n"/>
     </row>
     <row r="891">
       <c r="B891" s="26" t="n"/>
@@ -16781,7 +15896,6 @@
       <c r="O891" s="27" t="n"/>
       <c r="Q891" s="27" t="n"/>
       <c r="T891" s="26" t="n"/>
-      <c r="U891" s="26" t="n"/>
     </row>
     <row r="892">
       <c r="B892" s="26" t="n"/>
@@ -16799,7 +15913,6 @@
       <c r="O892" s="27" t="n"/>
       <c r="Q892" s="27" t="n"/>
       <c r="T892" s="26" t="n"/>
-      <c r="U892" s="26" t="n"/>
     </row>
     <row r="893">
       <c r="B893" s="26" t="n"/>
@@ -16817,7 +15930,6 @@
       <c r="O893" s="27" t="n"/>
       <c r="Q893" s="27" t="n"/>
       <c r="T893" s="26" t="n"/>
-      <c r="U893" s="26" t="n"/>
     </row>
     <row r="894">
       <c r="B894" s="26" t="n"/>
@@ -16835,7 +15947,6 @@
       <c r="O894" s="27" t="n"/>
       <c r="Q894" s="27" t="n"/>
       <c r="T894" s="26" t="n"/>
-      <c r="U894" s="26" t="n"/>
     </row>
     <row r="895">
       <c r="B895" s="26" t="n"/>
@@ -16853,7 +15964,6 @@
       <c r="O895" s="27" t="n"/>
       <c r="Q895" s="27" t="n"/>
       <c r="T895" s="26" t="n"/>
-      <c r="U895" s="26" t="n"/>
     </row>
     <row r="896">
       <c r="B896" s="26" t="n"/>
@@ -16871,7 +15981,6 @@
       <c r="O896" s="27" t="n"/>
       <c r="Q896" s="27" t="n"/>
       <c r="T896" s="26" t="n"/>
-      <c r="U896" s="26" t="n"/>
     </row>
     <row r="897">
       <c r="B897" s="26" t="n"/>
@@ -16889,7 +15998,6 @@
       <c r="O897" s="27" t="n"/>
       <c r="Q897" s="27" t="n"/>
       <c r="T897" s="26" t="n"/>
-      <c r="U897" s="26" t="n"/>
     </row>
     <row r="898">
       <c r="B898" s="26" t="n"/>
@@ -16907,7 +16015,6 @@
       <c r="O898" s="27" t="n"/>
       <c r="Q898" s="27" t="n"/>
       <c r="T898" s="26" t="n"/>
-      <c r="U898" s="26" t="n"/>
     </row>
     <row r="899">
       <c r="B899" s="26" t="n"/>
@@ -16925,7 +16032,6 @@
       <c r="O899" s="27" t="n"/>
       <c r="Q899" s="27" t="n"/>
       <c r="T899" s="26" t="n"/>
-      <c r="U899" s="26" t="n"/>
     </row>
     <row r="900">
       <c r="B900" s="26" t="n"/>
@@ -16943,7 +16049,6 @@
       <c r="O900" s="27" t="n"/>
       <c r="Q900" s="27" t="n"/>
       <c r="T900" s="26" t="n"/>
-      <c r="U900" s="26" t="n"/>
     </row>
     <row r="901">
       <c r="B901" s="26" t="n"/>
@@ -16961,7 +16066,6 @@
       <c r="O901" s="27" t="n"/>
       <c r="Q901" s="27" t="n"/>
       <c r="T901" s="26" t="n"/>
-      <c r="U901" s="26" t="n"/>
     </row>
     <row r="902">
       <c r="B902" s="26" t="n"/>
@@ -16979,7 +16083,6 @@
       <c r="O902" s="27" t="n"/>
       <c r="Q902" s="27" t="n"/>
       <c r="T902" s="26" t="n"/>
-      <c r="U902" s="26" t="n"/>
     </row>
     <row r="903">
       <c r="B903" s="26" t="n"/>
@@ -16997,7 +16100,6 @@
       <c r="O903" s="27" t="n"/>
       <c r="Q903" s="27" t="n"/>
       <c r="T903" s="26" t="n"/>
-      <c r="U903" s="26" t="n"/>
     </row>
     <row r="904">
       <c r="B904" s="26" t="n"/>
@@ -17015,7 +16117,6 @@
       <c r="O904" s="27" t="n"/>
       <c r="Q904" s="27" t="n"/>
       <c r="T904" s="26" t="n"/>
-      <c r="U904" s="26" t="n"/>
     </row>
     <row r="905">
       <c r="B905" s="26" t="n"/>
@@ -17033,7 +16134,6 @@
       <c r="O905" s="27" t="n"/>
       <c r="Q905" s="27" t="n"/>
       <c r="T905" s="26" t="n"/>
-      <c r="U905" s="26" t="n"/>
     </row>
     <row r="906">
       <c r="B906" s="26" t="n"/>
@@ -17051,7 +16151,6 @@
       <c r="O906" s="27" t="n"/>
       <c r="Q906" s="27" t="n"/>
       <c r="T906" s="26" t="n"/>
-      <c r="U906" s="26" t="n"/>
     </row>
     <row r="907">
       <c r="B907" s="26" t="n"/>
@@ -17069,7 +16168,6 @@
       <c r="O907" s="27" t="n"/>
       <c r="Q907" s="27" t="n"/>
       <c r="T907" s="26" t="n"/>
-      <c r="U907" s="26" t="n"/>
     </row>
     <row r="908">
       <c r="B908" s="26" t="n"/>
@@ -17087,7 +16185,6 @@
       <c r="O908" s="27" t="n"/>
       <c r="Q908" s="27" t="n"/>
       <c r="T908" s="26" t="n"/>
-      <c r="U908" s="26" t="n"/>
     </row>
     <row r="909">
       <c r="B909" s="26" t="n"/>
@@ -17105,7 +16202,6 @@
       <c r="O909" s="27" t="n"/>
       <c r="Q909" s="27" t="n"/>
       <c r="T909" s="26" t="n"/>
-      <c r="U909" s="26" t="n"/>
     </row>
     <row r="910">
       <c r="B910" s="26" t="n"/>
@@ -17123,7 +16219,6 @@
       <c r="O910" s="27" t="n"/>
       <c r="Q910" s="27" t="n"/>
       <c r="T910" s="26" t="n"/>
-      <c r="U910" s="26" t="n"/>
     </row>
     <row r="911">
       <c r="B911" s="26" t="n"/>
@@ -17141,7 +16236,6 @@
       <c r="O911" s="27" t="n"/>
       <c r="Q911" s="27" t="n"/>
       <c r="T911" s="26" t="n"/>
-      <c r="U911" s="26" t="n"/>
     </row>
     <row r="912">
       <c r="B912" s="26" t="n"/>
@@ -17159,7 +16253,6 @@
       <c r="O912" s="27" t="n"/>
       <c r="Q912" s="27" t="n"/>
       <c r="T912" s="26" t="n"/>
-      <c r="U912" s="26" t="n"/>
     </row>
     <row r="913">
       <c r="B913" s="26" t="n"/>
@@ -17177,7 +16270,6 @@
       <c r="O913" s="27" t="n"/>
       <c r="Q913" s="27" t="n"/>
       <c r="T913" s="26" t="n"/>
-      <c r="U913" s="26" t="n"/>
     </row>
     <row r="914">
       <c r="B914" s="26" t="n"/>
@@ -17195,7 +16287,6 @@
       <c r="O914" s="27" t="n"/>
       <c r="Q914" s="27" t="n"/>
       <c r="T914" s="26" t="n"/>
-      <c r="U914" s="26" t="n"/>
     </row>
     <row r="915">
       <c r="B915" s="26" t="n"/>
@@ -17213,7 +16304,6 @@
       <c r="O915" s="27" t="n"/>
       <c r="Q915" s="27" t="n"/>
       <c r="T915" s="26" t="n"/>
-      <c r="U915" s="26" t="n"/>
     </row>
     <row r="916">
       <c r="B916" s="26" t="n"/>
@@ -17231,7 +16321,6 @@
       <c r="O916" s="27" t="n"/>
       <c r="Q916" s="27" t="n"/>
       <c r="T916" s="26" t="n"/>
-      <c r="U916" s="26" t="n"/>
     </row>
     <row r="917">
       <c r="B917" s="26" t="n"/>
@@ -17249,7 +16338,6 @@
       <c r="O917" s="27" t="n"/>
       <c r="Q917" s="27" t="n"/>
       <c r="T917" s="26" t="n"/>
-      <c r="U917" s="26" t="n"/>
     </row>
     <row r="918">
       <c r="B918" s="26" t="n"/>
@@ -17267,7 +16355,6 @@
       <c r="O918" s="27" t="n"/>
       <c r="Q918" s="27" t="n"/>
       <c r="T918" s="26" t="n"/>
-      <c r="U918" s="26" t="n"/>
     </row>
     <row r="919">
       <c r="B919" s="26" t="n"/>
@@ -17285,7 +16372,6 @@
       <c r="O919" s="27" t="n"/>
       <c r="Q919" s="27" t="n"/>
       <c r="T919" s="26" t="n"/>
-      <c r="U919" s="26" t="n"/>
     </row>
     <row r="920">
       <c r="B920" s="26" t="n"/>
@@ -17303,7 +16389,6 @@
       <c r="O920" s="27" t="n"/>
       <c r="Q920" s="27" t="n"/>
       <c r="T920" s="26" t="n"/>
-      <c r="U920" s="26" t="n"/>
     </row>
     <row r="921">
       <c r="B921" s="26" t="n"/>
@@ -17321,7 +16406,6 @@
       <c r="O921" s="27" t="n"/>
       <c r="Q921" s="27" t="n"/>
       <c r="T921" s="26" t="n"/>
-      <c r="U921" s="26" t="n"/>
     </row>
     <row r="922">
       <c r="B922" s="26" t="n"/>
@@ -17339,7 +16423,6 @@
       <c r="O922" s="27" t="n"/>
       <c r="Q922" s="27" t="n"/>
       <c r="T922" s="26" t="n"/>
-      <c r="U922" s="26" t="n"/>
     </row>
     <row r="923">
       <c r="B923" s="26" t="n"/>
@@ -17357,7 +16440,6 @@
       <c r="O923" s="27" t="n"/>
       <c r="Q923" s="27" t="n"/>
       <c r="T923" s="26" t="n"/>
-      <c r="U923" s="26" t="n"/>
     </row>
     <row r="924">
       <c r="B924" s="26" t="n"/>
@@ -17375,7 +16457,6 @@
       <c r="O924" s="27" t="n"/>
       <c r="Q924" s="27" t="n"/>
       <c r="T924" s="26" t="n"/>
-      <c r="U924" s="26" t="n"/>
     </row>
     <row r="925">
       <c r="B925" s="26" t="n"/>
@@ -17393,7 +16474,6 @@
       <c r="O925" s="27" t="n"/>
       <c r="Q925" s="27" t="n"/>
       <c r="T925" s="26" t="n"/>
-      <c r="U925" s="26" t="n"/>
     </row>
     <row r="926">
       <c r="B926" s="26" t="n"/>
@@ -17411,7 +16491,6 @@
       <c r="O926" s="27" t="n"/>
       <c r="Q926" s="27" t="n"/>
       <c r="T926" s="26" t="n"/>
-      <c r="U926" s="26" t="n"/>
     </row>
     <row r="927">
       <c r="B927" s="26" t="n"/>
@@ -17429,7 +16508,6 @@
       <c r="O927" s="27" t="n"/>
       <c r="Q927" s="27" t="n"/>
       <c r="T927" s="26" t="n"/>
-      <c r="U927" s="26" t="n"/>
     </row>
     <row r="928">
       <c r="B928" s="26" t="n"/>
@@ -17447,7 +16525,6 @@
       <c r="O928" s="27" t="n"/>
       <c r="Q928" s="27" t="n"/>
       <c r="T928" s="26" t="n"/>
-      <c r="U928" s="26" t="n"/>
     </row>
     <row r="929">
       <c r="B929" s="26" t="n"/>
@@ -17465,7 +16542,6 @@
       <c r="O929" s="27" t="n"/>
       <c r="Q929" s="27" t="n"/>
       <c r="T929" s="26" t="n"/>
-      <c r="U929" s="26" t="n"/>
     </row>
     <row r="930">
       <c r="B930" s="26" t="n"/>
@@ -17483,7 +16559,6 @@
       <c r="O930" s="27" t="n"/>
       <c r="Q930" s="27" t="n"/>
       <c r="T930" s="26" t="n"/>
-      <c r="U930" s="26" t="n"/>
     </row>
     <row r="931">
       <c r="B931" s="26" t="n"/>
@@ -17501,7 +16576,6 @@
       <c r="O931" s="27" t="n"/>
       <c r="Q931" s="27" t="n"/>
       <c r="T931" s="26" t="n"/>
-      <c r="U931" s="26" t="n"/>
     </row>
     <row r="932">
       <c r="B932" s="26" t="n"/>
@@ -17519,7 +16593,6 @@
       <c r="O932" s="27" t="n"/>
       <c r="Q932" s="27" t="n"/>
       <c r="T932" s="26" t="n"/>
-      <c r="U932" s="26" t="n"/>
     </row>
     <row r="933">
       <c r="B933" s="26" t="n"/>
@@ -17537,7 +16610,6 @@
       <c r="O933" s="27" t="n"/>
       <c r="Q933" s="27" t="n"/>
       <c r="T933" s="26" t="n"/>
-      <c r="U933" s="26" t="n"/>
     </row>
     <row r="934">
       <c r="B934" s="26" t="n"/>
@@ -17555,7 +16627,6 @@
       <c r="O934" s="27" t="n"/>
       <c r="Q934" s="27" t="n"/>
       <c r="T934" s="26" t="n"/>
-      <c r="U934" s="26" t="n"/>
     </row>
     <row r="935">
       <c r="B935" s="26" t="n"/>
@@ -17573,7 +16644,6 @@
       <c r="O935" s="27" t="n"/>
       <c r="Q935" s="27" t="n"/>
       <c r="T935" s="26" t="n"/>
-      <c r="U935" s="26" t="n"/>
     </row>
     <row r="936">
       <c r="B936" s="26" t="n"/>
@@ -17591,7 +16661,6 @@
       <c r="O936" s="27" t="n"/>
       <c r="Q936" s="27" t="n"/>
       <c r="T936" s="26" t="n"/>
-      <c r="U936" s="26" t="n"/>
     </row>
     <row r="937">
       <c r="B937" s="26" t="n"/>
@@ -17609,7 +16678,6 @@
       <c r="O937" s="27" t="n"/>
       <c r="Q937" s="27" t="n"/>
       <c r="T937" s="26" t="n"/>
-      <c r="U937" s="26" t="n"/>
     </row>
     <row r="938">
       <c r="B938" s="26" t="n"/>
@@ -17627,7 +16695,6 @@
       <c r="O938" s="27" t="n"/>
       <c r="Q938" s="27" t="n"/>
       <c r="T938" s="26" t="n"/>
-      <c r="U938" s="26" t="n"/>
     </row>
     <row r="939">
       <c r="B939" s="26" t="n"/>
@@ -17645,7 +16712,6 @@
       <c r="O939" s="27" t="n"/>
       <c r="Q939" s="27" t="n"/>
       <c r="T939" s="26" t="n"/>
-      <c r="U939" s="26" t="n"/>
     </row>
     <row r="940">
       <c r="B940" s="26" t="n"/>
@@ -17663,7 +16729,6 @@
       <c r="O940" s="27" t="n"/>
       <c r="Q940" s="27" t="n"/>
       <c r="T940" s="26" t="n"/>
-      <c r="U940" s="26" t="n"/>
     </row>
     <row r="941">
       <c r="B941" s="26" t="n"/>
@@ -17681,7 +16746,6 @@
       <c r="O941" s="27" t="n"/>
       <c r="Q941" s="27" t="n"/>
       <c r="T941" s="26" t="n"/>
-      <c r="U941" s="26" t="n"/>
     </row>
     <row r="942">
       <c r="B942" s="26" t="n"/>
@@ -17699,7 +16763,6 @@
       <c r="O942" s="27" t="n"/>
       <c r="Q942" s="27" t="n"/>
       <c r="T942" s="26" t="n"/>
-      <c r="U942" s="26" t="n"/>
     </row>
     <row r="943">
       <c r="B943" s="26" t="n"/>
@@ -17717,7 +16780,6 @@
       <c r="O943" s="27" t="n"/>
       <c r="Q943" s="27" t="n"/>
       <c r="T943" s="26" t="n"/>
-      <c r="U943" s="26" t="n"/>
     </row>
     <row r="944">
       <c r="B944" s="26" t="n"/>
@@ -17735,7 +16797,6 @@
       <c r="O944" s="27" t="n"/>
       <c r="Q944" s="27" t="n"/>
       <c r="T944" s="26" t="n"/>
-      <c r="U944" s="26" t="n"/>
     </row>
     <row r="945">
       <c r="B945" s="26" t="n"/>
@@ -17753,7 +16814,6 @@
       <c r="O945" s="27" t="n"/>
       <c r="Q945" s="27" t="n"/>
       <c r="T945" s="26" t="n"/>
-      <c r="U945" s="26" t="n"/>
     </row>
     <row r="946">
       <c r="B946" s="26" t="n"/>
@@ -17771,7 +16831,6 @@
       <c r="O946" s="27" t="n"/>
       <c r="Q946" s="27" t="n"/>
       <c r="T946" s="26" t="n"/>
-      <c r="U946" s="26" t="n"/>
     </row>
     <row r="947">
       <c r="B947" s="26" t="n"/>
@@ -17789,7 +16848,6 @@
       <c r="O947" s="27" t="n"/>
       <c r="Q947" s="27" t="n"/>
       <c r="T947" s="26" t="n"/>
-      <c r="U947" s="26" t="n"/>
     </row>
     <row r="948">
       <c r="B948" s="26" t="n"/>
@@ -17807,7 +16865,6 @@
       <c r="O948" s="27" t="n"/>
       <c r="Q948" s="27" t="n"/>
       <c r="T948" s="26" t="n"/>
-      <c r="U948" s="26" t="n"/>
     </row>
     <row r="949">
       <c r="B949" s="26" t="n"/>
@@ -17825,7 +16882,6 @@
       <c r="O949" s="27" t="n"/>
       <c r="Q949" s="27" t="n"/>
       <c r="T949" s="26" t="n"/>
-      <c r="U949" s="26" t="n"/>
     </row>
     <row r="950">
       <c r="B950" s="26" t="n"/>
@@ -17843,7 +16899,6 @@
       <c r="O950" s="27" t="n"/>
       <c r="Q950" s="27" t="n"/>
       <c r="T950" s="26" t="n"/>
-      <c r="U950" s="26" t="n"/>
     </row>
     <row r="951">
       <c r="B951" s="26" t="n"/>
@@ -17861,7 +16916,6 @@
       <c r="O951" s="27" t="n"/>
       <c r="Q951" s="27" t="n"/>
       <c r="T951" s="26" t="n"/>
-      <c r="U951" s="26" t="n"/>
     </row>
     <row r="952">
       <c r="B952" s="26" t="n"/>
@@ -17879,7 +16933,6 @@
       <c r="O952" s="27" t="n"/>
       <c r="Q952" s="27" t="n"/>
       <c r="T952" s="26" t="n"/>
-      <c r="U952" s="26" t="n"/>
     </row>
     <row r="953">
       <c r="B953" s="26" t="n"/>
@@ -17897,7 +16950,6 @@
       <c r="O953" s="27" t="n"/>
       <c r="Q953" s="27" t="n"/>
       <c r="T953" s="26" t="n"/>
-      <c r="U953" s="26" t="n"/>
     </row>
     <row r="954">
       <c r="B954" s="26" t="n"/>
@@ -17915,7 +16967,6 @@
       <c r="O954" s="27" t="n"/>
       <c r="Q954" s="27" t="n"/>
       <c r="T954" s="26" t="n"/>
-      <c r="U954" s="26" t="n"/>
     </row>
     <row r="955">
       <c r="B955" s="26" t="n"/>
@@ -17933,7 +16984,6 @@
       <c r="O955" s="27" t="n"/>
       <c r="Q955" s="27" t="n"/>
       <c r="T955" s="26" t="n"/>
-      <c r="U955" s="26" t="n"/>
     </row>
     <row r="956">
       <c r="B956" s="26" t="n"/>
@@ -17951,7 +17001,6 @@
       <c r="O956" s="27" t="n"/>
       <c r="Q956" s="27" t="n"/>
       <c r="T956" s="26" t="n"/>
-      <c r="U956" s="26" t="n"/>
     </row>
     <row r="957">
       <c r="B957" s="26" t="n"/>
@@ -17969,7 +17018,6 @@
       <c r="O957" s="27" t="n"/>
       <c r="Q957" s="27" t="n"/>
       <c r="T957" s="26" t="n"/>
-      <c r="U957" s="26" t="n"/>
     </row>
     <row r="958">
       <c r="B958" s="26" t="n"/>
@@ -17987,7 +17035,6 @@
       <c r="O958" s="27" t="n"/>
       <c r="Q958" s="27" t="n"/>
       <c r="T958" s="26" t="n"/>
-      <c r="U958" s="26" t="n"/>
     </row>
     <row r="959">
       <c r="B959" s="26" t="n"/>
@@ -18005,7 +17052,6 @@
       <c r="O959" s="27" t="n"/>
       <c r="Q959" s="27" t="n"/>
       <c r="T959" s="26" t="n"/>
-      <c r="U959" s="26" t="n"/>
     </row>
     <row r="960">
       <c r="B960" s="26" t="n"/>
@@ -18023,7 +17069,6 @@
       <c r="O960" s="27" t="n"/>
       <c r="Q960" s="27" t="n"/>
       <c r="T960" s="26" t="n"/>
-      <c r="U960" s="26" t="n"/>
     </row>
     <row r="961">
       <c r="B961" s="26" t="n"/>
@@ -18041,7 +17086,6 @@
       <c r="O961" s="27" t="n"/>
       <c r="Q961" s="27" t="n"/>
       <c r="T961" s="26" t="n"/>
-      <c r="U961" s="26" t="n"/>
     </row>
     <row r="962">
       <c r="B962" s="26" t="n"/>
@@ -18059,7 +17103,6 @@
       <c r="O962" s="27" t="n"/>
       <c r="Q962" s="27" t="n"/>
       <c r="T962" s="26" t="n"/>
-      <c r="U962" s="26" t="n"/>
     </row>
     <row r="963">
       <c r="B963" s="26" t="n"/>
@@ -18077,7 +17120,6 @@
       <c r="O963" s="27" t="n"/>
       <c r="Q963" s="27" t="n"/>
       <c r="T963" s="26" t="n"/>
-      <c r="U963" s="26" t="n"/>
     </row>
     <row r="964">
       <c r="B964" s="26" t="n"/>
@@ -18095,7 +17137,6 @@
       <c r="O964" s="27" t="n"/>
       <c r="Q964" s="27" t="n"/>
       <c r="T964" s="26" t="n"/>
-      <c r="U964" s="26" t="n"/>
     </row>
     <row r="965">
       <c r="B965" s="26" t="n"/>
@@ -18113,7 +17154,6 @@
       <c r="O965" s="27" t="n"/>
       <c r="Q965" s="27" t="n"/>
       <c r="T965" s="26" t="n"/>
-      <c r="U965" s="26" t="n"/>
     </row>
     <row r="966">
       <c r="B966" s="26" t="n"/>
@@ -18131,7 +17171,6 @@
       <c r="O966" s="27" t="n"/>
       <c r="Q966" s="27" t="n"/>
       <c r="T966" s="26" t="n"/>
-      <c r="U966" s="26" t="n"/>
     </row>
     <row r="967">
       <c r="B967" s="26" t="n"/>
@@ -18149,7 +17188,6 @@
       <c r="O967" s="27" t="n"/>
       <c r="Q967" s="27" t="n"/>
       <c r="T967" s="26" t="n"/>
-      <c r="U967" s="26" t="n"/>
     </row>
     <row r="968">
       <c r="B968" s="26" t="n"/>
@@ -18167,7 +17205,6 @@
       <c r="O968" s="27" t="n"/>
       <c r="Q968" s="27" t="n"/>
       <c r="T968" s="26" t="n"/>
-      <c r="U968" s="26" t="n"/>
     </row>
     <row r="969">
       <c r="B969" s="26" t="n"/>
@@ -18185,7 +17222,6 @@
       <c r="O969" s="27" t="n"/>
       <c r="Q969" s="27" t="n"/>
       <c r="T969" s="26" t="n"/>
-      <c r="U969" s="26" t="n"/>
     </row>
     <row r="970">
       <c r="B970" s="26" t="n"/>
@@ -18203,7 +17239,6 @@
       <c r="O970" s="27" t="n"/>
       <c r="Q970" s="27" t="n"/>
       <c r="T970" s="26" t="n"/>
-      <c r="U970" s="26" t="n"/>
     </row>
     <row r="971">
       <c r="B971" s="26" t="n"/>
@@ -18221,7 +17256,6 @@
       <c r="O971" s="27" t="n"/>
       <c r="Q971" s="27" t="n"/>
       <c r="T971" s="26" t="n"/>
-      <c r="U971" s="26" t="n"/>
     </row>
     <row r="972">
       <c r="B972" s="26" t="n"/>
@@ -18239,7 +17273,6 @@
       <c r="O972" s="27" t="n"/>
       <c r="Q972" s="27" t="n"/>
       <c r="T972" s="26" t="n"/>
-      <c r="U972" s="26" t="n"/>
     </row>
     <row r="973">
       <c r="B973" s="26" t="n"/>
@@ -18257,7 +17290,6 @@
       <c r="O973" s="27" t="n"/>
       <c r="Q973" s="27" t="n"/>
       <c r="T973" s="26" t="n"/>
-      <c r="U973" s="26" t="n"/>
     </row>
     <row r="974">
       <c r="B974" s="26" t="n"/>
@@ -18275,7 +17307,6 @@
       <c r="O974" s="27" t="n"/>
       <c r="Q974" s="27" t="n"/>
       <c r="T974" s="26" t="n"/>
-      <c r="U974" s="26" t="n"/>
     </row>
     <row r="975">
       <c r="B975" s="26" t="n"/>
@@ -18293,7 +17324,6 @@
       <c r="O975" s="27" t="n"/>
       <c r="Q975" s="27" t="n"/>
       <c r="T975" s="26" t="n"/>
-      <c r="U975" s="26" t="n"/>
     </row>
     <row r="976">
       <c r="B976" s="26" t="n"/>
@@ -18311,7 +17341,6 @@
       <c r="O976" s="27" t="n"/>
       <c r="Q976" s="27" t="n"/>
       <c r="T976" s="26" t="n"/>
-      <c r="U976" s="26" t="n"/>
     </row>
     <row r="977">
       <c r="B977" s="26" t="n"/>
@@ -18329,7 +17358,6 @@
       <c r="O977" s="27" t="n"/>
       <c r="Q977" s="27" t="n"/>
       <c r="T977" s="26" t="n"/>
-      <c r="U977" s="26" t="n"/>
     </row>
     <row r="978">
       <c r="B978" s="26" t="n"/>
@@ -18347,7 +17375,6 @@
       <c r="O978" s="27" t="n"/>
       <c r="Q978" s="27" t="n"/>
       <c r="T978" s="26" t="n"/>
-      <c r="U978" s="26" t="n"/>
     </row>
     <row r="979">
       <c r="B979" s="26" t="n"/>
@@ -18365,7 +17392,6 @@
       <c r="O979" s="27" t="n"/>
       <c r="Q979" s="27" t="n"/>
       <c r="T979" s="26" t="n"/>
-      <c r="U979" s="26" t="n"/>
     </row>
     <row r="980">
       <c r="B980" s="26" t="n"/>
@@ -18383,7 +17409,6 @@
       <c r="O980" s="27" t="n"/>
       <c r="Q980" s="27" t="n"/>
       <c r="T980" s="26" t="n"/>
-      <c r="U980" s="26" t="n"/>
     </row>
     <row r="981">
       <c r="B981" s="26" t="n"/>
@@ -18401,7 +17426,6 @@
       <c r="O981" s="27" t="n"/>
       <c r="Q981" s="27" t="n"/>
       <c r="T981" s="26" t="n"/>
-      <c r="U981" s="26" t="n"/>
     </row>
     <row r="982">
       <c r="B982" s="26" t="n"/>
@@ -18419,7 +17443,6 @@
       <c r="O982" s="27" t="n"/>
       <c r="Q982" s="27" t="n"/>
       <c r="T982" s="26" t="n"/>
-      <c r="U982" s="26" t="n"/>
     </row>
     <row r="983">
       <c r="B983" s="26" t="n"/>
@@ -18437,7 +17460,6 @@
       <c r="O983" s="27" t="n"/>
       <c r="Q983" s="27" t="n"/>
       <c r="T983" s="26" t="n"/>
-      <c r="U983" s="26" t="n"/>
     </row>
     <row r="984">
       <c r="B984" s="26" t="n"/>
@@ -18455,7 +17477,6 @@
       <c r="O984" s="27" t="n"/>
       <c r="Q984" s="27" t="n"/>
       <c r="T984" s="26" t="n"/>
-      <c r="U984" s="26" t="n"/>
     </row>
     <row r="985">
       <c r="B985" s="26" t="n"/>
@@ -18473,7 +17494,6 @@
       <c r="O985" s="27" t="n"/>
       <c r="Q985" s="27" t="n"/>
       <c r="T985" s="26" t="n"/>
-      <c r="U985" s="26" t="n"/>
     </row>
     <row r="986">
       <c r="B986" s="26" t="n"/>
@@ -18491,7 +17511,6 @@
       <c r="O986" s="27" t="n"/>
       <c r="Q986" s="27" t="n"/>
       <c r="T986" s="26" t="n"/>
-      <c r="U986" s="26" t="n"/>
     </row>
     <row r="987">
       <c r="B987" s="26" t="n"/>
@@ -18509,7 +17528,6 @@
       <c r="O987" s="27" t="n"/>
       <c r="Q987" s="27" t="n"/>
       <c r="T987" s="26" t="n"/>
-      <c r="U987" s="26" t="n"/>
     </row>
     <row r="988">
       <c r="B988" s="26" t="n"/>
@@ -18527,7 +17545,6 @@
       <c r="O988" s="27" t="n"/>
       <c r="Q988" s="27" t="n"/>
       <c r="T988" s="26" t="n"/>
-      <c r="U988" s="26" t="n"/>
     </row>
     <row r="989">
       <c r="B989" s="26" t="n"/>
@@ -18545,7 +17562,6 @@
       <c r="O989" s="27" t="n"/>
       <c r="Q989" s="27" t="n"/>
       <c r="T989" s="26" t="n"/>
-      <c r="U989" s="26" t="n"/>
     </row>
     <row r="990">
       <c r="B990" s="26" t="n"/>
@@ -18563,7 +17579,6 @@
       <c r="O990" s="27" t="n"/>
       <c r="Q990" s="27" t="n"/>
       <c r="T990" s="26" t="n"/>
-      <c r="U990" s="26" t="n"/>
     </row>
     <row r="991">
       <c r="B991" s="26" t="n"/>
@@ -18581,7 +17596,6 @@
       <c r="O991" s="27" t="n"/>
       <c r="Q991" s="27" t="n"/>
       <c r="T991" s="26" t="n"/>
-      <c r="U991" s="26" t="n"/>
     </row>
     <row r="992">
       <c r="B992" s="26" t="n"/>
@@ -18599,7 +17613,6 @@
       <c r="O992" s="27" t="n"/>
       <c r="Q992" s="27" t="n"/>
       <c r="T992" s="26" t="n"/>
-      <c r="U992" s="26" t="n"/>
     </row>
     <row r="993">
       <c r="B993" s="26" t="n"/>
@@ -18617,7 +17630,6 @@
       <c r="O993" s="27" t="n"/>
       <c r="Q993" s="27" t="n"/>
       <c r="T993" s="26" t="n"/>
-      <c r="U993" s="26" t="n"/>
     </row>
     <row r="994">
       <c r="B994" s="26" t="n"/>
@@ -18635,7 +17647,6 @@
       <c r="O994" s="27" t="n"/>
       <c r="Q994" s="27" t="n"/>
       <c r="T994" s="26" t="n"/>
-      <c r="U994" s="26" t="n"/>
     </row>
     <row r="995">
       <c r="B995" s="26" t="n"/>
@@ -18653,7 +17664,6 @@
       <c r="O995" s="27" t="n"/>
       <c r="Q995" s="27" t="n"/>
       <c r="T995" s="26" t="n"/>
-      <c r="U995" s="26" t="n"/>
     </row>
     <row r="996">
       <c r="B996" s="26" t="n"/>
@@ -18671,7 +17681,6 @@
       <c r="O996" s="27" t="n"/>
       <c r="Q996" s="27" t="n"/>
       <c r="T996" s="26" t="n"/>
-      <c r="U996" s="26" t="n"/>
     </row>
     <row r="997">
       <c r="B997" s="26" t="n"/>
@@ -18689,7 +17698,6 @@
       <c r="O997" s="27" t="n"/>
       <c r="Q997" s="27" t="n"/>
       <c r="T997" s="26" t="n"/>
-      <c r="U997" s="26" t="n"/>
     </row>
     <row r="998">
       <c r="B998" s="26" t="n"/>
@@ -18707,7 +17715,6 @@
       <c r="O998" s="27" t="n"/>
       <c r="Q998" s="27" t="n"/>
       <c r="T998" s="26" t="n"/>
-      <c r="U998" s="26" t="n"/>
     </row>
     <row r="999">
       <c r="B999" s="26" t="n"/>
@@ -18725,7 +17732,6 @@
       <c r="O999" s="27" t="n"/>
       <c r="Q999" s="27" t="n"/>
       <c r="T999" s="26" t="n"/>
-      <c r="U999" s="26" t="n"/>
     </row>
     <row r="1000">
       <c r="B1000" s="26" t="n"/>
@@ -18743,7 +17749,6 @@
       <c r="O1000" s="27" t="n"/>
       <c r="Q1000" s="27" t="n"/>
       <c r="T1000" s="26" t="n"/>
-      <c r="U1000" s="26" t="n"/>
     </row>
     <row r="1001">
       <c r="B1001" s="26" t="n"/>
@@ -18761,7 +17766,6 @@
       <c r="O1001" s="27" t="n"/>
       <c r="Q1001" s="27" t="n"/>
       <c r="T1001" s="26" t="n"/>
-      <c r="U1001" s="26" t="n"/>
     </row>
     <row r="1002">
       <c r="B1002" s="26" t="n"/>
@@ -18779,7 +17783,6 @@
       <c r="O1002" s="27" t="n"/>
       <c r="Q1002" s="27" t="n"/>
       <c r="T1002" s="26" t="n"/>
-      <c r="U1002" s="26" t="n"/>
     </row>
     <row r="1003">
       <c r="B1003" s="26" t="n"/>
@@ -18797,7 +17800,6 @@
       <c r="O1003" s="27" t="n"/>
       <c r="Q1003" s="27" t="n"/>
       <c r="T1003" s="26" t="n"/>
-      <c r="U1003" s="26" t="n"/>
     </row>
     <row r="1004">
       <c r="B1004" s="26" t="n"/>
@@ -18815,10 +17817,9 @@
       <c r="O1004" s="27" t="n"/>
       <c r="Q1004" s="27" t="n"/>
       <c r="T1004" s="26" t="n"/>
-      <c r="U1004" s="26" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:U4"/>
+  <autoFilter ref="A4:T4"/>
   <mergeCells count="6">
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="A1:S1"/>
@@ -18827,12 +17828,15 @@
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A2:S2"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="G5:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"نعم,لا,TRUE,FALSE"</formula1>
     </dataValidation>
     <dataValidation sqref="R5:R1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"single,three"</formula1>
+    </dataValidation>
+    <dataValidation sqref="U5:U1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"residential,commercial,industrial"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18845,10 +17849,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="110" customWidth="1" min="2" max="2"/>
     <col width="44" customWidth="1" min="3" max="3"/>
   </cols>
@@ -18856,9 +17860,10 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="28" t="inlineStr">
         <is>
-          <t>تعليمات الاستيراد — عقد ترحيل رسمي</t>
+          <t>تعليمات استيراد المشتركين — عقد v4</t>
         </is>
       </c>
+      <c r="B1" s="29" t="inlineStr"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="30" t="inlineStr">
@@ -18866,9 +17871,9 @@
           <t>Template Type</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
-          <t>Migration_Template</t>
+          <t>customer</t>
         </is>
       </c>
     </row>
@@ -18878,85 +17883,75 @@
           <t>Template Version</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
+      <c r="B3" s="29" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="30" t="inlineStr">
-        <is>
-          <t>نوع الملف</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>الحقول الإلزامية</t>
         </is>
       </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>name، customer_number، meter_number، phase. mobile اختياري.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>موديل العداد</t>
+        </is>
+      </c>
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>يتم توليد موديل العداد والعداد تلقائياً من النظام اعتماداً على phase. لا تدخل meter_model_id أو meter_model_code أو usage.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="30" t="inlineStr">
-        <is>
-          <t>الحقول الاختيارية</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="30" t="inlineStr">
-        <is>
-          <t>قواعد الهوية</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>القراءات</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="30" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
-          <t>القيم المنطقية</t>
+          <t>opening_reading أولاً ثم meter_reading؛ الفراغ لا ينشئ قراءة، والصفر قراءة صحيحة.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="30" t="inlineStr">
         <is>
-          <t>الطور</t>
+          <t>الأرصدة</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="30" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
-          <t>الأرقام</t>
+          <t>current_balance يقبل القيم الموجبة والصفر والسالبة لأنها أرصدة مالية.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="30" t="inlineStr">
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>تنبيه</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="30" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
-          <t>Example</t>
+          <t>لا تغيّر العناوين، لا تدمج خلايا Data، لا تستخدم صيغاً، واحفظ الأصفار البادئة.</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
-        <is>
-          <t>customer_number=C001، opening_reading=0، phase=single.</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="9" ht="22" customHeight="1"/>
+    <row r="10" ht="22" customHeight="1"/>
+    <row r="11" ht="22" customHeight="1"/>
+    <row r="12" ht="22" customHeight="1"/>
+    <row r="13" ht="24" customHeight="1"/>
     <row r="14" ht="18" customHeight="1"/>
     <row r="15" ht="18" customHeight="1"/>
     <row r="16" ht="18" customHeight="1"/>

--- a/utility_core/static/src/Migration_Template.xlsx
+++ b/utility_core/static/src/Migration_Template.xlsx
@@ -794,7 +794,7 @@
       </c>
       <c r="P4" s="31" t="inlineStr">
         <is>
-          <t>الرصيد السابق (الخط الساخن)</t>
+          <t>الرصيد السابق قبل (الخط الساخن)</t>
         </is>
       </c>
       <c r="Q4" s="31" t="inlineStr">
